--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AFB1F1-8086-4891-AA71-02C7685AD55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1DEE1F-0CE3-4956-947A-495A3CCF0A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
@@ -1429,27 +1429,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1476,6 +1456,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1490,6 +1490,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -1506,12 +1512,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2210,7 +2210,7 @@
       <c r="D28" s="65"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="N1bniBsjFOWLRxdCAar69hrlEM89c03rP7SFp0KDKKg2PT/Fzi93IUEM0/YTx8R/V9C3aAcUX/3BjRYts8Kapw==" saltValue="/7LjJiM4eMOJa+EPUVtI/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -7426,7 +7426,7 @@
       <c r="W204" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OZkxDk4rNmiY0bwTeAfr9sFLtGEt5H7SGRyOhmna/Z5nZRsAqJ268PtC6jmA1a3saGvWIIWSmtFq+H59shqt9A==" saltValue="V9fDjjgPfjxKshOz7dOcQQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="Q3:Q4"/>
@@ -7554,10 +7554,10 @@
       <c r="K3" s="162" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="136" t="s">
+      <c r="L3" s="130" t="s">
         <v>93</v>
       </c>
-      <c r="M3" s="136"/>
+      <c r="M3" s="130"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="159"/>
@@ -10579,7 +10579,7 @@
       <c r="M204" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="l3k+gWAWlR4/pSeTmmgiDsBu7LNk1LybqKqFfe5ZRTKX3jYB4g0VqzxieCU6b7atoPeLQ5HFjUM+Vzp8RJmX3Q==" saltValue="Gc9HWf2uqFK1alO3ASRJ6A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="13">
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
@@ -13091,7 +13091,7 @@
       <c r="J203" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vodLsXrd3Ef6p2Yi+tY4XSxwkIwXrHriY0ruq4Tvpt5nzczjUFfj0aWksF/+1KqHY+2a1APfb9XGkFQJFpIA9g==" saltValue="IuCLLmLdSSOG0cXBMfRCaA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="5">
     <mergeCell ref="E2:J2"/>
     <mergeCell ref="A2:A3"/>
@@ -14784,7 +14784,7 @@
       <c r="F205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AEf8B3NkHMrpwwXPwspM1WvFjieFsxrut9CgnkEo979A3NvoyIwBELW2k8aTLSV9u+x9+Jd1VqFe3PHMux/vog==" saltValue="eRsmOeEOXqnJ+mlZ6hvciA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:F2"/>
@@ -20217,7 +20217,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="37NOUPegG9zFwNZbEG9rJ1fPQH04ua4vUFfqrfSGHK2Y5NsLHTqzLf9lM9U8w+bFRYXqjEzJgmiyi5bcFeIbUw==" saltValue="hJzB/vyeo8DVz6BnSGvclQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="14">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -23813,7 +23813,7 @@
       <c r="O205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1AUsWISJhWm6QtpGotet1zugWWYXk0LTk1oXU2Eoh7GXjBl99fWY7dGeEyfdIGqfr3T+iIGENbiUZDidI+XIaQ==" saltValue="0HwUzD1E8J58Q9wccJliPQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="16">
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="K3:O3"/>
@@ -26572,7 +26572,7 @@
       <c r="K205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/tdCV0IIceWEsiDL5UPg5UK+Bm4XMf3IZiNHcQy+OItWgW3ttFyTgSkF2Oxxq4ozOvGqeXgahohLJPyPIo4UbQ==" saltValue="RiNyU9yX5yrqz0ejzihzdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B3:F3"/>
@@ -26698,113 +26698,113 @@
       <c r="A2" s="88" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="130"/>
-      <c r="S2" s="130"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="125" t="s">
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="124"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="V2" s="126"/>
-      <c r="W2" s="126"/>
-      <c r="X2" s="126"/>
-      <c r="Y2" s="126"/>
-      <c r="Z2" s="126"/>
-      <c r="AA2" s="126"/>
-      <c r="AB2" s="126"/>
-      <c r="AC2" s="126"/>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="126"/>
-      <c r="AG2" s="127"/>
-      <c r="AH2" s="122" t="s">
+      <c r="V2" s="131"/>
+      <c r="W2" s="131"/>
+      <c r="X2" s="131"/>
+      <c r="Y2" s="131"/>
+      <c r="Z2" s="131"/>
+      <c r="AA2" s="131"/>
+      <c r="AB2" s="131"/>
+      <c r="AC2" s="131"/>
+      <c r="AD2" s="131"/>
+      <c r="AE2" s="131"/>
+      <c r="AF2" s="131"/>
+      <c r="AG2" s="132"/>
+      <c r="AH2" s="134" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="122"/>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="122"/>
-      <c r="AO2" s="122"/>
-      <c r="AP2" s="122"/>
-      <c r="AQ2" s="122"/>
-      <c r="AR2" s="122"/>
-      <c r="AS2" s="122"/>
+      <c r="AI2" s="134"/>
+      <c r="AJ2" s="134"/>
+      <c r="AK2" s="134"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="134"/>
+      <c r="AN2" s="134"/>
+      <c r="AO2" s="134"/>
+      <c r="AP2" s="134"/>
+      <c r="AQ2" s="134"/>
+      <c r="AR2" s="134"/>
+      <c r="AS2" s="134"/>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="132"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="N3" s="133"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="133"/>
-      <c r="R3" s="133"/>
-      <c r="S3" s="133"/>
-      <c r="T3" s="134"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="128"/>
       <c r="U3" s="96"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="128"/>
-      <c r="Z3" s="128"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="128"/>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="128"/>
+      <c r="V3" s="133"/>
+      <c r="W3" s="133"/>
+      <c r="X3" s="133"/>
+      <c r="Y3" s="133"/>
+      <c r="Z3" s="133"/>
+      <c r="AA3" s="133"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="133"/>
+      <c r="AD3" s="133"/>
+      <c r="AE3" s="133"/>
+      <c r="AF3" s="133"/>
       <c r="AG3" s="97"/>
-      <c r="AH3" s="122"/>
-      <c r="AI3" s="122"/>
-      <c r="AJ3" s="122"/>
-      <c r="AK3" s="122"/>
-      <c r="AL3" s="122"/>
-      <c r="AM3" s="122"/>
-      <c r="AN3" s="122"/>
-      <c r="AO3" s="122"/>
-      <c r="AP3" s="122"/>
-      <c r="AQ3" s="122"/>
-      <c r="AR3" s="122"/>
-      <c r="AS3" s="122"/>
+      <c r="AH3" s="134"/>
+      <c r="AI3" s="134"/>
+      <c r="AJ3" s="134"/>
+      <c r="AK3" s="134"/>
+      <c r="AL3" s="134"/>
+      <c r="AM3" s="134"/>
+      <c r="AN3" s="134"/>
+      <c r="AO3" s="134"/>
+      <c r="AP3" s="134"/>
+      <c r="AQ3" s="134"/>
+      <c r="AR3" s="134"/>
+      <c r="AS3" s="134"/>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="122" t="s">
         <v>222</v>
       </c>
-      <c r="D4" s="123" t="s">
+      <c r="D4" s="135" t="s">
         <v>34</v>
       </c>
       <c r="E4" s="118" t="s">
@@ -26817,7 +26817,7 @@
       </c>
       <c r="I4" s="118"/>
       <c r="J4" s="118"/>
-      <c r="K4" s="135" t="s">
+      <c r="K4" s="129" t="s">
         <v>223</v>
       </c>
       <c r="L4" s="108" t="s">
@@ -26899,7 +26899,7 @@
       <c r="A5" s="88"/>
       <c r="B5" s="110"/>
       <c r="C5" s="96"/>
-      <c r="D5" s="124"/>
+      <c r="D5" s="136"/>
       <c r="E5" s="6" t="s">
         <v>42</v>
       </c>
@@ -26918,7 +26918,7 @@
       <c r="J5" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="K5" s="136"/>
+      <c r="K5" s="130"/>
       <c r="L5" s="12" t="s">
         <v>46</v>
       </c>
@@ -36397,22 +36397,8 @@
       <c r="AS205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="I1wd1/fJyHDMnQve9p1E1kxYGR4Gnbf+C7db4s8VaSTKRQJ7BIkuGo7+5iTw/LxaS0Dn9kQ5b6IJdAnBB5OS/w==" saltValue="AS8LQhQaLqQG4ZBI2YQ1dA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AN4:AP4"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
     <mergeCell ref="AQ4:AS4"/>
     <mergeCell ref="AH2:AS3"/>
     <mergeCell ref="D4:D5"/>
@@ -36429,6 +36415,20 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="L4:O4"/>
+    <mergeCell ref="U2:AG3"/>
+    <mergeCell ref="AN4:AP4"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 L5 M5 N5 O5 P5 Q5 R5 AH5 AI5 AK5 AL5 AN5 AO5 AQ5 AR5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -36528,7 +36528,7 @@
       <c r="I3" s="118"/>
       <c r="J3" s="118"/>
       <c r="K3" s="118"/>
-      <c r="L3" s="122" t="s">
+      <c r="L3" s="134" t="s">
         <v>159</v>
       </c>
     </row>
@@ -36552,7 +36552,7 @@
         <v>163</v>
       </c>
       <c r="K4" s="108"/>
-      <c r="L4" s="122"/>
+      <c r="L4" s="134"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="139"/>
@@ -39387,7 +39387,7 @@
       <c r="L205" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="I4Takf89+NP8kCf+OJh0Cmrb+3nnr7MrNAQ2Vi5XFOf/misnvLtZKkj3nSkYiWHhXV9/rIBBrn6jgpnuUcuDnw==" saltValue="SN9PZXohv8/YDVgIyzH/HA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="D2:L2"/>
     <mergeCell ref="A2:A5"/>
@@ -39498,16 +39498,16 @@
       </c>
       <c r="D3" s="95"/>
       <c r="E3" s="100"/>
-      <c r="F3" s="129" t="s">
+      <c r="F3" s="123" t="s">
         <v>168</v>
       </c>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="143" t="s">
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="145" t="s">
         <v>196</v>
       </c>
-      <c r="K3" s="142" t="s">
+      <c r="K3" s="144" t="s">
         <v>169</v>
       </c>
       <c r="L3" s="108" t="s">
@@ -39524,30 +39524,30 @@
       <c r="Q3" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="R3" s="122" t="s">
+      <c r="R3" s="134" t="s">
         <v>175</v>
       </c>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
+      <c r="S3" s="134"/>
+      <c r="T3" s="134"/>
+      <c r="U3" s="134"/>
+      <c r="V3" s="134"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="138"/>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="142" t="s">
         <v>134</v>
       </c>
       <c r="D4" s="94" t="s">
         <v>123</v>
       </c>
       <c r="E4" s="100"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="142"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="144"/>
       <c r="L4" s="108"/>
       <c r="M4" s="108"/>
       <c r="N4" s="115"/>
@@ -39569,7 +39569,7 @@
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="139"/>
-      <c r="C5" s="147"/>
+      <c r="C5" s="143"/>
       <c r="D5" s="67" t="s">
         <v>0</v>
       </c>
@@ -39588,8 +39588,8 @@
       <c r="I5" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="J5" s="145"/>
-      <c r="K5" s="142"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="144"/>
       <c r="L5" s="108"/>
       <c r="M5" s="108"/>
       <c r="N5" s="32" t="s">
@@ -44415,13 +44415,8 @@
       <c r="V205" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gmPCmbArCeTQGxfXpiykcH7DYRo+gVaQmApH9OcOCruusA1hbmioATt/e2Uc0T9Fq4y6o8NsDY4y9bjIDMrFKw==" saltValue="944MPcKY7Tgg7RQ4YzvHNQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C3:E3"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="S4:T4"/>
@@ -44434,6 +44429,11 @@
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="P2:P5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U5:V5 F5:I5 K3:K5" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -46129,7 +46129,7 @@
       <c r="F205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="qUd4JhC6utB+AGWDAK4ECXbZkCd/gF8MTa25Y43fdyJI5sqgE5xOt0RnW2th6wJdGBc/RbL8OgmK999JZcXKxA==" saltValue="0QjQOmfY2M326rTq8bwnEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="9">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:A5"/>
@@ -49077,7 +49077,7 @@
       <c r="L205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7I98irOMaen5mYMcyqY+TcD1vkWeTie7uZ4AheMLUWeoSM1n57JXwDst8o/ba+YdtMDlFYafwW5fGtZde6YEAA==" saltValue="8uuMQsSpvdTU2mpdRTp55Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="9">
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:L4"/>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1DEE1F-0CE3-4956-947A-495A3CCF0A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873C1E13-45D4-4A7E-A265-E54B4DB98AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
@@ -1429,7 +1429,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1456,26 +1476,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1490,12 +1490,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -1512,6 +1506,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2210,7 +2210,7 @@
       <c r="D28" s="65"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="N1bniBsjFOWLRxdCAar69hrlEM89c03rP7SFp0KDKKg2PT/Fzi93IUEM0/YTx8R/V9C3aAcUX/3BjRYts8Kapw==" saltValue="/7LjJiM4eMOJa+EPUVtI/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ttuikl6SGMUK0RmKP8ZHj/8oHZ+lV5VHL9m/8ozKHh0FHyC3HzjMJRfhBm321hHclq1Nx6r12KkNIjTl28bJuw==" saltValue="NL2doltTOA5WyZ9sLm8ajw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -7554,10 +7554,10 @@
       <c r="K3" s="162" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="130" t="s">
+      <c r="L3" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="M3" s="130"/>
+      <c r="M3" s="136"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="159"/>
@@ -20217,7 +20217,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="37NOUPegG9zFwNZbEG9rJ1fPQH04ua4vUFfqrfSGHK2Y5NsLHTqzLf9lM9U8w+bFRYXqjEzJgmiyi5bcFeIbUw==" saltValue="hJzB/vyeo8DVz6BnSGvclQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GhlKraMdKV818mROCVRouxwDOIReLAA/hx+ateP6YA0zSgb/GXAZj7CthSY0g07VprNTUKp5s3R0mwZXakUORA==" saltValue="XSY4tIFIO7u8dG3Zztyw6g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="14">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -20246,8 +20246,8 @@
     <hyperlink ref="V5" r:id="rId4" location="reasonsDaysLost" xr:uid="{3955310B-45A1-4FFC-AD47-D85E65B9B8C5}"/>
     <hyperlink ref="W5" r:id="rId5" location="reasonsDaysLost" xr:uid="{F6A2D174-87CA-4A84-A59B-9C5B3EDFA410}"/>
     <hyperlink ref="X5" r:id="rId6" location="reasonsDaysLost" xr:uid="{4AD9F6B4-F493-4D51-A425-E40A5E342DD0}"/>
-    <hyperlink ref="E5" r:id="rId7" xr:uid="{8E8691ED-310C-4B0D-98E7-1C757A32EA68}"/>
-    <hyperlink ref="J5" r:id="rId8" xr:uid="{FDCA5CD8-C8A1-4C49-864F-2B6D02C8EA6C}"/>
+    <hyperlink ref="E5" r:id="rId7" location="Ports" xr:uid="{8E8691ED-310C-4B0D-98E7-1C757A32EA68}"/>
+    <hyperlink ref="J5" r:id="rId8" location="Ports" xr:uid="{FDCA5CD8-C8A1-4C49-864F-2B6D02C8EA6C}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -23813,7 +23813,7 @@
       <c r="O205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1AUsWISJhWm6QtpGotet1zugWWYXk0LTk1oXU2Eoh7GXjBl99fWY7dGeEyfdIGqfr3T+iIGENbiUZDidI+XIaQ==" saltValue="0HwUzD1E8J58Q9wccJliPQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="MxKMvKfRJJ6xW3cNnTEDsxL50i68PJNHvusRHcv4T2Q702w2ctSXPuq5hVPZ1r0m2V0uRNipZ/0tzSLxx36ebg==" saltValue="w3WXlxJTrUFNnwU9bJY+Vw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="16">
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="K3:O3"/>
@@ -23846,6 +23846,7 @@
     <hyperlink ref="H4" r:id="rId6" xr:uid="{C4D05E8A-B26C-4196-BF44-6883318591EB}"/>
     <hyperlink ref="I4:I5" r:id="rId7" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{0B822938-81D2-4E79-AA2B-FF0568175FC7}"/>
     <hyperlink ref="J4:J5" r:id="rId8" location="gearGroups" display="MAIN_FISHING_GEAR_CODE" xr:uid="{CCCFD829-5BF1-44B5-8500-349E2822309E}"/>
+    <hyperlink ref="H4:H5" r:id="rId9" location="Ports" display="PORT_CODE" xr:uid="{44C3BCF2-CCDC-4213-9DFE-452592BB90D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26572,7 +26573,7 @@
       <c r="K205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/tdCV0IIceWEsiDL5UPg5UK+Bm4XMf3IZiNHcQy+OItWgW3ttFyTgSkF2Oxxq4ozOvGqeXgahohLJPyPIo4UbQ==" saltValue="RiNyU9yX5yrqz0ejzihzdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uOlrmBRDFpS46FcDo7VfHuPO8b6tpORxIImLrIT7/0RvntiQUgdh10FGAuDIsY05gBvMIV4jfyfRp0lIyGJe9w==" saltValue="dKqMLkw/q2eGXJUvT/Us2Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B3:F3"/>
@@ -26591,8 +26592,8 @@
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" location="countries" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
     <hyperlink ref="G5" r:id="rId2" location="countries" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
+    <hyperlink ref="C5" r:id="rId3" location="Ports" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
+    <hyperlink ref="H5" r:id="rId4" location="Ports" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26698,113 +26699,113 @@
       <c r="A2" s="88" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="129" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="124"/>
-      <c r="T2" s="125"/>
-      <c r="U2" s="122" t="s">
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="130"/>
+      <c r="Q2" s="130"/>
+      <c r="R2" s="130"/>
+      <c r="S2" s="130"/>
+      <c r="T2" s="131"/>
+      <c r="U2" s="125" t="s">
         <v>70</v>
       </c>
-      <c r="V2" s="131"/>
-      <c r="W2" s="131"/>
-      <c r="X2" s="131"/>
-      <c r="Y2" s="131"/>
-      <c r="Z2" s="131"/>
-      <c r="AA2" s="131"/>
-      <c r="AB2" s="131"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="131"/>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="132"/>
-      <c r="AH2" s="134" t="s">
+      <c r="V2" s="126"/>
+      <c r="W2" s="126"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="126"/>
+      <c r="Z2" s="126"/>
+      <c r="AA2" s="126"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="126"/>
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="126"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" s="134"/>
-      <c r="AJ2" s="134"/>
-      <c r="AK2" s="134"/>
-      <c r="AL2" s="134"/>
-      <c r="AM2" s="134"/>
-      <c r="AN2" s="134"/>
-      <c r="AO2" s="134"/>
-      <c r="AP2" s="134"/>
-      <c r="AQ2" s="134"/>
-      <c r="AR2" s="134"/>
-      <c r="AS2" s="134"/>
+      <c r="AI2" s="122"/>
+      <c r="AJ2" s="122"/>
+      <c r="AK2" s="122"/>
+      <c r="AL2" s="122"/>
+      <c r="AM2" s="122"/>
+      <c r="AN2" s="122"/>
+      <c r="AO2" s="122"/>
+      <c r="AP2" s="122"/>
+      <c r="AQ2" s="122"/>
+      <c r="AR2" s="122"/>
+      <c r="AS2" s="122"/>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="127"/>
-      <c r="T3" s="128"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="133"/>
+      <c r="R3" s="133"/>
+      <c r="S3" s="133"/>
+      <c r="T3" s="134"/>
       <c r="U3" s="96"/>
-      <c r="V3" s="133"/>
-      <c r="W3" s="133"/>
-      <c r="X3" s="133"/>
-      <c r="Y3" s="133"/>
-      <c r="Z3" s="133"/>
-      <c r="AA3" s="133"/>
-      <c r="AB3" s="133"/>
-      <c r="AC3" s="133"/>
-      <c r="AD3" s="133"/>
-      <c r="AE3" s="133"/>
-      <c r="AF3" s="133"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
       <c r="AG3" s="97"/>
-      <c r="AH3" s="134"/>
-      <c r="AI3" s="134"/>
-      <c r="AJ3" s="134"/>
-      <c r="AK3" s="134"/>
-      <c r="AL3" s="134"/>
-      <c r="AM3" s="134"/>
-      <c r="AN3" s="134"/>
-      <c r="AO3" s="134"/>
-      <c r="AP3" s="134"/>
-      <c r="AQ3" s="134"/>
-      <c r="AR3" s="134"/>
-      <c r="AS3" s="134"/>
+      <c r="AH3" s="122"/>
+      <c r="AI3" s="122"/>
+      <c r="AJ3" s="122"/>
+      <c r="AK3" s="122"/>
+      <c r="AL3" s="122"/>
+      <c r="AM3" s="122"/>
+      <c r="AN3" s="122"/>
+      <c r="AO3" s="122"/>
+      <c r="AP3" s="122"/>
+      <c r="AQ3" s="122"/>
+      <c r="AR3" s="122"/>
+      <c r="AS3" s="122"/>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="122" t="s">
+      <c r="C4" s="125" t="s">
         <v>222</v>
       </c>
-      <c r="D4" s="135" t="s">
+      <c r="D4" s="123" t="s">
         <v>34</v>
       </c>
       <c r="E4" s="118" t="s">
@@ -26817,7 +26818,7 @@
       </c>
       <c r="I4" s="118"/>
       <c r="J4" s="118"/>
-      <c r="K4" s="129" t="s">
+      <c r="K4" s="135" t="s">
         <v>223</v>
       </c>
       <c r="L4" s="108" t="s">
@@ -26899,7 +26900,7 @@
       <c r="A5" s="88"/>
       <c r="B5" s="110"/>
       <c r="C5" s="96"/>
-      <c r="D5" s="136"/>
+      <c r="D5" s="124"/>
       <c r="E5" s="6" t="s">
         <v>42</v>
       </c>
@@ -26918,7 +26919,7 @@
       <c r="J5" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="K5" s="130"/>
+      <c r="K5" s="136"/>
       <c r="L5" s="12" t="s">
         <v>46</v>
       </c>
@@ -36399,6 +36400,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="I1wd1/fJyHDMnQve9p1E1kxYGR4Gnbf+C7db4s8VaSTKRQJ7BIkuGo7+5iTw/LxaS0Dn9kQ5b6IJdAnBB5OS/w==" saltValue="AS8LQhQaLqQG4ZBI2YQ1dA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="U2:AG3"/>
+    <mergeCell ref="AN4:AP4"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
     <mergeCell ref="AQ4:AS4"/>
     <mergeCell ref="AH2:AS3"/>
     <mergeCell ref="D4:D5"/>
@@ -36415,20 +36430,6 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="L4:O4"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AN4:AP4"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 L5 M5 N5 O5 P5 Q5 R5 AH5 AI5 AK5 AL5 AN5 AO5 AQ5 AR5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -36528,7 +36529,7 @@
       <c r="I3" s="118"/>
       <c r="J3" s="118"/>
       <c r="K3" s="118"/>
-      <c r="L3" s="134" t="s">
+      <c r="L3" s="122" t="s">
         <v>159</v>
       </c>
     </row>
@@ -36552,7 +36553,7 @@
         <v>163</v>
       </c>
       <c r="K4" s="108"/>
-      <c r="L4" s="134"/>
+      <c r="L4" s="122"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="139"/>
@@ -39498,16 +39499,16 @@
       </c>
       <c r="D3" s="95"/>
       <c r="E3" s="100"/>
-      <c r="F3" s="123" t="s">
+      <c r="F3" s="129" t="s">
         <v>168</v>
       </c>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="145" t="s">
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="143" t="s">
         <v>196</v>
       </c>
-      <c r="K3" s="144" t="s">
+      <c r="K3" s="142" t="s">
         <v>169</v>
       </c>
       <c r="L3" s="108" t="s">
@@ -39524,30 +39525,30 @@
       <c r="Q3" s="104" t="s">
         <v>174</v>
       </c>
-      <c r="R3" s="134" t="s">
+      <c r="R3" s="122" t="s">
         <v>175</v>
       </c>
-      <c r="S3" s="134"/>
-      <c r="T3" s="134"/>
-      <c r="U3" s="134"/>
-      <c r="V3" s="134"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="122"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="122"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="138"/>
-      <c r="C4" s="142" t="s">
+      <c r="C4" s="146" t="s">
         <v>134</v>
       </c>
       <c r="D4" s="94" t="s">
         <v>123</v>
       </c>
       <c r="E4" s="100"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="144"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="142"/>
       <c r="L4" s="108"/>
       <c r="M4" s="108"/>
       <c r="N4" s="115"/>
@@ -39569,7 +39570,7 @@
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="139"/>
-      <c r="C5" s="143"/>
+      <c r="C5" s="147"/>
       <c r="D5" s="67" t="s">
         <v>0</v>
       </c>
@@ -39588,8 +39589,8 @@
       <c r="I5" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="J5" s="147"/>
-      <c r="K5" s="144"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="142"/>
       <c r="L5" s="108"/>
       <c r="M5" s="108"/>
       <c r="N5" s="32" t="s">
@@ -44417,6 +44418,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="gmPCmbArCeTQGxfXpiykcH7DYRo+gVaQmApH9OcOCruusA1hbmioATt/e2Uc0T9Fq4y6o8NsDY4y9bjIDMrFKw==" saltValue="944MPcKY7Tgg7RQ4YzvHNQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="R4:R5"/>
     <mergeCell ref="S4:T4"/>
@@ -44429,11 +44435,6 @@
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="P2:P5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U5:V5 F5:I5 K3:K5" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB3AC46-2A20-4EA3-A312-8E4F46E56224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4161693-458D-4F15-810B-2E26A55B18BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="405" windowWidth="27705" windowHeight="15090" tabRatio="879" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="330" yWindow="390" windowWidth="27705" windowHeight="15090" tabRatio="879" firstSheet="2" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -1073,7 +1073,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1153,6 +1153,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1186,6 +1256,75 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1198,6 +1337,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1206,203 +1352,48 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1410,32 +1401,21 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1774,24 +1754,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="43"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="66"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="69"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="15"/>
@@ -1841,15 +1821,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="21"/>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="70"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="47"/>
+      <c r="G8" s="70"/>
       <c r="H8" s="23"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2031,11 +2011,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="21"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="50"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="73"/>
       <c r="H26" s="23"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2133,110 +2113,110 @@
       <c r="W1" s="7"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="119" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="123" t="s">
+      <c r="C2" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="123" t="s">
+      <c r="D2" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="102" t="s">
         <v>194</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="97" t="s">
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="104" t="s">
         <v>204</v>
       </c>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97" t="s">
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="97"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="108" t="s">
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="72" t="s">
+      <c r="R2" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="S2" s="74"/>
-      <c r="T2" s="86" t="s">
+      <c r="S2" s="86"/>
+      <c r="T2" s="101" t="s">
         <v>202</v>
       </c>
-      <c r="U2" s="86"/>
-      <c r="V2" s="86" t="s">
+      <c r="U2" s="101"/>
+      <c r="V2" s="101" t="s">
         <v>201</v>
       </c>
-      <c r="W2" s="86"/>
+      <c r="W2" s="101"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="124"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="77" t="s">
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="76" t="s">
+      <c r="K3" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="71" t="s">
+      <c r="L3" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="M3" s="76" t="s">
+      <c r="M3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="O3" s="76" t="s">
+      <c r="O3" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="125" t="s">
+      <c r="P3" s="62" t="s">
         <v>198</v>
       </c>
-      <c r="Q3" s="109"/>
-      <c r="R3" s="126" t="s">
+      <c r="Q3" s="106"/>
+      <c r="R3" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="S3" s="126" t="s">
+      <c r="S3" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="T3" s="127" t="s">
+      <c r="T3" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="76" t="s">
+      <c r="U3" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="V3" s="71" t="s">
+      <c r="V3" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="W3" s="71" t="s">
+      <c r="W3" s="40" t="s">
         <v>200</v>
       </c>
     </row>
@@ -7319,60 +7299,60 @@
       <c r="M1" s="14"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="119" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="123" t="s">
+      <c r="C2" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="123" t="s">
+      <c r="D2" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="105" t="s">
         <v>206</v>
       </c>
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="105" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="108" t="s">
+      <c r="G2" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="H2" s="128" t="s">
+      <c r="H2" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="129" t="s">
+      <c r="I2" s="122" t="s">
         <v>209</v>
       </c>
-      <c r="J2" s="128" t="s">
+      <c r="J2" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="128" t="s">
+      <c r="K2" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="90" t="s">
+      <c r="L2" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="90"/>
+      <c r="M2" s="96"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="124"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="71" t="s">
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="M3" s="71" t="s">
+      <c r="M3" s="40" t="s">
         <v>200</v>
       </c>
     </row>
@@ -10379,11 +10359,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="12">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="E2:E3"/>
@@ -10391,6 +10366,11 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H2:H3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 G2:G3 I2:I3 E2:E3 L3 M3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -10399,7 +10379,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="G2:G3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{4D21FAB4-D1ED-49FA-A8E9-1A452DA8E255}"/>
-    <hyperlink ref="I2:I3" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{4AAC5290-0C1E-413E-9063-304F215E9866}"/>
+    <hyperlink ref="I2:I3" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD" xr:uid="{4AAC5290-0C1E-413E-9063-304F215E9866}"/>
     <hyperlink ref="E2" r:id="rId3" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{26B5C55C-6931-4D84-B6B4-4AA585019D2E}"/>
     <hyperlink ref="F2" r:id="rId4" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{312D6457-0D67-4610-B478-F5AE649B98F6}"/>
     <hyperlink ref="L3" r:id="rId5" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{11FAA504-1FFB-4306-A7A1-4F548FAD3A87}"/>
@@ -10443,37 +10423,37 @@
       <c r="K1" s="9"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="123" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="122" t="s">
+      <c r="C2" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="122" t="s">
+      <c r="D2" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="101" t="s">
+      <c r="E2" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="101" t="s">
+      <c r="F2" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="G2" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="101" t="s">
+      <c r="H2" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="101" t="s">
+      <c r="J2" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="K2" s="101" t="s">
+      <c r="K2" s="53" t="s">
         <v>211</v>
       </c>
     </row>
@@ -13118,22 +13098,22 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="99" t="s">
+      <c r="D2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="F2" s="99" t="s">
+      <c r="F2" s="54" t="s">
         <v>100</v>
       </c>
     </row>
@@ -14811,180 +14791,180 @@
       <c r="X1" s="8"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58" t="s">
+      <c r="C2" s="74"/>
+      <c r="D2" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58" t="s">
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="74"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="59" t="s">
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="58"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="74"/>
+      <c r="U3" s="74"/>
+      <c r="V3" s="74"/>
+      <c r="W3" s="74"/>
+      <c r="X3" s="74"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="62" t="s">
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="75" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62" t="s">
+      <c r="E4" s="76"/>
+      <c r="F4" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="63"/>
-      <c r="H4" s="66" t="s">
+      <c r="G4" s="76"/>
+      <c r="H4" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="79" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="65"/>
-      <c r="K4" s="62" t="s">
+      <c r="J4" s="80"/>
+      <c r="K4" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="63"/>
-      <c r="M4" s="66" t="s">
+      <c r="L4" s="76"/>
+      <c r="M4" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="58" t="s">
+      <c r="N4" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58" t="s">
+      <c r="O4" s="74"/>
+      <c r="P4" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="72" t="s">
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
+      <c r="U4" s="84" t="s">
         <v>130</v>
       </c>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73"/>
-      <c r="X4" s="74"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="86"/>
     </row>
     <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
-      <c r="B5" s="67" t="s">
+      <c r="A5" s="74"/>
+      <c r="B5" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="130" t="s">
+      <c r="E5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="67" t="s">
+      <c r="F5" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="69"/>
-      <c r="I5" s="71" t="s">
+      <c r="H5" s="82"/>
+      <c r="I5" s="40" t="s">
         <v>126</v>
       </c>
       <c r="J5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="68" t="s">
+      <c r="K5" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="68" t="s">
+      <c r="L5" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="69"/>
-      <c r="N5" s="67" t="s">
+      <c r="M5" s="82"/>
+      <c r="N5" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="67" t="s">
+      <c r="O5" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="P5" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="Q5" s="67" t="s">
+      <c r="Q5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="76" t="s">
+      <c r="R5" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="76" t="s">
+      <c r="S5" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="67" t="s">
+      <c r="T5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="U5" s="71" t="s">
+      <c r="U5" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="V5" s="71" t="s">
+      <c r="V5" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="W5" s="71" t="s">
+      <c r="W5" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="X5" s="71" t="s">
+      <c r="X5" s="40" t="s">
         <v>134</v>
       </c>
     </row>
@@ -20248,99 +20228,99 @@
       <c r="O1" s="8"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82" t="s">
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="83"/>
-      <c r="I2" s="84" t="s">
+      <c r="H2" s="89"/>
+      <c r="I2" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="J2" s="75" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="81"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="92"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="58" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="100" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="86" t="s">
+      <c r="F3" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="87" t="s">
+      <c r="G3" s="97" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="J3" s="54" t="s">
+      <c r="J3" s="102" t="s">
         <v>137</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57" t="s">
+      <c r="L3" s="93"/>
+      <c r="M3" s="93" t="s">
         <v>140</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="89" t="s">
+      <c r="N3" s="93"/>
+      <c r="O3" s="94" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="69"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="67" t="s">
+      <c r="A4" s="82"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="M4" s="67" t="s">
+      <c r="M4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="N4" s="77" t="s">
+      <c r="N4" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="O4" s="89"/>
+      <c r="O4" s="94"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -23819,73 +23799,73 @@
       <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="104" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97" t="s">
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104" t="s">
         <v>143</v>
       </c>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="72" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="85" t="s">
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="85" t="s">
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="95" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="69"/>
-      <c r="B4" s="71" t="s">
+      <c r="A4" s="82"/>
+      <c r="B4" s="40" t="s">
         <v>126</v>
       </c>
       <c r="C4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="90"/>
-      <c r="G4" s="71" t="s">
+      <c r="F4" s="96"/>
+      <c r="G4" s="40" t="s">
         <v>126</v>
       </c>
       <c r="H4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="76" t="s">
+      <c r="I4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="J4" s="76" t="s">
+      <c r="J4" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="90"/>
+      <c r="K4" s="96"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -26490,13 +26470,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="7">
+    <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="G3:J3"/>
-    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4 B4 C4 H4" xr:uid="{E97A6FE4-6BFF-4959-9F92-FB6DF23A11A6}">
@@ -26602,237 +26582,237 @@
       <c r="AO1" s="7"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="84" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="72" t="s">
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="86"/>
+      <c r="U2" s="84" t="s">
         <v>170</v>
       </c>
-      <c r="V2" s="73"/>
-      <c r="W2" s="73"/>
-      <c r="X2" s="73"/>
-      <c r="Y2" s="73"/>
-      <c r="Z2" s="73"/>
-      <c r="AA2" s="73"/>
-      <c r="AB2" s="73"/>
-      <c r="AC2" s="73"/>
-      <c r="AD2" s="73"/>
-      <c r="AE2" s="73"/>
-      <c r="AF2" s="73"/>
-      <c r="AG2" s="74"/>
-      <c r="AH2" s="72" t="s">
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="85"/>
+      <c r="AB2" s="85"/>
+      <c r="AC2" s="85"/>
+      <c r="AD2" s="85"/>
+      <c r="AE2" s="85"/>
+      <c r="AF2" s="85"/>
+      <c r="AG2" s="86"/>
+      <c r="AH2" s="84" t="s">
         <v>157</v>
       </c>
-      <c r="AI2" s="73"/>
-      <c r="AJ2" s="73"/>
-      <c r="AK2" s="73"/>
-      <c r="AL2" s="73"/>
-      <c r="AM2" s="73"/>
-      <c r="AN2" s="73"/>
-      <c r="AO2" s="74"/>
+      <c r="AI2" s="85"/>
+      <c r="AJ2" s="85"/>
+      <c r="AK2" s="85"/>
+      <c r="AL2" s="85"/>
+      <c r="AM2" s="85"/>
+      <c r="AN2" s="85"/>
+      <c r="AO2" s="86"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="85" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="95" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="108" t="s">
+      <c r="D3" s="105" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="97" t="s">
+      <c r="E3" s="104" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97" t="s">
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="100" t="s">
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="108" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="86" t="s">
+      <c r="L3" s="101" t="s">
         <v>151</v>
       </c>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="97" t="s">
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="104" t="s">
         <v>152</v>
       </c>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="86" t="s">
+      <c r="Q3" s="104"/>
+      <c r="R3" s="104"/>
+      <c r="S3" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="86"/>
-      <c r="U3" s="97" t="s">
+      <c r="T3" s="101"/>
+      <c r="U3" s="104" t="s">
         <v>156</v>
       </c>
-      <c r="V3" s="97" t="s">
+      <c r="V3" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="W3" s="97" t="s">
+      <c r="W3" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="X3" s="97" t="s">
+      <c r="X3" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" s="97" t="s">
+      <c r="Y3" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="Z3" s="97" t="s">
+      <c r="Z3" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="AA3" s="97" t="s">
+      <c r="AA3" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="AB3" s="97" t="s">
+      <c r="AB3" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="AC3" s="97" t="s">
+      <c r="AC3" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="AD3" s="97" t="s">
+      <c r="AD3" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="AE3" s="97" t="s">
+      <c r="AE3" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="AF3" s="97" t="s">
+      <c r="AF3" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="AG3" s="97" t="s">
+      <c r="AG3" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="AH3" s="86" t="s">
+      <c r="AH3" s="101" t="s">
         <v>166</v>
       </c>
-      <c r="AI3" s="86"/>
-      <c r="AJ3" s="86" t="s">
+      <c r="AI3" s="101"/>
+      <c r="AJ3" s="101" t="s">
         <v>167</v>
       </c>
-      <c r="AK3" s="86"/>
-      <c r="AL3" s="86" t="s">
+      <c r="AK3" s="101"/>
+      <c r="AL3" s="101" t="s">
         <v>168</v>
       </c>
-      <c r="AM3" s="86"/>
-      <c r="AN3" s="86" t="s">
+      <c r="AM3" s="101"/>
+      <c r="AN3" s="101" t="s">
         <v>169</v>
       </c>
-      <c r="AO3" s="86"/>
+      <c r="AO3" s="101"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="69"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="98" t="s">
+      <c r="A4" s="82"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="98" t="s">
+      <c r="F4" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="107" t="s">
+      <c r="G4" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="98" t="s">
+      <c r="H4" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="98" t="s">
+      <c r="I4" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="107" t="s">
+      <c r="J4" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="102"/>
-      <c r="L4" s="71" t="s">
+      <c r="K4" s="109"/>
+      <c r="L4" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="M4" s="71" t="s">
+      <c r="M4" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="N4" s="71" t="s">
+      <c r="N4" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="O4" s="71" t="s">
+      <c r="O4" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="P4" s="70" t="s">
+      <c r="P4" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="Q4" s="70" t="s">
+      <c r="Q4" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="R4" s="70" t="s">
+      <c r="R4" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="S4" s="78" t="s">
+      <c r="S4" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="U4" s="97"/>
-      <c r="V4" s="97"/>
-      <c r="W4" s="97"/>
-      <c r="X4" s="97"/>
-      <c r="Y4" s="97"/>
-      <c r="Z4" s="97"/>
-      <c r="AA4" s="97"/>
-      <c r="AB4" s="97"/>
-      <c r="AC4" s="97"/>
-      <c r="AD4" s="97"/>
-      <c r="AE4" s="97"/>
-      <c r="AF4" s="97"/>
-      <c r="AG4" s="97"/>
-      <c r="AH4" s="112" t="s">
+      <c r="U4" s="104"/>
+      <c r="V4" s="104"/>
+      <c r="W4" s="104"/>
+      <c r="X4" s="104"/>
+      <c r="Y4" s="104"/>
+      <c r="Z4" s="104"/>
+      <c r="AA4" s="104"/>
+      <c r="AB4" s="104"/>
+      <c r="AC4" s="104"/>
+      <c r="AD4" s="104"/>
+      <c r="AE4" s="104"/>
+      <c r="AF4" s="104"/>
+      <c r="AG4" s="104"/>
+      <c r="AH4" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="AI4" s="70" t="s">
+      <c r="AI4" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="AJ4" s="70" t="s">
+      <c r="AJ4" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="AK4" s="70" t="s">
+      <c r="AK4" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="AL4" s="70" t="s">
+      <c r="AL4" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="AM4" s="70" t="s">
+      <c r="AM4" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="AN4" s="70" t="s">
+      <c r="AN4" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="AO4" s="70" t="s">
+      <c r="AO4" s="44" t="s">
         <v>165</v>
       </c>
     </row>
@@ -35439,6 +35419,20 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="U2:AG2"/>
+    <mergeCell ref="AH2:AO2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
     <mergeCell ref="AN3:AO3"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="W3:W4"/>
@@ -35455,20 +35449,6 @@
     <mergeCell ref="AG3:AG4"/>
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="B2:T2"/>
-    <mergeCell ref="U2:AG2"/>
-    <mergeCell ref="AH2:AO2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN4 D3:D4 L4 M4 N4 O4 P4 Q4 R4 AH4 AI4 AJ4 AK4 AL4 AM4 AO4" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35529,100 +35509,100 @@
       <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="84" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="72" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="84" t="s">
         <v>173</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="74"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="86"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="86" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86" t="s">
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101" t="s">
         <v>174</v>
       </c>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86" t="s">
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="101" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="93"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86" t="s">
+      <c r="A4" s="87"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86" t="s">
+      <c r="E4" s="101"/>
+      <c r="F4" s="101" t="s">
         <v>178</v>
       </c>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86" t="s">
+      <c r="G4" s="101"/>
+      <c r="H4" s="101" t="s">
         <v>177</v>
       </c>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86" t="s">
+      <c r="I4" s="101"/>
+      <c r="J4" s="101" t="s">
         <v>176</v>
       </c>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="69"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="76" t="s">
+      <c r="A5" s="82"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="110" t="s">
+      <c r="G5" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="110" t="s">
+      <c r="I5" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="76" t="s">
+      <c r="J5" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="110" t="s">
+      <c r="K5" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="L5" s="76" t="s">
+      <c r="L5" s="45" t="s">
         <v>80</v>
       </c>
     </row>
@@ -38499,132 +38479,132 @@
       <c r="V1" s="7"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="77" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="60"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="103" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="88" t="s">
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="K2" s="116" t="s">
+      <c r="K2" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="L2" s="86" t="s">
+      <c r="L2" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="89" t="s">
+      <c r="M2" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="N2" s="86" t="s">
+      <c r="N2" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="O2" s="72"/>
-      <c r="P2" s="66" t="s">
+      <c r="O2" s="84"/>
+      <c r="P2" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="Q2" s="74" t="s">
+      <c r="Q2" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="R2" s="105" t="s">
+      <c r="R2" s="110" t="s">
         <v>187</v>
       </c>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105"/>
-      <c r="V2" s="105"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="117" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="61"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="89" t="s">
+      <c r="E3" s="83"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="S3" s="86" t="s">
+      <c r="S3" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86" t="s">
+      <c r="T3" s="101"/>
+      <c r="U3" s="101" t="s">
         <v>189</v>
       </c>
-      <c r="V3" s="86"/>
+      <c r="V3" s="101"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="69"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="67" t="s">
+      <c r="A4" s="82"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="G4" s="71" t="s">
+      <c r="G4" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="H4" s="71" t="s">
+      <c r="H4" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="118" t="s">
+      <c r="I4" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="J4" s="91"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="113" t="s">
+      <c r="J4" s="103"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="O4" s="114" t="s">
+      <c r="O4" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="101" t="s">
+      <c r="P4" s="82"/>
+      <c r="Q4" s="86"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="T4" s="101" t="s">
+      <c r="T4" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="U4" s="70" t="s">
+      <c r="U4" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="V4" s="70" t="s">
+      <c r="V4" s="44" t="s">
         <v>191</v>
       </c>
     </row>
@@ -43432,6 +43412,11 @@
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:T3"/>
@@ -43444,11 +43429,6 @@
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="P2:P4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 I4 F4 G4 H4 U4 V4" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -43486,32 +43466,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="42" t="s">
         <v>95</v>
       </c>
     </row>
@@ -45170,58 +45150,58 @@
       <c r="L1" s="8"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="88" t="s">
+      <c r="D2" s="102" t="s">
         <v>192</v>
       </c>
-      <c r="E2" s="120" t="s">
+      <c r="E2" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="121"/>
-      <c r="G2" s="88" t="s">
+      <c r="F2" s="118"/>
+      <c r="G2" s="102" t="s">
         <v>194</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="61"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="69"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="94" t="s">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="94" t="s">
+      <c r="F3" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="91"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="94" t="s">
+      <c r="G3" s="103"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="J3" s="92" t="s">
+      <c r="J3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="119" t="s">
+      <c r="K3" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="94" t="s">
+      <c r="L3" s="52" t="s">
         <v>196</v>
       </c>
     </row>
@@ -48047,8 +48027,10 @@
     <hyperlink ref="L3" r:id="rId2" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{EB80831C-DDCE-4E4D-A605-160D23E19E90}"/>
     <hyperlink ref="E3" r:id="rId3" location="typesOfFate" xr:uid="{F8152E0B-B9D5-4E81-A374-4985E0AF2D58}"/>
     <hyperlink ref="F3" r:id="rId4" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
+    <hyperlink ref="D2:D3" r:id="rId5" location="allSpecies" display="SPECIES" xr:uid="{6CBAC676-A508-4773-8413-1235C4C5E5A3}"/>
+    <hyperlink ref="G2:G3" r:id="rId6" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD" xr:uid="{ED59D94C-1F64-49E4-9EEE-43CC4D45D7D9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4161693-458D-4F15-810B-2E26A55B18BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B3E72E-1566-43C2-8877-CBC356D750BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="390" windowWidth="27705" windowHeight="15090" tabRatio="879" firstSheet="2" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28920" yWindow="450" windowWidth="27705" windowHeight="15090" tabRatio="879" firstSheet="2" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="210">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -167,9 +167,6 @@
     <t>SEX</t>
   </si>
   <si>
-    <t>DEPREDATION_DETAILS</t>
-  </si>
-  <si>
     <t>PRESERVATION_METHOD</t>
   </si>
   <si>
@@ -239,15 +236,6 @@
     <t>MATURITY</t>
   </si>
   <si>
-    <t>KW | HP | BHP</t>
-  </si>
-  <si>
-    <t>KG | T</t>
-  </si>
-  <si>
-    <t>DAYS | NM</t>
-  </si>
-  <si>
     <t>CODE</t>
   </si>
   <si>
@@ -258,9 +246,6 @@
   </si>
   <si>
     <t>OBSERVED_TRIP_ID</t>
-  </si>
-  <si>
-    <t>GEAR</t>
   </si>
   <si>
     <t>SET_ID</t>
@@ -282,12 +267,6 @@
   </si>
   <si>
     <t>NET</t>
-  </si>
-  <si>
-    <t>M | KM</t>
-  </si>
-  <si>
-    <t>MM | CM | M</t>
   </si>
   <si>
     <t>VALUE_MT</t>
@@ -326,13 +305,7 @@
     <t>ON_RETRIEVAL</t>
   </si>
   <si>
-    <t>Purse seine fishing events &gt; Setting operations &gt; Cetaceans and whale sharks sightings during setting</t>
-  </si>
-  <si>
     <t>SIGHTING_BEFORE_SETTING</t>
-  </si>
-  <si>
-    <t>NUM_SIGHTED</t>
   </si>
   <si>
     <t>CAUGHT_INSIDE_NET</t>
@@ -401,15 +374,6 @@
     <t>PERSONNEL</t>
   </si>
   <si>
-    <t>TONNAGE (GT)</t>
-  </si>
-  <si>
-    <t>LENGTH_OVERALL (M)</t>
-  </si>
-  <si>
-    <t>FISH_STORAGE_CAPACITY (M3)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> IOTC ROS data reporting form - Purse seine</t>
   </si>
   <si>
@@ -455,16 +419,7 @@
     <t>REASON_4</t>
   </si>
   <si>
-    <t>FLAG_OR_CHARTERING</t>
-  </si>
-  <si>
-    <t>SPECIES_1</t>
-  </si>
-  <si>
     <t>MAIN_FISHING_GEAR</t>
-  </si>
-  <si>
-    <t>LICENSED TARGET SPECIES</t>
   </si>
   <si>
     <t>FISHING MASTER</t>
@@ -690,6 +645,39 @@
   </si>
   <si>
     <t>Purse seine &gt; Daily activities</t>
+  </si>
+  <si>
+    <t>FLAG_OR_CHARTERING_STATE</t>
+  </si>
+  <si>
+    <t>REGISTRATION_NUMBER</t>
+  </si>
+  <si>
+    <t>LICENSED_TARGET_SPECIES</t>
+  </si>
+  <si>
+    <t>GROSS_TONNAGE</t>
+  </si>
+  <si>
+    <t>LOA_M</t>
+  </si>
+  <si>
+    <t>POWER_UNIT</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>FISH_STORAGE_CAPACITY_M3</t>
+  </si>
+  <si>
+    <t>Purse seine fishing events &gt; Setting operations &gt; Cetacean and whale shark sightings during setting</t>
+  </si>
+  <si>
+    <t>NUMBER_SIGHTED</t>
+  </si>
+  <si>
+    <t>DESTINATION</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1061,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1154,9 +1142,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1174,12 +1159,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1193,15 +1172,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1222,6 +1194,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1355,14 +1330,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1372,8 +1339,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1388,9 +1363,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1407,14 +1379,25 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1754,39 +1737,39 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="64" t="s">
-        <v>120</v>
+      <c r="B2" s="59" t="s">
+        <v>108</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="66"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="64"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="16" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H4" s="20"/>
     </row>
@@ -1802,7 +1785,7 @@
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="21"/>
       <c r="C6" s="24" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
@@ -1821,26 +1804,26 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="21"/>
-      <c r="C8" s="70" t="s">
-        <v>105</v>
+      <c r="C8" s="65" t="s">
+        <v>96</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="65"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="70" t="s">
-        <v>106</v>
+      <c r="F8" s="65" t="s">
+        <v>97</v>
       </c>
-      <c r="G8" s="70"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="23"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="21"/>
       <c r="C9" s="25" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="22"/>
       <c r="F9" s="25" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G9" s="26"/>
       <c r="H9" s="23"/>
@@ -1848,12 +1831,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="21"/>
       <c r="C10" s="27" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="23"/>
@@ -1870,7 +1853,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="21"/>
       <c r="C12" s="27" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="22"/>
@@ -1881,7 +1864,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="21"/>
       <c r="C13" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="22"/>
@@ -1910,7 +1893,7 @@
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="21"/>
       <c r="C16" s="24" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
@@ -1930,7 +1913,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="21"/>
       <c r="C18" s="27" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="22"/>
@@ -1941,7 +1924,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="21"/>
       <c r="C19" s="32" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="22"/>
@@ -1952,7 +1935,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="21"/>
       <c r="C20" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="31"/>
       <c r="E20" s="22"/>
@@ -1963,7 +1946,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="21"/>
       <c r="C21" s="27" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="22"/>
@@ -1992,7 +1975,7 @@
     <row r="24" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B24" s="21"/>
       <c r="C24" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D24" s="28"/>
       <c r="E24" s="22"/>
@@ -2011,11 +1994,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="21"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="73"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="68"/>
       <c r="H26" s="23"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2058,7 +2041,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:W203"/>
+  <dimension ref="A1:X203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -2082,12 +2065,13 @@
     <col min="19" max="19" width="16.7109375" style="3" customWidth="1"/>
     <col min="20" max="20" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="30.7109375" customWidth="1"/>
+    <col min="22" max="22" width="23.5703125" style="3" customWidth="1"/>
+    <col min="23" max="24" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -2111,116 +2095,121 @@
       <c r="U1" s="7"/>
       <c r="V1" s="7"/>
       <c r="W1" s="7"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>69</v>
+      <c r="X1" s="7"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="113" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>71</v>
+      <c r="B2" s="113" t="s">
+        <v>66</v>
       </c>
-      <c r="C2" s="119" t="s">
-        <v>72</v>
+      <c r="C2" s="113" t="s">
+        <v>67</v>
       </c>
-      <c r="D2" s="119" t="s">
-        <v>73</v>
+      <c r="D2" s="113" t="s">
+        <v>68</v>
       </c>
-      <c r="E2" s="102" t="s">
-        <v>194</v>
+      <c r="E2" s="97" t="s">
+        <v>179</v>
       </c>
-      <c r="F2" s="93" t="s">
-        <v>203</v>
+      <c r="F2" s="88" t="s">
+        <v>188</v>
       </c>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="104" t="s">
-        <v>204</v>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="99" t="s">
+        <v>189</v>
       </c>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="104" t="s">
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="104"/>
-      <c r="P2" s="104"/>
-      <c r="Q2" s="105" t="s">
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="84" t="s">
-        <v>62</v>
+      <c r="R2" s="79" t="s">
+        <v>61</v>
       </c>
-      <c r="S2" s="86"/>
-      <c r="T2" s="101" t="s">
-        <v>202</v>
+      <c r="S2" s="81"/>
+      <c r="T2" s="79" t="s">
+        <v>187</v>
       </c>
-      <c r="U2" s="101"/>
-      <c r="V2" s="101" t="s">
-        <v>201</v>
+      <c r="U2" s="80"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="96" t="s">
+        <v>186</v>
       </c>
-      <c r="W2" s="101"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="46" t="s">
+      <c r="X2" s="96"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="114"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="46" t="s">
-        <v>197</v>
+      <c r="H3" s="45" t="s">
+        <v>182</v>
       </c>
-      <c r="I3" s="42" t="s">
-        <v>48</v>
+      <c r="I3" s="41" t="s">
+        <v>47</v>
       </c>
       <c r="J3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="44" t="s">
         <v>37</v>
       </c>
       <c r="L3" s="40" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
-      <c r="M3" s="45" t="s">
-        <v>48</v>
+      <c r="M3" s="44" t="s">
+        <v>47</v>
       </c>
       <c r="N3" s="40" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
-      <c r="O3" s="45" t="s">
+      <c r="O3" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="62" t="s">
-        <v>198</v>
+      <c r="P3" s="56" t="s">
+        <v>183</v>
       </c>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="50" t="s">
+      <c r="Q3" s="104"/>
+      <c r="R3" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="S3" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="S3" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="T3" s="63" t="s">
+      <c r="T3" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="45" t="s">
-        <v>40</v>
+      <c r="U3" s="44" t="s">
+        <v>39</v>
       </c>
-      <c r="V3" s="40" t="s">
-        <v>199</v>
+      <c r="V3" s="44" t="s">
+        <v>209</v>
       </c>
       <c r="W3" s="40" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" s="40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2242,10 +2231,11 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4" s="12"/>
+      <c r="V4" s="2"/>
       <c r="W4" s="12"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4" s="12"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2267,10 +2257,11 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5" s="12"/>
+      <c r="V5" s="2"/>
       <c r="W5" s="12"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" s="12"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2292,10 +2283,11 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
-      <c r="V6" s="12"/>
+      <c r="V6" s="2"/>
       <c r="W6" s="12"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X6" s="12"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2317,10 +2309,11 @@
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
-      <c r="V7" s="12"/>
+      <c r="V7" s="2"/>
       <c r="W7" s="12"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X7" s="12"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2342,10 +2335,11 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="12"/>
+      <c r="V8" s="2"/>
       <c r="W8" s="12"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X8" s="12"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2367,10 +2361,11 @@
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
-      <c r="V9" s="12"/>
+      <c r="V9" s="2"/>
       <c r="W9" s="12"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X9" s="12"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2392,10 +2387,11 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
-      <c r="V10" s="12"/>
+      <c r="V10" s="2"/>
       <c r="W10" s="12"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X10" s="12"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2417,10 +2413,11 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
-      <c r="V11" s="12"/>
+      <c r="V11" s="2"/>
       <c r="W11" s="12"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X11" s="12"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2442,10 +2439,11 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
-      <c r="V12" s="12"/>
+      <c r="V12" s="2"/>
       <c r="W12" s="12"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X12" s="12"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2467,10 +2465,11 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
-      <c r="V13" s="12"/>
+      <c r="V13" s="2"/>
       <c r="W13" s="12"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X13" s="12"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2492,10 +2491,11 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
-      <c r="V14" s="12"/>
+      <c r="V14" s="2"/>
       <c r="W14" s="12"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X14" s="12"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2517,10 +2517,11 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="12"/>
+      <c r="V15" s="2"/>
       <c r="W15" s="12"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X15" s="12"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2542,10 +2543,11 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
-      <c r="V16" s="12"/>
+      <c r="V16" s="2"/>
       <c r="W16" s="12"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X16" s="12"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2567,10 +2569,11 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
-      <c r="V17" s="12"/>
+      <c r="V17" s="2"/>
       <c r="W17" s="12"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X17" s="12"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2592,10 +2595,11 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
-      <c r="V18" s="12"/>
+      <c r="V18" s="2"/>
       <c r="W18" s="12"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X18" s="12"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2617,10 +2621,11 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
-      <c r="V19" s="12"/>
+      <c r="V19" s="2"/>
       <c r="W19" s="12"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X19" s="12"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2642,10 +2647,11 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
-      <c r="V20" s="12"/>
+      <c r="V20" s="2"/>
       <c r="W20" s="12"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X20" s="12"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2667,10 +2673,11 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
-      <c r="V21" s="12"/>
+      <c r="V21" s="2"/>
       <c r="W21" s="12"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X21" s="12"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2692,10 +2699,11 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
-      <c r="V22" s="12"/>
+      <c r="V22" s="2"/>
       <c r="W22" s="12"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X22" s="12"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2717,10 +2725,11 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
-      <c r="V23" s="12"/>
+      <c r="V23" s="2"/>
       <c r="W23" s="12"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X23" s="12"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2742,10 +2751,11 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-      <c r="V24" s="12"/>
+      <c r="V24" s="2"/>
       <c r="W24" s="12"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X24" s="12"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2767,10 +2777,11 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
-      <c r="V25" s="12"/>
+      <c r="V25" s="2"/>
       <c r="W25" s="12"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X25" s="12"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2792,10 +2803,11 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
-      <c r="V26" s="12"/>
+      <c r="V26" s="2"/>
       <c r="W26" s="12"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X26" s="12"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2817,10 +2829,11 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
-      <c r="V27" s="12"/>
+      <c r="V27" s="2"/>
       <c r="W27" s="12"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X27" s="12"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2842,10 +2855,11 @@
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
-      <c r="V28" s="12"/>
+      <c r="V28" s="2"/>
       <c r="W28" s="12"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X28" s="12"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2867,10 +2881,11 @@
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
-      <c r="V29" s="12"/>
+      <c r="V29" s="2"/>
       <c r="W29" s="12"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X29" s="12"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2892,10 +2907,11 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
-      <c r="V30" s="12"/>
+      <c r="V30" s="2"/>
       <c r="W30" s="12"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X30" s="12"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2917,10 +2933,11 @@
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
-      <c r="V31" s="12"/>
+      <c r="V31" s="2"/>
       <c r="W31" s="12"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X31" s="12"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2942,10 +2959,11 @@
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
-      <c r="V32" s="12"/>
+      <c r="V32" s="2"/>
       <c r="W32" s="12"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" s="12"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2967,10 +2985,11 @@
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
-      <c r="V33" s="12"/>
+      <c r="V33" s="2"/>
       <c r="W33" s="12"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" s="12"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2992,10 +3011,11 @@
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
-      <c r="V34" s="12"/>
+      <c r="V34" s="2"/>
       <c r="W34" s="12"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X34" s="12"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3017,10 +3037,11 @@
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
-      <c r="V35" s="12"/>
+      <c r="V35" s="2"/>
       <c r="W35" s="12"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X35" s="12"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3042,10 +3063,11 @@
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
-      <c r="V36" s="12"/>
+      <c r="V36" s="2"/>
       <c r="W36" s="12"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X36" s="12"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3067,10 +3089,11 @@
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
-      <c r="V37" s="12"/>
+      <c r="V37" s="2"/>
       <c r="W37" s="12"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" s="12"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3092,10 +3115,11 @@
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
-      <c r="V38" s="12"/>
+      <c r="V38" s="2"/>
       <c r="W38" s="12"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X38" s="12"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3117,10 +3141,11 @@
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
-      <c r="V39" s="12"/>
+      <c r="V39" s="2"/>
       <c r="W39" s="12"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X39" s="12"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3142,10 +3167,11 @@
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
-      <c r="V40" s="12"/>
+      <c r="V40" s="2"/>
       <c r="W40" s="12"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X40" s="12"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3167,10 +3193,11 @@
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
-      <c r="V41" s="12"/>
+      <c r="V41" s="2"/>
       <c r="W41" s="12"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X41" s="12"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3192,10 +3219,11 @@
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
-      <c r="V42" s="12"/>
+      <c r="V42" s="2"/>
       <c r="W42" s="12"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X42" s="12"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3217,10 +3245,11 @@
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
-      <c r="V43" s="12"/>
+      <c r="V43" s="2"/>
       <c r="W43" s="12"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X43" s="12"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3242,10 +3271,11 @@
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
-      <c r="V44" s="12"/>
+      <c r="V44" s="2"/>
       <c r="W44" s="12"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X44" s="12"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3267,10 +3297,11 @@
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
-      <c r="V45" s="12"/>
+      <c r="V45" s="2"/>
       <c r="W45" s="12"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X45" s="12"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3292,10 +3323,11 @@
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
-      <c r="V46" s="12"/>
+      <c r="V46" s="2"/>
       <c r="W46" s="12"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X46" s="12"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3317,10 +3349,11 @@
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
-      <c r="V47" s="12"/>
+      <c r="V47" s="2"/>
       <c r="W47" s="12"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X47" s="12"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3342,10 +3375,11 @@
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
-      <c r="V48" s="12"/>
+      <c r="V48" s="2"/>
       <c r="W48" s="12"/>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X48" s="12"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3367,10 +3401,11 @@
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
-      <c r="V49" s="12"/>
+      <c r="V49" s="2"/>
       <c r="W49" s="12"/>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X49" s="12"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3392,10 +3427,11 @@
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
-      <c r="V50" s="12"/>
+      <c r="V50" s="2"/>
       <c r="W50" s="12"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X50" s="12"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3417,10 +3453,11 @@
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
-      <c r="V51" s="12"/>
+      <c r="V51" s="2"/>
       <c r="W51" s="12"/>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X51" s="12"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3442,10 +3479,11 @@
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
-      <c r="V52" s="12"/>
+      <c r="V52" s="2"/>
       <c r="W52" s="12"/>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X52" s="12"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3467,10 +3505,11 @@
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
-      <c r="V53" s="12"/>
+      <c r="V53" s="2"/>
       <c r="W53" s="12"/>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X53" s="12"/>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3492,10 +3531,11 @@
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
-      <c r="V54" s="12"/>
+      <c r="V54" s="2"/>
       <c r="W54" s="12"/>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X54" s="12"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3517,10 +3557,11 @@
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
-      <c r="V55" s="12"/>
+      <c r="V55" s="2"/>
       <c r="W55" s="12"/>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X55" s="12"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3542,10 +3583,11 @@
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
-      <c r="V56" s="12"/>
+      <c r="V56" s="2"/>
       <c r="W56" s="12"/>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X56" s="12"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3567,10 +3609,11 @@
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
-      <c r="V57" s="12"/>
+      <c r="V57" s="2"/>
       <c r="W57" s="12"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X57" s="12"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3592,10 +3635,11 @@
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
-      <c r="V58" s="12"/>
+      <c r="V58" s="2"/>
       <c r="W58" s="12"/>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X58" s="12"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3617,10 +3661,11 @@
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
-      <c r="V59" s="12"/>
+      <c r="V59" s="2"/>
       <c r="W59" s="12"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X59" s="12"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3642,10 +3687,11 @@
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
-      <c r="V60" s="12"/>
+      <c r="V60" s="2"/>
       <c r="W60" s="12"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X60" s="12"/>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3667,10 +3713,11 @@
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
-      <c r="V61" s="12"/>
+      <c r="V61" s="2"/>
       <c r="W61" s="12"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X61" s="12"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3692,10 +3739,11 @@
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
-      <c r="V62" s="12"/>
+      <c r="V62" s="2"/>
       <c r="W62" s="12"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X62" s="12"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3717,10 +3765,11 @@
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
-      <c r="V63" s="12"/>
+      <c r="V63" s="2"/>
       <c r="W63" s="12"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X63" s="12"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3742,10 +3791,11 @@
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
-      <c r="V64" s="12"/>
+      <c r="V64" s="2"/>
       <c r="W64" s="12"/>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X64" s="12"/>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3767,10 +3817,11 @@
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
-      <c r="V65" s="12"/>
+      <c r="V65" s="2"/>
       <c r="W65" s="12"/>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X65" s="12"/>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3792,10 +3843,11 @@
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
-      <c r="V66" s="12"/>
+      <c r="V66" s="2"/>
       <c r="W66" s="12"/>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X66" s="12"/>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3817,10 +3869,11 @@
       <c r="S67" s="2"/>
       <c r="T67" s="2"/>
       <c r="U67" s="2"/>
-      <c r="V67" s="12"/>
+      <c r="V67" s="2"/>
       <c r="W67" s="12"/>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X67" s="12"/>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3842,10 +3895,11 @@
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
-      <c r="V68" s="12"/>
+      <c r="V68" s="2"/>
       <c r="W68" s="12"/>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X68" s="12"/>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3867,10 +3921,11 @@
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
-      <c r="V69" s="12"/>
+      <c r="V69" s="2"/>
       <c r="W69" s="12"/>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X69" s="12"/>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3892,10 +3947,11 @@
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
-      <c r="V70" s="12"/>
+      <c r="V70" s="2"/>
       <c r="W70" s="12"/>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X70" s="12"/>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3917,10 +3973,11 @@
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
-      <c r="V71" s="12"/>
+      <c r="V71" s="2"/>
       <c r="W71" s="12"/>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X71" s="12"/>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3942,10 +3999,11 @@
       <c r="S72" s="2"/>
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
-      <c r="V72" s="12"/>
+      <c r="V72" s="2"/>
       <c r="W72" s="12"/>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X72" s="12"/>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3967,10 +4025,11 @@
       <c r="S73" s="2"/>
       <c r="T73" s="2"/>
       <c r="U73" s="2"/>
-      <c r="V73" s="12"/>
+      <c r="V73" s="2"/>
       <c r="W73" s="12"/>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X73" s="12"/>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3992,10 +4051,11 @@
       <c r="S74" s="2"/>
       <c r="T74" s="2"/>
       <c r="U74" s="2"/>
-      <c r="V74" s="12"/>
+      <c r="V74" s="2"/>
       <c r="W74" s="12"/>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X74" s="12"/>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4017,10 +4077,11 @@
       <c r="S75" s="2"/>
       <c r="T75" s="2"/>
       <c r="U75" s="2"/>
-      <c r="V75" s="12"/>
+      <c r="V75" s="2"/>
       <c r="W75" s="12"/>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X75" s="12"/>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4042,10 +4103,11 @@
       <c r="S76" s="2"/>
       <c r="T76" s="2"/>
       <c r="U76" s="2"/>
-      <c r="V76" s="12"/>
+      <c r="V76" s="2"/>
       <c r="W76" s="12"/>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X76" s="12"/>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4067,10 +4129,11 @@
       <c r="S77" s="2"/>
       <c r="T77" s="2"/>
       <c r="U77" s="2"/>
-      <c r="V77" s="12"/>
+      <c r="V77" s="2"/>
       <c r="W77" s="12"/>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X77" s="12"/>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -4092,10 +4155,11 @@
       <c r="S78" s="2"/>
       <c r="T78" s="2"/>
       <c r="U78" s="2"/>
-      <c r="V78" s="12"/>
+      <c r="V78" s="2"/>
       <c r="W78" s="12"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X78" s="12"/>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -4117,10 +4181,11 @@
       <c r="S79" s="2"/>
       <c r="T79" s="2"/>
       <c r="U79" s="2"/>
-      <c r="V79" s="12"/>
+      <c r="V79" s="2"/>
       <c r="W79" s="12"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X79" s="12"/>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -4142,10 +4207,11 @@
       <c r="S80" s="2"/>
       <c r="T80" s="2"/>
       <c r="U80" s="2"/>
-      <c r="V80" s="12"/>
+      <c r="V80" s="2"/>
       <c r="W80" s="12"/>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X80" s="12"/>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -4167,10 +4233,11 @@
       <c r="S81" s="2"/>
       <c r="T81" s="2"/>
       <c r="U81" s="2"/>
-      <c r="V81" s="12"/>
+      <c r="V81" s="2"/>
       <c r="W81" s="12"/>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X81" s="12"/>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4192,10 +4259,11 @@
       <c r="S82" s="2"/>
       <c r="T82" s="2"/>
       <c r="U82" s="2"/>
-      <c r="V82" s="12"/>
+      <c r="V82" s="2"/>
       <c r="W82" s="12"/>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X82" s="12"/>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4217,10 +4285,11 @@
       <c r="S83" s="2"/>
       <c r="T83" s="2"/>
       <c r="U83" s="2"/>
-      <c r="V83" s="12"/>
+      <c r="V83" s="2"/>
       <c r="W83" s="12"/>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X83" s="12"/>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4242,10 +4311,11 @@
       <c r="S84" s="2"/>
       <c r="T84" s="2"/>
       <c r="U84" s="2"/>
-      <c r="V84" s="12"/>
+      <c r="V84" s="2"/>
       <c r="W84" s="12"/>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X84" s="12"/>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4267,10 +4337,11 @@
       <c r="S85" s="2"/>
       <c r="T85" s="2"/>
       <c r="U85" s="2"/>
-      <c r="V85" s="12"/>
+      <c r="V85" s="2"/>
       <c r="W85" s="12"/>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X85" s="12"/>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4292,10 +4363,11 @@
       <c r="S86" s="2"/>
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
-      <c r="V86" s="12"/>
+      <c r="V86" s="2"/>
       <c r="W86" s="12"/>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X86" s="12"/>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4317,10 +4389,11 @@
       <c r="S87" s="2"/>
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
-      <c r="V87" s="12"/>
+      <c r="V87" s="2"/>
       <c r="W87" s="12"/>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X87" s="12"/>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4342,10 +4415,11 @@
       <c r="S88" s="2"/>
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
-      <c r="V88" s="12"/>
+      <c r="V88" s="2"/>
       <c r="W88" s="12"/>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X88" s="12"/>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4367,10 +4441,11 @@
       <c r="S89" s="2"/>
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
-      <c r="V89" s="12"/>
+      <c r="V89" s="2"/>
       <c r="W89" s="12"/>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X89" s="12"/>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4392,10 +4467,11 @@
       <c r="S90" s="2"/>
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
-      <c r="V90" s="12"/>
+      <c r="V90" s="2"/>
       <c r="W90" s="12"/>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X90" s="12"/>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4417,10 +4493,11 @@
       <c r="S91" s="2"/>
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
-      <c r="V91" s="12"/>
+      <c r="V91" s="2"/>
       <c r="W91" s="12"/>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X91" s="12"/>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4442,10 +4519,11 @@
       <c r="S92" s="2"/>
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
-      <c r="V92" s="12"/>
+      <c r="V92" s="2"/>
       <c r="W92" s="12"/>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X92" s="12"/>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -4467,10 +4545,11 @@
       <c r="S93" s="2"/>
       <c r="T93" s="2"/>
       <c r="U93" s="2"/>
-      <c r="V93" s="12"/>
+      <c r="V93" s="2"/>
       <c r="W93" s="12"/>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X93" s="12"/>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4492,10 +4571,11 @@
       <c r="S94" s="2"/>
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
-      <c r="V94" s="12"/>
+      <c r="V94" s="2"/>
       <c r="W94" s="12"/>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X94" s="12"/>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4517,10 +4597,11 @@
       <c r="S95" s="2"/>
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
-      <c r="V95" s="12"/>
+      <c r="V95" s="2"/>
       <c r="W95" s="12"/>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X95" s="12"/>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4542,10 +4623,11 @@
       <c r="S96" s="2"/>
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
-      <c r="V96" s="12"/>
+      <c r="V96" s="2"/>
       <c r="W96" s="12"/>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X96" s="12"/>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4567,10 +4649,11 @@
       <c r="S97" s="2"/>
       <c r="T97" s="2"/>
       <c r="U97" s="2"/>
-      <c r="V97" s="12"/>
+      <c r="V97" s="2"/>
       <c r="W97" s="12"/>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X97" s="12"/>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4592,10 +4675,11 @@
       <c r="S98" s="2"/>
       <c r="T98" s="2"/>
       <c r="U98" s="2"/>
-      <c r="V98" s="12"/>
+      <c r="V98" s="2"/>
       <c r="W98" s="12"/>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X98" s="12"/>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4617,10 +4701,11 @@
       <c r="S99" s="2"/>
       <c r="T99" s="2"/>
       <c r="U99" s="2"/>
-      <c r="V99" s="12"/>
+      <c r="V99" s="2"/>
       <c r="W99" s="12"/>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X99" s="12"/>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4642,10 +4727,11 @@
       <c r="S100" s="2"/>
       <c r="T100" s="2"/>
       <c r="U100" s="2"/>
-      <c r="V100" s="12"/>
+      <c r="V100" s="2"/>
       <c r="W100" s="12"/>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X100" s="12"/>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -4667,10 +4753,11 @@
       <c r="S101" s="2"/>
       <c r="T101" s="2"/>
       <c r="U101" s="2"/>
-      <c r="V101" s="12"/>
+      <c r="V101" s="2"/>
       <c r="W101" s="12"/>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X101" s="12"/>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4692,10 +4779,11 @@
       <c r="S102" s="2"/>
       <c r="T102" s="2"/>
       <c r="U102" s="2"/>
-      <c r="V102" s="12"/>
+      <c r="V102" s="2"/>
       <c r="W102" s="12"/>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X102" s="12"/>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4717,10 +4805,11 @@
       <c r="S103" s="2"/>
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
-      <c r="V103" s="12"/>
+      <c r="V103" s="2"/>
       <c r="W103" s="12"/>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X103" s="12"/>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4742,10 +4831,11 @@
       <c r="S104" s="2"/>
       <c r="T104" s="2"/>
       <c r="U104" s="2"/>
-      <c r="V104" s="12"/>
+      <c r="V104" s="2"/>
       <c r="W104" s="12"/>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X104" s="12"/>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4767,10 +4857,11 @@
       <c r="S105" s="2"/>
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
-      <c r="V105" s="12"/>
+      <c r="V105" s="2"/>
       <c r="W105" s="12"/>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X105" s="12"/>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4792,10 +4883,11 @@
       <c r="S106" s="2"/>
       <c r="T106" s="2"/>
       <c r="U106" s="2"/>
-      <c r="V106" s="12"/>
+      <c r="V106" s="2"/>
       <c r="W106" s="12"/>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X106" s="12"/>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4817,10 +4909,11 @@
       <c r="S107" s="2"/>
       <c r="T107" s="2"/>
       <c r="U107" s="2"/>
-      <c r="V107" s="12"/>
+      <c r="V107" s="2"/>
       <c r="W107" s="12"/>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X107" s="12"/>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4842,10 +4935,11 @@
       <c r="S108" s="2"/>
       <c r="T108" s="2"/>
       <c r="U108" s="2"/>
-      <c r="V108" s="12"/>
+      <c r="V108" s="2"/>
       <c r="W108" s="12"/>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X108" s="12"/>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4867,10 +4961,11 @@
       <c r="S109" s="2"/>
       <c r="T109" s="2"/>
       <c r="U109" s="2"/>
-      <c r="V109" s="12"/>
+      <c r="V109" s="2"/>
       <c r="W109" s="12"/>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X109" s="12"/>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4892,10 +4987,11 @@
       <c r="S110" s="2"/>
       <c r="T110" s="2"/>
       <c r="U110" s="2"/>
-      <c r="V110" s="12"/>
+      <c r="V110" s="2"/>
       <c r="W110" s="12"/>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X110" s="12"/>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -4917,10 +5013,11 @@
       <c r="S111" s="2"/>
       <c r="T111" s="2"/>
       <c r="U111" s="2"/>
-      <c r="V111" s="12"/>
+      <c r="V111" s="2"/>
       <c r="W111" s="12"/>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X111" s="12"/>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -4942,10 +5039,11 @@
       <c r="S112" s="2"/>
       <c r="T112" s="2"/>
       <c r="U112" s="2"/>
-      <c r="V112" s="12"/>
+      <c r="V112" s="2"/>
       <c r="W112" s="12"/>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X112" s="12"/>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4967,10 +5065,11 @@
       <c r="S113" s="2"/>
       <c r="T113" s="2"/>
       <c r="U113" s="2"/>
-      <c r="V113" s="12"/>
+      <c r="V113" s="2"/>
       <c r="W113" s="12"/>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X113" s="12"/>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -4992,10 +5091,11 @@
       <c r="S114" s="2"/>
       <c r="T114" s="2"/>
       <c r="U114" s="2"/>
-      <c r="V114" s="12"/>
+      <c r="V114" s="2"/>
       <c r="W114" s="12"/>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X114" s="12"/>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -5017,10 +5117,11 @@
       <c r="S115" s="2"/>
       <c r="T115" s="2"/>
       <c r="U115" s="2"/>
-      <c r="V115" s="12"/>
+      <c r="V115" s="2"/>
       <c r="W115" s="12"/>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X115" s="12"/>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -5042,10 +5143,11 @@
       <c r="S116" s="2"/>
       <c r="T116" s="2"/>
       <c r="U116" s="2"/>
-      <c r="V116" s="12"/>
+      <c r="V116" s="2"/>
       <c r="W116" s="12"/>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X116" s="12"/>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -5067,10 +5169,11 @@
       <c r="S117" s="2"/>
       <c r="T117" s="2"/>
       <c r="U117" s="2"/>
-      <c r="V117" s="12"/>
+      <c r="V117" s="2"/>
       <c r="W117" s="12"/>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X117" s="12"/>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -5092,10 +5195,11 @@
       <c r="S118" s="2"/>
       <c r="T118" s="2"/>
       <c r="U118" s="2"/>
-      <c r="V118" s="12"/>
+      <c r="V118" s="2"/>
       <c r="W118" s="12"/>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X118" s="12"/>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -5117,10 +5221,11 @@
       <c r="S119" s="2"/>
       <c r="T119" s="2"/>
       <c r="U119" s="2"/>
-      <c r="V119" s="12"/>
+      <c r="V119" s="2"/>
       <c r="W119" s="12"/>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X119" s="12"/>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -5142,10 +5247,11 @@
       <c r="S120" s="2"/>
       <c r="T120" s="2"/>
       <c r="U120" s="2"/>
-      <c r="V120" s="12"/>
+      <c r="V120" s="2"/>
       <c r="W120" s="12"/>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X120" s="12"/>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -5167,10 +5273,11 @@
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
       <c r="U121" s="2"/>
-      <c r="V121" s="12"/>
+      <c r="V121" s="2"/>
       <c r="W121" s="12"/>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X121" s="12"/>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -5192,10 +5299,11 @@
       <c r="S122" s="2"/>
       <c r="T122" s="2"/>
       <c r="U122" s="2"/>
-      <c r="V122" s="12"/>
+      <c r="V122" s="2"/>
       <c r="W122" s="12"/>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X122" s="12"/>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5217,10 +5325,11 @@
       <c r="S123" s="2"/>
       <c r="T123" s="2"/>
       <c r="U123" s="2"/>
-      <c r="V123" s="12"/>
+      <c r="V123" s="2"/>
       <c r="W123" s="12"/>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X123" s="12"/>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -5242,10 +5351,11 @@
       <c r="S124" s="2"/>
       <c r="T124" s="2"/>
       <c r="U124" s="2"/>
-      <c r="V124" s="12"/>
+      <c r="V124" s="2"/>
       <c r="W124" s="12"/>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X124" s="12"/>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -5267,10 +5377,11 @@
       <c r="S125" s="2"/>
       <c r="T125" s="2"/>
       <c r="U125" s="2"/>
-      <c r="V125" s="12"/>
+      <c r="V125" s="2"/>
       <c r="W125" s="12"/>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X125" s="12"/>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -5292,10 +5403,11 @@
       <c r="S126" s="2"/>
       <c r="T126" s="2"/>
       <c r="U126" s="2"/>
-      <c r="V126" s="12"/>
+      <c r="V126" s="2"/>
       <c r="W126" s="12"/>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X126" s="12"/>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -5317,10 +5429,11 @@
       <c r="S127" s="2"/>
       <c r="T127" s="2"/>
       <c r="U127" s="2"/>
-      <c r="V127" s="12"/>
+      <c r="V127" s="2"/>
       <c r="W127" s="12"/>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X127" s="12"/>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -5342,10 +5455,11 @@
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
       <c r="U128" s="2"/>
-      <c r="V128" s="12"/>
+      <c r="V128" s="2"/>
       <c r="W128" s="12"/>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X128" s="12"/>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -5367,10 +5481,11 @@
       <c r="S129" s="2"/>
       <c r="T129" s="2"/>
       <c r="U129" s="2"/>
-      <c r="V129" s="12"/>
+      <c r="V129" s="2"/>
       <c r="W129" s="12"/>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X129" s="12"/>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -5392,10 +5507,11 @@
       <c r="S130" s="2"/>
       <c r="T130" s="2"/>
       <c r="U130" s="2"/>
-      <c r="V130" s="12"/>
+      <c r="V130" s="2"/>
       <c r="W130" s="12"/>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X130" s="12"/>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -5417,10 +5533,11 @@
       <c r="S131" s="2"/>
       <c r="T131" s="2"/>
       <c r="U131" s="2"/>
-      <c r="V131" s="12"/>
+      <c r="V131" s="2"/>
       <c r="W131" s="12"/>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X131" s="12"/>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -5442,10 +5559,11 @@
       <c r="S132" s="2"/>
       <c r="T132" s="2"/>
       <c r="U132" s="2"/>
-      <c r="V132" s="12"/>
+      <c r="V132" s="2"/>
       <c r="W132" s="12"/>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X132" s="12"/>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -5467,10 +5585,11 @@
       <c r="S133" s="2"/>
       <c r="T133" s="2"/>
       <c r="U133" s="2"/>
-      <c r="V133" s="12"/>
+      <c r="V133" s="2"/>
       <c r="W133" s="12"/>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X133" s="12"/>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -5492,10 +5611,11 @@
       <c r="S134" s="2"/>
       <c r="T134" s="2"/>
       <c r="U134" s="2"/>
-      <c r="V134" s="12"/>
+      <c r="V134" s="2"/>
       <c r="W134" s="12"/>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X134" s="12"/>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -5517,10 +5637,11 @@
       <c r="S135" s="2"/>
       <c r="T135" s="2"/>
       <c r="U135" s="2"/>
-      <c r="V135" s="12"/>
+      <c r="V135" s="2"/>
       <c r="W135" s="12"/>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X135" s="12"/>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -5542,10 +5663,11 @@
       <c r="S136" s="2"/>
       <c r="T136" s="2"/>
       <c r="U136" s="2"/>
-      <c r="V136" s="12"/>
+      <c r="V136" s="2"/>
       <c r="W136" s="12"/>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X136" s="12"/>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -5567,10 +5689,11 @@
       <c r="S137" s="2"/>
       <c r="T137" s="2"/>
       <c r="U137" s="2"/>
-      <c r="V137" s="12"/>
+      <c r="V137" s="2"/>
       <c r="W137" s="12"/>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X137" s="12"/>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -5592,10 +5715,11 @@
       <c r="S138" s="2"/>
       <c r="T138" s="2"/>
       <c r="U138" s="2"/>
-      <c r="V138" s="12"/>
+      <c r="V138" s="2"/>
       <c r="W138" s="12"/>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X138" s="12"/>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -5617,10 +5741,11 @@
       <c r="S139" s="2"/>
       <c r="T139" s="2"/>
       <c r="U139" s="2"/>
-      <c r="V139" s="12"/>
+      <c r="V139" s="2"/>
       <c r="W139" s="12"/>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X139" s="12"/>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -5642,10 +5767,11 @@
       <c r="S140" s="2"/>
       <c r="T140" s="2"/>
       <c r="U140" s="2"/>
-      <c r="V140" s="12"/>
+      <c r="V140" s="2"/>
       <c r="W140" s="12"/>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X140" s="12"/>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -5667,10 +5793,11 @@
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
       <c r="U141" s="2"/>
-      <c r="V141" s="12"/>
+      <c r="V141" s="2"/>
       <c r="W141" s="12"/>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X141" s="12"/>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -5692,10 +5819,11 @@
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
       <c r="U142" s="2"/>
-      <c r="V142" s="12"/>
+      <c r="V142" s="2"/>
       <c r="W142" s="12"/>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X142" s="12"/>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -5717,10 +5845,11 @@
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
       <c r="U143" s="2"/>
-      <c r="V143" s="12"/>
+      <c r="V143" s="2"/>
       <c r="W143" s="12"/>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X143" s="12"/>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -5742,10 +5871,11 @@
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
       <c r="U144" s="2"/>
-      <c r="V144" s="12"/>
+      <c r="V144" s="2"/>
       <c r="W144" s="12"/>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X144" s="12"/>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -5767,10 +5897,11 @@
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>
       <c r="U145" s="2"/>
-      <c r="V145" s="12"/>
+      <c r="V145" s="2"/>
       <c r="W145" s="12"/>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X145" s="12"/>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -5792,10 +5923,11 @@
       <c r="S146" s="2"/>
       <c r="T146" s="2"/>
       <c r="U146" s="2"/>
-      <c r="V146" s="12"/>
+      <c r="V146" s="2"/>
       <c r="W146" s="12"/>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X146" s="12"/>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5817,10 +5949,11 @@
       <c r="S147" s="2"/>
       <c r="T147" s="2"/>
       <c r="U147" s="2"/>
-      <c r="V147" s="12"/>
+      <c r="V147" s="2"/>
       <c r="W147" s="12"/>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X147" s="12"/>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5842,10 +5975,11 @@
       <c r="S148" s="2"/>
       <c r="T148" s="2"/>
       <c r="U148" s="2"/>
-      <c r="V148" s="12"/>
+      <c r="V148" s="2"/>
       <c r="W148" s="12"/>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X148" s="12"/>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -5867,10 +6001,11 @@
       <c r="S149" s="2"/>
       <c r="T149" s="2"/>
       <c r="U149" s="2"/>
-      <c r="V149" s="12"/>
+      <c r="V149" s="2"/>
       <c r="W149" s="12"/>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X149" s="12"/>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -5892,10 +6027,11 @@
       <c r="S150" s="2"/>
       <c r="T150" s="2"/>
       <c r="U150" s="2"/>
-      <c r="V150" s="12"/>
+      <c r="V150" s="2"/>
       <c r="W150" s="12"/>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X150" s="12"/>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -5917,10 +6053,11 @@
       <c r="S151" s="2"/>
       <c r="T151" s="2"/>
       <c r="U151" s="2"/>
-      <c r="V151" s="12"/>
+      <c r="V151" s="2"/>
       <c r="W151" s="12"/>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X151" s="12"/>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -5942,10 +6079,11 @@
       <c r="S152" s="2"/>
       <c r="T152" s="2"/>
       <c r="U152" s="2"/>
-      <c r="V152" s="12"/>
+      <c r="V152" s="2"/>
       <c r="W152" s="12"/>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X152" s="12"/>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -5967,10 +6105,11 @@
       <c r="S153" s="2"/>
       <c r="T153" s="2"/>
       <c r="U153" s="2"/>
-      <c r="V153" s="12"/>
+      <c r="V153" s="2"/>
       <c r="W153" s="12"/>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X153" s="12"/>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -5992,10 +6131,11 @@
       <c r="S154" s="2"/>
       <c r="T154" s="2"/>
       <c r="U154" s="2"/>
-      <c r="V154" s="12"/>
+      <c r="V154" s="2"/>
       <c r="W154" s="12"/>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X154" s="12"/>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -6017,10 +6157,11 @@
       <c r="S155" s="2"/>
       <c r="T155" s="2"/>
       <c r="U155" s="2"/>
-      <c r="V155" s="12"/>
+      <c r="V155" s="2"/>
       <c r="W155" s="12"/>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X155" s="12"/>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -6042,10 +6183,11 @@
       <c r="S156" s="2"/>
       <c r="T156" s="2"/>
       <c r="U156" s="2"/>
-      <c r="V156" s="12"/>
+      <c r="V156" s="2"/>
       <c r="W156" s="12"/>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X156" s="12"/>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -6067,10 +6209,11 @@
       <c r="S157" s="2"/>
       <c r="T157" s="2"/>
       <c r="U157" s="2"/>
-      <c r="V157" s="12"/>
+      <c r="V157" s="2"/>
       <c r="W157" s="12"/>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X157" s="12"/>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -6092,10 +6235,11 @@
       <c r="S158" s="2"/>
       <c r="T158" s="2"/>
       <c r="U158" s="2"/>
-      <c r="V158" s="12"/>
+      <c r="V158" s="2"/>
       <c r="W158" s="12"/>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X158" s="12"/>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -6117,10 +6261,11 @@
       <c r="S159" s="2"/>
       <c r="T159" s="2"/>
       <c r="U159" s="2"/>
-      <c r="V159" s="12"/>
+      <c r="V159" s="2"/>
       <c r="W159" s="12"/>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X159" s="12"/>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -6142,10 +6287,11 @@
       <c r="S160" s="2"/>
       <c r="T160" s="2"/>
       <c r="U160" s="2"/>
-      <c r="V160" s="12"/>
+      <c r="V160" s="2"/>
       <c r="W160" s="12"/>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X160" s="12"/>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -6167,10 +6313,11 @@
       <c r="S161" s="2"/>
       <c r="T161" s="2"/>
       <c r="U161" s="2"/>
-      <c r="V161" s="12"/>
+      <c r="V161" s="2"/>
       <c r="W161" s="12"/>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X161" s="12"/>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -6192,10 +6339,11 @@
       <c r="S162" s="2"/>
       <c r="T162" s="2"/>
       <c r="U162" s="2"/>
-      <c r="V162" s="12"/>
+      <c r="V162" s="2"/>
       <c r="W162" s="12"/>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X162" s="12"/>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -6217,10 +6365,11 @@
       <c r="S163" s="2"/>
       <c r="T163" s="2"/>
       <c r="U163" s="2"/>
-      <c r="V163" s="12"/>
+      <c r="V163" s="2"/>
       <c r="W163" s="12"/>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X163" s="12"/>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -6242,10 +6391,11 @@
       <c r="S164" s="2"/>
       <c r="T164" s="2"/>
       <c r="U164" s="2"/>
-      <c r="V164" s="12"/>
+      <c r="V164" s="2"/>
       <c r="W164" s="12"/>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X164" s="12"/>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -6267,10 +6417,11 @@
       <c r="S165" s="2"/>
       <c r="T165" s="2"/>
       <c r="U165" s="2"/>
-      <c r="V165" s="12"/>
+      <c r="V165" s="2"/>
       <c r="W165" s="12"/>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X165" s="12"/>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -6292,10 +6443,11 @@
       <c r="S166" s="2"/>
       <c r="T166" s="2"/>
       <c r="U166" s="2"/>
-      <c r="V166" s="12"/>
+      <c r="V166" s="2"/>
       <c r="W166" s="12"/>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X166" s="12"/>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -6317,10 +6469,11 @@
       <c r="S167" s="2"/>
       <c r="T167" s="2"/>
       <c r="U167" s="2"/>
-      <c r="V167" s="12"/>
+      <c r="V167" s="2"/>
       <c r="W167" s="12"/>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X167" s="12"/>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -6342,10 +6495,11 @@
       <c r="S168" s="2"/>
       <c r="T168" s="2"/>
       <c r="U168" s="2"/>
-      <c r="V168" s="12"/>
+      <c r="V168" s="2"/>
       <c r="W168" s="12"/>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X168" s="12"/>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -6367,10 +6521,11 @@
       <c r="S169" s="2"/>
       <c r="T169" s="2"/>
       <c r="U169" s="2"/>
-      <c r="V169" s="12"/>
+      <c r="V169" s="2"/>
       <c r="W169" s="12"/>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X169" s="12"/>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -6392,10 +6547,11 @@
       <c r="S170" s="2"/>
       <c r="T170" s="2"/>
       <c r="U170" s="2"/>
-      <c r="V170" s="12"/>
+      <c r="V170" s="2"/>
       <c r="W170" s="12"/>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X170" s="12"/>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -6417,10 +6573,11 @@
       <c r="S171" s="2"/>
       <c r="T171" s="2"/>
       <c r="U171" s="2"/>
-      <c r="V171" s="12"/>
+      <c r="V171" s="2"/>
       <c r="W171" s="12"/>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X171" s="12"/>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -6442,10 +6599,11 @@
       <c r="S172" s="2"/>
       <c r="T172" s="2"/>
       <c r="U172" s="2"/>
-      <c r="V172" s="12"/>
+      <c r="V172" s="2"/>
       <c r="W172" s="12"/>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X172" s="12"/>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -6467,10 +6625,11 @@
       <c r="S173" s="2"/>
       <c r="T173" s="2"/>
       <c r="U173" s="2"/>
-      <c r="V173" s="12"/>
+      <c r="V173" s="2"/>
       <c r="W173" s="12"/>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X173" s="12"/>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -6492,10 +6651,11 @@
       <c r="S174" s="2"/>
       <c r="T174" s="2"/>
       <c r="U174" s="2"/>
-      <c r="V174" s="12"/>
+      <c r="V174" s="2"/>
       <c r="W174" s="12"/>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X174" s="12"/>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -6517,10 +6677,11 @@
       <c r="S175" s="2"/>
       <c r="T175" s="2"/>
       <c r="U175" s="2"/>
-      <c r="V175" s="12"/>
+      <c r="V175" s="2"/>
       <c r="W175" s="12"/>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X175" s="12"/>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -6542,10 +6703,11 @@
       <c r="S176" s="2"/>
       <c r="T176" s="2"/>
       <c r="U176" s="2"/>
-      <c r="V176" s="12"/>
+      <c r="V176" s="2"/>
       <c r="W176" s="12"/>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X176" s="12"/>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -6567,10 +6729,11 @@
       <c r="S177" s="2"/>
       <c r="T177" s="2"/>
       <c r="U177" s="2"/>
-      <c r="V177" s="12"/>
+      <c r="V177" s="2"/>
       <c r="W177" s="12"/>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X177" s="12"/>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -6592,10 +6755,11 @@
       <c r="S178" s="2"/>
       <c r="T178" s="2"/>
       <c r="U178" s="2"/>
-      <c r="V178" s="12"/>
+      <c r="V178" s="2"/>
       <c r="W178" s="12"/>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X178" s="12"/>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -6617,10 +6781,11 @@
       <c r="S179" s="2"/>
       <c r="T179" s="2"/>
       <c r="U179" s="2"/>
-      <c r="V179" s="12"/>
+      <c r="V179" s="2"/>
       <c r="W179" s="12"/>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X179" s="12"/>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -6642,10 +6807,11 @@
       <c r="S180" s="2"/>
       <c r="T180" s="2"/>
       <c r="U180" s="2"/>
-      <c r="V180" s="12"/>
+      <c r="V180" s="2"/>
       <c r="W180" s="12"/>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X180" s="12"/>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -6667,10 +6833,11 @@
       <c r="S181" s="2"/>
       <c r="T181" s="2"/>
       <c r="U181" s="2"/>
-      <c r="V181" s="12"/>
+      <c r="V181" s="2"/>
       <c r="W181" s="12"/>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X181" s="12"/>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -6692,10 +6859,11 @@
       <c r="S182" s="2"/>
       <c r="T182" s="2"/>
       <c r="U182" s="2"/>
-      <c r="V182" s="12"/>
+      <c r="V182" s="2"/>
       <c r="W182" s="12"/>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X182" s="12"/>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -6717,10 +6885,11 @@
       <c r="S183" s="2"/>
       <c r="T183" s="2"/>
       <c r="U183" s="2"/>
-      <c r="V183" s="12"/>
+      <c r="V183" s="2"/>
       <c r="W183" s="12"/>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X183" s="12"/>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -6742,10 +6911,11 @@
       <c r="S184" s="2"/>
       <c r="T184" s="2"/>
       <c r="U184" s="2"/>
-      <c r="V184" s="12"/>
+      <c r="V184" s="2"/>
       <c r="W184" s="12"/>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X184" s="12"/>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -6767,10 +6937,11 @@
       <c r="S185" s="2"/>
       <c r="T185" s="2"/>
       <c r="U185" s="2"/>
-      <c r="V185" s="12"/>
+      <c r="V185" s="2"/>
       <c r="W185" s="12"/>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X185" s="12"/>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -6792,10 +6963,11 @@
       <c r="S186" s="2"/>
       <c r="T186" s="2"/>
       <c r="U186" s="2"/>
-      <c r="V186" s="12"/>
+      <c r="V186" s="2"/>
       <c r="W186" s="12"/>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X186" s="12"/>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -6817,10 +6989,11 @@
       <c r="S187" s="2"/>
       <c r="T187" s="2"/>
       <c r="U187" s="2"/>
-      <c r="V187" s="12"/>
+      <c r="V187" s="2"/>
       <c r="W187" s="12"/>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X187" s="12"/>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -6842,10 +7015,11 @@
       <c r="S188" s="2"/>
       <c r="T188" s="2"/>
       <c r="U188" s="2"/>
-      <c r="V188" s="12"/>
+      <c r="V188" s="2"/>
       <c r="W188" s="12"/>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X188" s="12"/>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -6867,10 +7041,11 @@
       <c r="S189" s="2"/>
       <c r="T189" s="2"/>
       <c r="U189" s="2"/>
-      <c r="V189" s="12"/>
+      <c r="V189" s="2"/>
       <c r="W189" s="12"/>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X189" s="12"/>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -6892,10 +7067,11 @@
       <c r="S190" s="2"/>
       <c r="T190" s="2"/>
       <c r="U190" s="2"/>
-      <c r="V190" s="12"/>
+      <c r="V190" s="2"/>
       <c r="W190" s="12"/>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X190" s="12"/>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -6917,10 +7093,11 @@
       <c r="S191" s="2"/>
       <c r="T191" s="2"/>
       <c r="U191" s="2"/>
-      <c r="V191" s="12"/>
+      <c r="V191" s="2"/>
       <c r="W191" s="12"/>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X191" s="12"/>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -6942,10 +7119,11 @@
       <c r="S192" s="2"/>
       <c r="T192" s="2"/>
       <c r="U192" s="2"/>
-      <c r="V192" s="12"/>
+      <c r="V192" s="2"/>
       <c r="W192" s="12"/>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X192" s="12"/>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -6967,10 +7145,11 @@
       <c r="S193" s="2"/>
       <c r="T193" s="2"/>
       <c r="U193" s="2"/>
-      <c r="V193" s="12"/>
+      <c r="V193" s="2"/>
       <c r="W193" s="12"/>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X193" s="12"/>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -6992,10 +7171,11 @@
       <c r="S194" s="2"/>
       <c r="T194" s="2"/>
       <c r="U194" s="2"/>
-      <c r="V194" s="12"/>
+      <c r="V194" s="2"/>
       <c r="W194" s="12"/>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X194" s="12"/>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -7017,10 +7197,11 @@
       <c r="S195" s="2"/>
       <c r="T195" s="2"/>
       <c r="U195" s="2"/>
-      <c r="V195" s="12"/>
+      <c r="V195" s="2"/>
       <c r="W195" s="12"/>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X195" s="12"/>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -7042,10 +7223,11 @@
       <c r="S196" s="2"/>
       <c r="T196" s="2"/>
       <c r="U196" s="2"/>
-      <c r="V196" s="12"/>
+      <c r="V196" s="2"/>
       <c r="W196" s="12"/>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X196" s="12"/>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -7067,10 +7249,11 @@
       <c r="S197" s="2"/>
       <c r="T197" s="2"/>
       <c r="U197" s="2"/>
-      <c r="V197" s="12"/>
+      <c r="V197" s="2"/>
       <c r="W197" s="12"/>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X197" s="12"/>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -7092,10 +7275,11 @@
       <c r="S198" s="2"/>
       <c r="T198" s="2"/>
       <c r="U198" s="2"/>
-      <c r="V198" s="12"/>
+      <c r="V198" s="2"/>
       <c r="W198" s="12"/>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X198" s="12"/>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -7117,10 +7301,11 @@
       <c r="S199" s="2"/>
       <c r="T199" s="2"/>
       <c r="U199" s="2"/>
-      <c r="V199" s="12"/>
+      <c r="V199" s="2"/>
       <c r="W199" s="12"/>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X199" s="12"/>
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -7142,10 +7327,11 @@
       <c r="S200" s="2"/>
       <c r="T200" s="2"/>
       <c r="U200" s="2"/>
-      <c r="V200" s="12"/>
+      <c r="V200" s="2"/>
       <c r="W200" s="12"/>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X200" s="12"/>
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -7167,10 +7353,11 @@
       <c r="S201" s="2"/>
       <c r="T201" s="2"/>
       <c r="U201" s="2"/>
-      <c r="V201" s="12"/>
+      <c r="V201" s="2"/>
       <c r="W201" s="12"/>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X201" s="12"/>
+    </row>
+    <row r="202" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -7192,10 +7379,11 @@
       <c r="S202" s="2"/>
       <c r="T202" s="2"/>
       <c r="U202" s="2"/>
-      <c r="V202" s="12"/>
+      <c r="V202" s="2"/>
       <c r="W202" s="12"/>
-    </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X202" s="12"/>
+    </row>
+    <row r="203" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -7217,27 +7405,28 @@
       <c r="S203" s="2"/>
       <c r="T203" s="2"/>
       <c r="U203" s="2"/>
-      <c r="V203" s="12"/>
+      <c r="V203" s="2"/>
       <c r="W203" s="12"/>
+      <c r="X203" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="L2Sz3EQ7q8X8k0QX9HuZLZGL5QPNBWFdKcjInYAvZRTs0m+8xQDeO1dotLIP3jnyp00b5HeXNCVrSLKkOEzPiQ==" saltValue="REBVsDLv+Xn50TjjAQQ/ZA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="W2:X2"/>
     <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="T2:U2"/>
     <mergeCell ref="R2:S2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="T2:V2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3 F3 H3 J3 L3 N3 Q2:Q3 V3 W3" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3 F3 H3 J3 L3 N3 Q2:Q3 W3 X3" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
     <dataValidation type="custom" sqref="P3" xr:uid="{746A974C-37B7-4392-8C1F-3624962D83AA}">
@@ -7245,16 +7434,16 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V3" r:id="rId1" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
-    <hyperlink ref="W3" r:id="rId2" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
-    <hyperlink ref="E2:E3" r:id="rId3" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
-    <hyperlink ref="H3" r:id="rId4" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
-    <hyperlink ref="L3" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
-    <hyperlink ref="F3" r:id="rId6" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
-    <hyperlink ref="J3" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
-    <hyperlink ref="N3" r:id="rId8" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
+    <hyperlink ref="W3" r:id="rId1" location="depredationSources" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
+    <hyperlink ref="X3" r:id="rId2" location="predators" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
+    <hyperlink ref="E2:E3" r:id="rId3" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
+    <hyperlink ref="H3" r:id="rId4" location="lengthMeasurementTools" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
+    <hyperlink ref="L3" r:id="rId5" location="lengthMeasurementTools" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
+    <hyperlink ref="F3" r:id="rId6" location="lengthMeasurementTypes" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
+    <hyperlink ref="J3" r:id="rId7" location="lengthMeasurementTypes" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
+    <hyperlink ref="N3" r:id="rId8" location="fishProcessingTypes" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
     <hyperlink ref="Q2:Q3" r:id="rId9" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
-    <hyperlink ref="P3" r:id="rId10" location="weightMeasurementTools" display="WEIGHT_MEASUREMENT_TOOL_CODE" xr:uid="{074E1E59-D343-4222-8E1C-310625164A04}"/>
+    <hyperlink ref="P3" r:id="rId10" location="weightMeasurementTools" xr:uid="{074E1E59-D343-4222-8E1C-310625164A04}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7283,7 +7472,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -7299,61 +7488,61 @@
       <c r="M1" s="14"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>69</v>
+      <c r="A2" s="113" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>71</v>
+      <c r="B2" s="113" t="s">
+        <v>66</v>
       </c>
-      <c r="C2" s="119" t="s">
-        <v>72</v>
+      <c r="C2" s="113" t="s">
+        <v>67</v>
       </c>
-      <c r="D2" s="119" t="s">
-        <v>73</v>
+      <c r="D2" s="113" t="s">
+        <v>68</v>
       </c>
-      <c r="E2" s="105" t="s">
-        <v>206</v>
+      <c r="E2" s="103" t="s">
+        <v>191</v>
       </c>
-      <c r="F2" s="105" t="s">
-        <v>207</v>
+      <c r="F2" s="103" t="s">
+        <v>192</v>
       </c>
-      <c r="G2" s="105" t="s">
-        <v>208</v>
+      <c r="G2" s="103" t="s">
+        <v>193</v>
       </c>
-      <c r="H2" s="121" t="s">
+      <c r="H2" s="116" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="115" t="s">
+        <v>194</v>
+      </c>
+      <c r="J2" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="122" t="s">
-        <v>209</v>
-      </c>
-      <c r="J2" s="121" t="s">
+      <c r="K2" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="121" t="s">
-        <v>47</v>
+      <c r="L2" s="91" t="s">
+        <v>186</v>
       </c>
-      <c r="L2" s="96" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="96"/>
+      <c r="M2" s="91"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
       <c r="L3" s="40" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="M3" s="40" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -10357,8 +10546,13 @@
       <c r="M203" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BGDYvh08S3NYZIuspsRRCAicI1Gp8B4hCVX6TD3PYP3B6k2058cKh0vrrp9OQ+vPcDsnDczSdbeeSJcJFOUPXA==" saltValue="U5shOM/WfotH/IVdI6hz3g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="E2:E3"/>
@@ -10366,11 +10560,6 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H2:H3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 G2:G3 I2:I3 E2:E3 L3 M3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -10378,14 +10567,14 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2:G3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{4D21FAB4-D1ED-49FA-A8E9-1A452DA8E255}"/>
+    <hyperlink ref="G2:G3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION" xr:uid="{4D21FAB4-D1ED-49FA-A8E9-1A452DA8E255}"/>
     <hyperlink ref="I2:I3" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD" xr:uid="{4AAC5290-0C1E-413E-9063-304F215E9866}"/>
     <hyperlink ref="E2" r:id="rId3" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{26B5C55C-6931-4D84-B6B4-4AA585019D2E}"/>
     <hyperlink ref="F2" r:id="rId4" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{312D6457-0D67-4610-B478-F5AE649B98F6}"/>
-    <hyperlink ref="L3" r:id="rId5" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{11FAA504-1FFB-4306-A7A1-4F548FAD3A87}"/>
-    <hyperlink ref="M3" r:id="rId6" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{AD1EB751-9874-431A-A9CC-CB89B7E2E48C}"/>
-    <hyperlink ref="E2:E3" r:id="rId7" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{F4906E56-6A88-4C64-867C-2ABD778A70BA}"/>
-    <hyperlink ref="F2:F3" r:id="rId8" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{EFA1D569-0D47-49ED-B0FE-53D3A24E5072}"/>
+    <hyperlink ref="L3" r:id="rId5" location="depredationSources" xr:uid="{11FAA504-1FFB-4306-A7A1-4F548FAD3A87}"/>
+    <hyperlink ref="M3" r:id="rId6" location="predators" xr:uid="{AD1EB751-9874-431A-A9CC-CB89B7E2E48C}"/>
+    <hyperlink ref="E2:E3" r:id="rId7" location="individualConditions" display="CONDITION_AT_CAPTURE" xr:uid="{F4906E56-6A88-4C64-867C-2ABD778A70BA}"/>
+    <hyperlink ref="F2:F3" r:id="rId8" location="individualConditions" display="CONDITION_AT_RELEASE" xr:uid="{EFA1D569-0D47-49ED-B0FE-53D3A24E5072}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -10409,7 +10598,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -10423,38 +10612,38 @@
       <c r="K1" s="9"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="123" t="s">
-        <v>69</v>
+      <c r="A2" s="58" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="123" t="s">
-        <v>71</v>
+      <c r="B2" s="58" t="s">
+        <v>66</v>
       </c>
-      <c r="C2" s="123" t="s">
-        <v>72</v>
+      <c r="C2" s="58" t="s">
+        <v>67</v>
       </c>
-      <c r="D2" s="123" t="s">
-        <v>73</v>
+      <c r="D2" s="58" t="s">
+        <v>68</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="G2" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="53" t="s">
+      <c r="I2" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="53" t="s">
-        <v>44</v>
+      <c r="J2" s="50" t="s">
+        <v>195</v>
       </c>
-      <c r="J2" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="K2" s="53" t="s">
-        <v>211</v>
+      <c r="K2" s="50" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -13058,14 +13247,14 @@
       <c r="K202" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Vwz9MEssO0goVxqhgAwHa3I8nZIbUsJ/hDmr5WJQRnRW1O9mkMmveNAJn3+YQYFbM386p0Qsf1A4Bx3j8YBqmQ==" saltValue="tCOsHPMw/F4qapC8jD1j6g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" location="tagTypes" display="TYPE_CODE" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
+    <hyperlink ref="G2" r:id="rId1" location="tagTypes" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13089,7 +13278,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -13098,23 +13287,23 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
-        <v>69</v>
+      <c r="A2" s="48" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="54" t="s">
-        <v>56</v>
+      <c r="B2" s="50" t="s">
+        <v>55</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="57" t="s">
-        <v>212</v>
+      <c r="E2" s="43" t="s">
+        <v>197</v>
       </c>
-      <c r="F2" s="54" t="s">
-        <v>100</v>
+      <c r="F2" s="50" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -14718,14 +14907,14 @@
       <c r="F202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="aNLIUFMRGP9rhjSiTMciqDb/aZXmvd2G4p0ihampL85tP7rFZHWXV1BGytlngLb76LLwu4rBmkz3rb0/vGhZ1A==" saltValue="rk028G82KZqr5K1O7ZHc0w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{A7F07E3F-7588-4A6B-9139-C33F06BE5D6F}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" location="surfaceFisheryActivityTypes" display="ACTIVITY_TYPE_CODE" xr:uid="{88637062-1DEC-43E2-B806-B93CACD553AC}"/>
+    <hyperlink ref="E2" r:id="rId1" location="surfaceFisheryActivityTypes" xr:uid="{88637062-1DEC-43E2-B806-B93CACD553AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14764,7 +14953,7 @@
   <sheetData>
     <row r="1" spans="1:25" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -14791,181 +14980,181 @@
       <c r="X1" s="8"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
-        <v>69</v>
+      <c r="A2" s="69" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="74" t="s">
-        <v>122</v>
+      <c r="B2" s="69" t="s">
+        <v>110</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74" t="s">
-        <v>123</v>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69" t="s">
+        <v>111</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74" t="s">
-        <v>127</v>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69" t="s">
+        <v>115</v>
       </c>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
+      <c r="W2" s="69"/>
+      <c r="X2" s="69"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="77" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="77" t="s">
-        <v>54</v>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
+      <c r="W3" s="69"/>
+      <c r="X3" s="69"/>
+      <c r="Y3" s="4"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="69"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70" t="s">
+        <v>112</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="4"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="74"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="75" t="s">
-        <v>124</v>
+      <c r="E4" s="71"/>
+      <c r="F4" s="70" t="s">
+        <v>113</v>
       </c>
-      <c r="E4" s="76"/>
-      <c r="F4" s="75" t="s">
-        <v>125</v>
+      <c r="G4" s="71"/>
+      <c r="H4" s="76" t="s">
+        <v>55</v>
       </c>
-      <c r="G4" s="76"/>
-      <c r="H4" s="81" t="s">
-        <v>56</v>
+      <c r="I4" s="74" t="s">
+        <v>112</v>
       </c>
-      <c r="I4" s="79" t="s">
-        <v>124</v>
+      <c r="J4" s="75"/>
+      <c r="K4" s="70" t="s">
+        <v>113</v>
       </c>
-      <c r="J4" s="80"/>
-      <c r="K4" s="75" t="s">
-        <v>125</v>
+      <c r="L4" s="71"/>
+      <c r="M4" s="76" t="s">
+        <v>55</v>
       </c>
-      <c r="L4" s="76"/>
-      <c r="M4" s="81" t="s">
-        <v>56</v>
+      <c r="N4" s="69" t="s">
+        <v>116</v>
       </c>
-      <c r="N4" s="74" t="s">
-        <v>128</v>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69" t="s">
+        <v>117</v>
       </c>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74" t="s">
-        <v>129</v>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="79" t="s">
+        <v>118</v>
       </c>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="84" t="s">
-        <v>130</v>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="81"/>
+    </row>
+    <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="69"/>
+      <c r="B5" s="41" t="s">
+        <v>92</v>
       </c>
-      <c r="V4" s="85"/>
-      <c r="W4" s="85"/>
-      <c r="X4" s="86"/>
-    </row>
-    <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="46" t="s">
-        <v>126</v>
+      <c r="D5" s="45" t="s">
+        <v>114</v>
       </c>
-      <c r="E5" s="46" t="s">
+      <c r="E5" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="82"/>
+      <c r="H5" s="77"/>
       <c r="I5" s="40" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="J5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="43" t="s">
+      <c r="L5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="82"/>
-      <c r="N5" s="42" t="s">
+      <c r="M5" s="77"/>
+      <c r="N5" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="42" t="s">
+      <c r="O5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="Q5" s="42" t="s">
+      <c r="Q5" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="45" t="s">
+      <c r="R5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="45" t="s">
+      <c r="S5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="42" t="s">
+      <c r="T5" s="41" t="s">
         <v>10</v>
       </c>
       <c r="U5" s="40" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="V5" s="40" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="W5" s="40" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="X5" s="40" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -15259,7 +15448,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -20145,7 +20334,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RdNrOAn/lQMbMlrvotSd6e7DAP6LRqnMQsSQdK2ijNoYLV6uZuPnsrPuGGdEV+gbuZ9hwJUmPp3VbLE6xYZ72A==" saltValue="8ZiNB57QGOGYw7UGazEnig==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -20169,9 +20358,9 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{1EF7C411-C924-445B-93A8-81FE1F6EF8E5}"/>
-    <hyperlink ref="I5" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{6665352C-5C90-46CB-A26B-B4E9D695ADBA}"/>
-    <hyperlink ref="U5" r:id="rId3" location="reasonsDaysLost" display="REASON_1_CODE" xr:uid="{6CDE9788-81BE-4354-9F23-5E2FD77D042A}"/>
+    <hyperlink ref="D5" r:id="rId1" location="countries" xr:uid="{1EF7C411-C924-445B-93A8-81FE1F6EF8E5}"/>
+    <hyperlink ref="I5" r:id="rId2" location="countries" xr:uid="{6665352C-5C90-46CB-A26B-B4E9D695ADBA}"/>
+    <hyperlink ref="U5" r:id="rId3" location="reasonsDaysLost" xr:uid="{6CDE9788-81BE-4354-9F23-5E2FD77D042A}"/>
     <hyperlink ref="V5" r:id="rId4" location="reasonsDaysLost" display="REASON_2_CODE" xr:uid="{3955310B-45A1-4FFC-AD47-D85E65B9B8C5}"/>
     <hyperlink ref="W5" r:id="rId5" location="reasonsDaysLost" display="REASON_3_CODE" xr:uid="{F6A2D174-87CA-4A84-A59B-9C5B3EDFA410}"/>
     <hyperlink ref="X5" r:id="rId6" location="reasonsDaysLost" display="REASON_4_CODE" xr:uid="{4AD9F6B4-F493-4D51-A425-E40A5E342DD0}"/>
@@ -20188,29 +20377,30 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:P204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="3"/>
-    <col min="3" max="3" width="23.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="14" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -20219,110 +20409,112 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="11"/>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
-      <c r="O1" s="8"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>69</v>
+      <c r="O1" s="7"/>
+      <c r="P1" s="8"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="76" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="88" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="89"/>
-      <c r="I2" s="48" t="s">
-        <v>138</v>
+      <c r="H2" s="117"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="103" t="s">
+        <v>201</v>
       </c>
-      <c r="J2" s="41" t="s">
-        <v>70</v>
+      <c r="K2" s="97" t="s">
+        <v>123</v>
       </c>
-      <c r="K2" s="90" t="s">
-        <v>116</v>
+      <c r="L2" s="85" t="s">
+        <v>107</v>
       </c>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="92"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="74" t="s">
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="87"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="82"/>
+      <c r="B3" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="100" t="s">
-        <v>135</v>
+      <c r="C3" s="95" t="s">
+        <v>199</v>
       </c>
-      <c r="D3" s="74" t="s">
+      <c r="D3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="118" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="115"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="88" t="s">
+        <v>124</v>
+      </c>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="88"/>
+      <c r="P3" s="89" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="77"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="97" t="s">
-        <v>136</v>
-      </c>
-      <c r="J3" s="102" t="s">
-        <v>137</v>
-      </c>
-      <c r="K3" s="93" t="s">
-        <v>139</v>
-      </c>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93" t="s">
-        <v>140</v>
-      </c>
-      <c r="N3" s="93"/>
-      <c r="O3" s="94" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="42" t="s">
+      <c r="N4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="46" t="s">
-        <v>141</v>
+      <c r="O4" s="45" t="s">
+        <v>126</v>
       </c>
-      <c r="M4" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="O4" s="94"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="89"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -20338,8 +20530,9 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -20355,8 +20548,9 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -20372,8 +20566,9 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -20389,8 +20584,9 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -20406,8 +20602,9 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -20423,8 +20620,9 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11"/>
@@ -20440,8 +20638,9 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -20457,8 +20656,9 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -20474,8 +20674,9 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -20491,8 +20692,9 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -20508,8 +20710,9 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -20525,8 +20728,9 @@
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -20542,8 +20746,9 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -20559,8 +20764,9 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -20576,8 +20782,9 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -20593,8 +20800,9 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -20610,8 +20818,9 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -20627,8 +20836,9 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -20644,8 +20854,9 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -20661,8 +20872,9 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -20678,8 +20890,9 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -20695,8 +20908,9 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -20712,8 +20926,9 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -20729,8 +20944,9 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -20746,8 +20962,9 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -20763,8 +20980,9 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -20780,8 +20998,9 @@
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -20797,8 +21016,9 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -20814,8 +21034,9 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -20831,8 +21052,9 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -20848,8 +21070,9 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -20865,8 +21088,9 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -20882,8 +21106,9 @@
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -20899,8 +21124,9 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -20916,8 +21142,9 @@
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -20933,8 +21160,9 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P40" s="2"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -20950,8 +21178,9 @@
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P41" s="2"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -20967,8 +21196,9 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P42" s="2"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -20984,8 +21214,9 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P43" s="2"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -21001,8 +21232,9 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P44" s="2"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -21018,8 +21250,9 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P45" s="2"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -21035,8 +21268,9 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P46" s="2"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -21052,8 +21286,9 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -21069,8 +21304,9 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P48" s="2"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -21086,8 +21322,9 @@
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P49" s="2"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -21103,8 +21340,9 @@
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P50" s="2"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -21120,8 +21358,9 @@
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P51" s="2"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -21137,8 +21376,9 @@
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P52" s="2"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -21154,8 +21394,9 @@
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P53" s="2"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -21171,8 +21412,9 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P54" s="2"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -21188,8 +21430,9 @@
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P55" s="2"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -21205,8 +21448,9 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -21222,8 +21466,9 @@
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P57" s="2"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -21239,8 +21484,9 @@
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P58" s="2"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -21256,8 +21502,9 @@
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P59" s="2"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -21273,8 +21520,9 @@
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P60" s="2"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -21290,8 +21538,9 @@
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P61" s="2"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -21307,8 +21556,9 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P62" s="2"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -21324,8 +21574,9 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P63" s="2"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -21341,8 +21592,9 @@
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P64" s="2"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -21358,8 +21610,9 @@
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P65" s="2"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -21375,8 +21628,9 @@
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P66" s="2"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -21392,8 +21646,9 @@
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P67" s="2"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -21409,8 +21664,9 @@
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P68" s="2"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -21426,8 +21682,9 @@
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P69" s="2"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -21443,8 +21700,9 @@
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P70" s="2"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -21460,8 +21718,9 @@
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P71" s="2"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -21477,8 +21736,9 @@
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P72" s="2"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -21494,8 +21754,9 @@
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P73" s="2"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -21511,8 +21772,9 @@
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P74" s="2"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -21528,8 +21790,9 @@
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P75" s="2"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -21545,8 +21808,9 @@
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P76" s="2"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -21562,8 +21826,9 @@
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P77" s="2"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -21579,8 +21844,9 @@
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P78" s="2"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -21596,8 +21862,9 @@
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P79" s="2"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -21613,8 +21880,9 @@
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -21630,8 +21898,9 @@
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P81" s="2"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -21647,8 +21916,9 @@
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P82" s="2"/>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -21664,8 +21934,9 @@
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P83" s="2"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -21681,8 +21952,9 @@
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P84" s="2"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -21698,8 +21970,9 @@
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P85" s="2"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -21715,8 +21988,9 @@
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P86" s="2"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -21732,8 +22006,9 @@
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P87" s="2"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -21749,8 +22024,9 @@
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P88" s="2"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -21766,8 +22042,9 @@
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P89" s="2"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -21783,8 +22060,9 @@
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P90" s="2"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -21800,8 +22078,9 @@
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P91" s="2"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -21817,8 +22096,9 @@
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P92" s="2"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -21834,8 +22114,9 @@
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P93" s="2"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -21851,8 +22132,9 @@
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P94" s="2"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -21868,8 +22150,9 @@
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P95" s="2"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -21885,8 +22168,9 @@
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P96" s="2"/>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -21902,8 +22186,9 @@
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P97" s="2"/>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -21919,8 +22204,9 @@
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P98" s="2"/>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -21936,8 +22222,9 @@
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P99" s="2"/>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -21953,8 +22240,9 @@
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P100" s="2"/>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -21970,8 +22258,9 @@
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P101" s="2"/>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -21987,8 +22276,9 @@
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P102" s="2"/>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -22004,8 +22294,9 @@
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P103" s="2"/>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -22021,8 +22312,9 @@
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P104" s="2"/>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -22038,8 +22330,9 @@
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P105" s="2"/>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -22055,8 +22348,9 @@
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P106" s="2"/>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -22072,8 +22366,9 @@
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P107" s="2"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -22089,8 +22384,9 @@
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P108" s="2"/>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -22106,8 +22402,9 @@
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P109" s="2"/>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -22123,8 +22420,9 @@
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P110" s="2"/>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -22140,8 +22438,9 @@
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P111" s="2"/>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -22157,8 +22456,9 @@
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P112" s="2"/>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -22174,8 +22474,9 @@
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P113" s="2"/>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -22191,8 +22492,9 @@
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P114" s="2"/>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -22208,8 +22510,9 @@
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P115" s="2"/>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -22225,8 +22528,9 @@
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P116" s="2"/>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -22242,8 +22546,9 @@
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P117" s="2"/>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -22259,8 +22564,9 @@
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P118" s="2"/>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -22276,8 +22582,9 @@
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P119" s="2"/>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -22293,8 +22600,9 @@
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P120" s="2"/>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -22310,8 +22618,9 @@
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P121" s="2"/>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -22327,8 +22636,9 @@
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P122" s="2"/>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -22344,8 +22654,9 @@
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P123" s="2"/>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -22361,8 +22672,9 @@
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P124" s="2"/>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -22378,8 +22690,9 @@
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P125" s="2"/>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -22395,8 +22708,9 @@
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P126" s="2"/>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -22412,8 +22726,9 @@
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P127" s="2"/>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -22429,8 +22744,9 @@
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P128" s="2"/>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -22446,8 +22762,9 @@
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P129" s="2"/>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -22463,8 +22780,9 @@
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P130" s="2"/>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -22480,8 +22798,9 @@
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P131" s="2"/>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -22497,8 +22816,9 @@
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P132" s="2"/>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -22514,8 +22834,9 @@
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P133" s="2"/>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -22531,8 +22852,9 @@
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P134" s="2"/>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -22548,8 +22870,9 @@
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P135" s="2"/>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -22565,8 +22888,9 @@
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P136" s="2"/>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -22582,8 +22906,9 @@
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P137" s="2"/>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -22599,8 +22924,9 @@
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P138" s="2"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -22616,8 +22942,9 @@
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P139" s="2"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -22633,8 +22960,9 @@
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P140" s="2"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -22650,8 +22978,9 @@
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P141" s="2"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -22667,8 +22996,9 @@
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P142" s="2"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -22684,8 +23014,9 @@
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P143" s="2"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -22701,8 +23032,9 @@
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P144" s="2"/>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -22718,8 +23050,9 @@
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P145" s="2"/>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -22735,8 +23068,9 @@
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P146" s="2"/>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -22752,8 +23086,9 @@
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P147" s="2"/>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -22769,8 +23104,9 @@
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P148" s="2"/>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -22786,8 +23122,9 @@
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P149" s="2"/>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -22803,8 +23140,9 @@
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P150" s="2"/>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -22820,8 +23158,9 @@
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P151" s="2"/>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -22837,8 +23176,9 @@
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P152" s="2"/>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -22854,8 +23194,9 @@
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P153" s="2"/>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -22871,8 +23212,9 @@
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P154" s="2"/>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -22888,8 +23230,9 @@
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P155" s="2"/>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -22905,8 +23248,9 @@
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P156" s="2"/>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -22922,8 +23266,9 @@
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P157" s="2"/>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -22939,8 +23284,9 @@
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P158" s="2"/>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -22956,8 +23302,9 @@
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P159" s="2"/>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -22973,8 +23320,9 @@
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P160" s="2"/>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -22990,8 +23338,9 @@
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P161" s="2"/>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -23007,8 +23356,9 @@
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P162" s="2"/>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -23024,8 +23374,9 @@
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P163" s="2"/>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -23041,8 +23392,9 @@
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P164" s="2"/>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -23058,8 +23410,9 @@
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P165" s="2"/>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -23075,8 +23428,9 @@
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P166" s="2"/>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -23092,8 +23446,9 @@
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P167" s="2"/>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -23109,8 +23464,9 @@
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P168" s="2"/>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -23126,8 +23482,9 @@
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P169" s="2"/>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -23143,8 +23500,9 @@
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P170" s="2"/>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -23160,8 +23518,9 @@
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P171" s="2"/>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -23177,8 +23536,9 @@
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P172" s="2"/>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -23194,8 +23554,9 @@
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P173" s="2"/>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -23211,8 +23572,9 @@
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P174" s="2"/>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -23228,8 +23590,9 @@
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P175" s="2"/>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -23245,8 +23608,9 @@
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P176" s="2"/>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -23262,8 +23626,9 @@
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P177" s="2"/>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -23279,8 +23644,9 @@
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P178" s="2"/>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -23296,8 +23662,9 @@
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P179" s="2"/>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -23313,8 +23680,9 @@
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P180" s="2"/>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -23330,8 +23698,9 @@
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P181" s="2"/>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -23347,8 +23716,9 @@
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P182" s="2"/>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -23364,8 +23734,9 @@
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P183" s="2"/>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -23381,8 +23752,9 @@
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P184" s="2"/>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -23398,8 +23770,9 @@
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P185" s="2"/>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -23415,8 +23788,9 @@
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P186" s="2"/>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -23432,8 +23806,9 @@
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P187" s="2"/>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -23449,8 +23824,9 @@
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P188" s="2"/>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -23466,8 +23842,9 @@
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P189" s="2"/>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -23483,8 +23860,9 @@
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P190" s="2"/>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -23500,8 +23878,9 @@
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P191" s="2"/>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -23517,8 +23896,9 @@
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P192" s="2"/>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -23534,8 +23914,9 @@
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P193" s="2"/>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -23551,8 +23932,9 @@
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P194" s="2"/>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -23568,8 +23950,9 @@
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P195" s="2"/>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -23585,8 +23968,9 @@
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P196" s="2"/>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -23602,8 +23986,9 @@
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P197" s="2"/>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -23619,8 +24004,9 @@
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P198" s="2"/>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -23636,8 +24022,9 @@
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P199" s="2"/>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -23653,8 +24040,9 @@
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P200" s="2"/>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -23670,8 +24058,9 @@
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P201" s="2"/>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -23687,8 +24076,9 @@
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P202" s="2"/>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -23704,8 +24094,9 @@
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P203" s="2"/>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -23721,42 +24112,45 @@
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
+      <c r="P204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="16">
+  <sheetProtection algorithmName="SHA-512" hashValue="bfwcZBaZ/SEpauMzvnRVd4A28z1cS1DkAIJnucm/zY9+/BV9GBCfb1hNoT3BC7EfOAKKln0AkgUeOJAdZmGg0A==" saltValue="vcjCV3XhbNlYrDAn3hdkSQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="17">
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:P4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4 I3:I4 J3:J4 H3:H4 N4" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 O4 H3:H4 J2:K2" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3:C4" r:id="rId1" location="countries" display="FLAG_OR_CHARTERING_CODE" xr:uid="{DA9CE3B1-74F9-4268-98AF-290FAC660EAD}"/>
+    <hyperlink ref="C3:C4" r:id="rId1" location="countries" display="FLAG_OR_CHARTERING_STATE" xr:uid="{DA9CE3B1-74F9-4268-98AF-290FAC660EAD}"/>
     <hyperlink ref="G3" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{4939BF01-E483-4611-A010-33B090D54E39}"/>
-    <hyperlink ref="I3" r:id="rId3" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{E9AF38ED-FD60-4672-8F14-35015A129362}"/>
-    <hyperlink ref="L4" r:id="rId4" location="countries" display="NATIONALITY_CODE" xr:uid="{10913ED0-4328-48D4-A042-6201D824CECA}"/>
-    <hyperlink ref="N4" r:id="rId5" location="countries" display="NATIONALITY_CODE" xr:uid="{3CF4C3FC-91EE-45A1-9C82-1871A741D19A}"/>
+    <hyperlink ref="J2" r:id="rId3" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{E9AF38ED-FD60-4672-8F14-35015A129362}"/>
+    <hyperlink ref="M4" r:id="rId4" location="countries" xr:uid="{10913ED0-4328-48D4-A042-6201D824CECA}"/>
+    <hyperlink ref="O4" r:id="rId5" location="countries" xr:uid="{3CF4C3FC-91EE-45A1-9C82-1871A741D19A}"/>
     <hyperlink ref="H3" r:id="rId6" display="PORT_CODE" xr:uid="{C4D05E8A-B26C-4196-BF44-6883318591EB}"/>
-    <hyperlink ref="I3:I4" r:id="rId7" location="targetSpecies" display="SPECIES_1" xr:uid="{0B822938-81D2-4E79-AA2B-FF0568175FC7}"/>
-    <hyperlink ref="J3:J4" r:id="rId8" location="gears" display="MAIN_FISHING_GEAR" xr:uid="{CCCFD829-5BF1-44B5-8500-349E2822309E}"/>
-    <hyperlink ref="H3:H4" r:id="rId9" location="Ports" display="PORT" xr:uid="{44C3BCF2-CCDC-4213-9DFE-452592BB90D5}"/>
+    <hyperlink ref="H3:H4" r:id="rId7" location="Ports" display="PORT" xr:uid="{44C3BCF2-CCDC-4213-9DFE-452592BB90D5}"/>
+    <hyperlink ref="G3:G4" r:id="rId8" location="countries" display="COUNTRY" xr:uid="{BD07189D-03AA-4AF5-B0D3-FF12F3E2E8CA}"/>
+    <hyperlink ref="J2:J4" r:id="rId9" location="targetSpecies" display="LICENSED_TARGET_SPECIES" xr:uid="{3E5E8972-E643-454E-9E2D-3185227AEE27}"/>
+    <hyperlink ref="K2:K4" r:id="rId10" location="gears" display="MAIN_FISHING_GEAR" xr:uid="{F9AD52CB-F3F1-40EF-8481-E96A756947D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23785,7 +24179,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -23799,73 +24193,73 @@
       <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>69</v>
+      <c r="A2" s="76" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="104" t="s">
-        <v>142</v>
+      <c r="B2" s="88" t="s">
+        <v>127</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104" t="s">
-        <v>143</v>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88" t="s">
+        <v>128</v>
       </c>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="84" t="s">
+      <c r="A3" s="82"/>
+      <c r="B3" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="95" t="s">
-        <v>56</v>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="76" t="s">
+        <v>55</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="G3" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="95" t="s">
-        <v>56</v>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="76" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
+      <c r="A4" s="77"/>
       <c r="B4" s="40" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="96"/>
+      <c r="F4" s="77"/>
       <c r="G4" s="40" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="H4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="45" t="s">
+      <c r="I4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="96"/>
+      <c r="K4" s="77"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -26468,7 +26862,7 @@
       <c r="K204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hbvz59o+k0C0Hv2oV09Yp7XAkMTBR+donU+qtEPDIB1sU7kBgfQMtgfOyOmvH5ZFdzL/TWJVxp4Q+WdslkFIFQ==" saltValue="No6gTqZaMMdNWS06APyBYg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:F2"/>
@@ -26484,8 +26878,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
-    <hyperlink ref="G4" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
+    <hyperlink ref="B4" r:id="rId1" location="countries" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
+    <hyperlink ref="G4" r:id="rId2" location="countries" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
     <hyperlink ref="C4" r:id="rId3" location="Ports" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
     <hyperlink ref="H4" r:id="rId4" location="Ports" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
   </hyperlinks>
@@ -26502,8 +26896,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="21.140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="3"/>
     <col min="6" max="6" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -26512,20 +26905,26 @@
     <col min="9" max="9" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="31.5703125" style="3" customWidth="1"/>
-    <col min="12" max="15" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="3" customWidth="1"/>
+    <col min="13" max="15" width="14.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" style="3" customWidth="1"/>
     <col min="19" max="19" width="9.140625" style="3"/>
-    <col min="20" max="20" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="9.140625" style="3"/>
+    <col min="20" max="20" width="9.85546875" style="3" customWidth="1"/>
+    <col min="21" max="21" width="7.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" style="3" customWidth="1"/>
+    <col min="23" max="23" width="7.42578125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" style="3" customWidth="1"/>
     <col min="25" max="25" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="9.140625" style="3"/>
     <col min="28" max="28" width="25.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" style="3"/>
+    <col min="29" max="29" width="7" style="3" customWidth="1"/>
     <col min="30" max="30" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.140625" style="3"/>
+    <col min="33" max="33" width="6.5703125" style="3" customWidth="1"/>
     <col min="34" max="34" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="36.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -26538,7 +26937,7 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -26582,238 +26981,238 @@
       <c r="AO1" s="7"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>69</v>
+      <c r="A2" s="76" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="84" t="s">
-        <v>171</v>
+      <c r="B2" s="79" t="s">
+        <v>156</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="86"/>
-      <c r="U2" s="84" t="s">
-        <v>170</v>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="79" t="s">
+        <v>155</v>
       </c>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="85"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
-      <c r="AE2" s="85"/>
-      <c r="AF2" s="85"/>
-      <c r="AG2" s="86"/>
-      <c r="AH2" s="84" t="s">
-        <v>157</v>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="81"/>
+      <c r="AH2" s="79" t="s">
+        <v>142</v>
       </c>
-      <c r="AI2" s="85"/>
-      <c r="AJ2" s="85"/>
-      <c r="AK2" s="85"/>
-      <c r="AL2" s="85"/>
-      <c r="AM2" s="85"/>
-      <c r="AN2" s="85"/>
-      <c r="AO2" s="86"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
+      <c r="AN2" s="80"/>
+      <c r="AO2" s="81"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="95" t="s">
-        <v>117</v>
+      <c r="A3" s="82"/>
+      <c r="B3" s="90" t="s">
+        <v>202</v>
       </c>
-      <c r="C3" s="107" t="s">
-        <v>118</v>
+      <c r="C3" s="100" t="s">
+        <v>203</v>
       </c>
-      <c r="D3" s="105" t="s">
+      <c r="D3" s="103" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="99" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="101" t="s">
+        <v>206</v>
+      </c>
+      <c r="L3" s="96" t="s">
+        <v>136</v>
+      </c>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="99" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="96" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" s="96"/>
+      <c r="U3" s="99" t="s">
+        <v>141</v>
+      </c>
+      <c r="V3" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="X3" s="99" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y3" s="99" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z3" s="99" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA3" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB3" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC3" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD3" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE3" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF3" s="99" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG3" s="99" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH3" s="96" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI3" s="96"/>
+      <c r="AJ3" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK3" s="96"/>
+      <c r="AL3" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM3" s="96"/>
+      <c r="AN3" s="96" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO3" s="96"/>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A4" s="77"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="120" t="s">
+        <v>204</v>
+      </c>
+      <c r="H4" s="120" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="120" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="120" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" s="102"/>
+      <c r="L4" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="N4" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="O4" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="P4" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q4" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="R4" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="S4" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="U4" s="99"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="99"/>
+      <c r="X4" s="99"/>
+      <c r="Y4" s="99"/>
+      <c r="Z4" s="99"/>
+      <c r="AA4" s="99"/>
+      <c r="AB4" s="99"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="99"/>
+      <c r="AE4" s="99"/>
+      <c r="AF4" s="99"/>
+      <c r="AG4" s="99"/>
+      <c r="AH4" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI4" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="AJ4" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104" t="s">
+      <c r="AK4" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="108" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="101" t="s">
-        <v>151</v>
-      </c>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="104" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="104"/>
-      <c r="S3" s="101" t="s">
-        <v>22</v>
-      </c>
-      <c r="T3" s="101"/>
-      <c r="U3" s="104" t="s">
-        <v>156</v>
-      </c>
-      <c r="V3" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="W3" s="104" t="s">
-        <v>34</v>
-      </c>
-      <c r="X3" s="104" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y3" s="104" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z3" s="104" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA3" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB3" s="104" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC3" s="104" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD3" s="104" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE3" s="104" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF3" s="104" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG3" s="104" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH3" s="101" t="s">
-        <v>166</v>
-      </c>
-      <c r="AI3" s="101"/>
-      <c r="AJ3" s="101" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK3" s="101"/>
-      <c r="AL3" s="101" t="s">
-        <v>168</v>
-      </c>
-      <c r="AM3" s="101"/>
-      <c r="AN3" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO3" s="101"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" s="109"/>
-      <c r="L4" s="40" t="s">
+      <c r="AL4" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="AM4" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="N4" s="40" t="s">
+      <c r="AN4" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="O4" s="40" t="s">
+      <c r="AO4" s="43" t="s">
         <v>150</v>
-      </c>
-      <c r="P4" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q4" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="R4" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="S4" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="T4" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="U4" s="104"/>
-      <c r="V4" s="104"/>
-      <c r="W4" s="104"/>
-      <c r="X4" s="104"/>
-      <c r="Y4" s="104"/>
-      <c r="Z4" s="104"/>
-      <c r="AA4" s="104"/>
-      <c r="AB4" s="104"/>
-      <c r="AC4" s="104"/>
-      <c r="AD4" s="104"/>
-      <c r="AE4" s="104"/>
-      <c r="AF4" s="104"/>
-      <c r="AG4" s="104"/>
-      <c r="AH4" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI4" s="44" t="s">
-        <v>159</v>
-      </c>
-      <c r="AJ4" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="AK4" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL4" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="AM4" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="AN4" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="AO4" s="44" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
@@ -35417,8 +35816,22 @@
       <c r="AO204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JacJblqysVn4VlodL3cUZIOB9Nry7+tfevwii5NIAWEA2sxBjghxk+OgRjF/SuUA1DLt+bB7HT5LyH8oN4ka6Q==" saltValue="mhMw97y/oUl8/Qxr6rgwXQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="X3:X4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="U2:AG2"/>
@@ -35435,20 +35848,6 @@
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="AN3:AO3"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="AL3:AM3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN4 D3:D4 L4 M4 N4 O4 P4 Q4 R4 AH4 AI4 AJ4 AK4 AL4 AM4 AO4" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35456,19 +35855,19 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D3:D4" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL_CODE" xr:uid="{67410786-49B8-4FAC-82C7-693110607986}"/>
-    <hyperlink ref="L4" r:id="rId2" location="fishPreservationMethods" display="METHOD_1_CODE" xr:uid="{1302D005-C0D4-48F4-9067-8DB21E13C99E}"/>
+    <hyperlink ref="D3:D4" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL" xr:uid="{67410786-49B8-4FAC-82C7-693110607986}"/>
+    <hyperlink ref="L4" r:id="rId2" location="fishPreservationMethods" xr:uid="{1302D005-C0D4-48F4-9067-8DB21E13C99E}"/>
     <hyperlink ref="M4" r:id="rId3" location="fishPreservationMethods" display="METHOD_2_CODE" xr:uid="{EEBE083B-4312-4FA4-A951-C9F9A824B321}"/>
     <hyperlink ref="N4" r:id="rId4" location="fishPreservationMethods" display="METHOD_3_CODE" xr:uid="{30064C75-6784-480A-88EC-D543ED3C0DC7}"/>
     <hyperlink ref="O4" r:id="rId5" location="fishPreservationMethods" display="METHOD_4_CODE" xr:uid="{57D15D5E-41AB-40B4-A2E0-8E05FF890560}"/>
-    <hyperlink ref="P4" r:id="rId6" location="fishStorageTypes" display="TYPE_1_CODE" xr:uid="{632D3564-65D3-45E5-BF57-3CF8FD5ACBAF}"/>
+    <hyperlink ref="P4" r:id="rId6" location="fishStorageTypes" xr:uid="{632D3564-65D3-45E5-BF57-3CF8FD5ACBAF}"/>
     <hyperlink ref="Q4" r:id="rId7" location="fishStorageTypes" display="TYPE_2_CODE" xr:uid="{BB5616AB-C383-462B-A9E4-AB799B92F802}"/>
     <hyperlink ref="R4" r:id="rId8" location="fishStorageTypes" display="TYPE_3_CODE" xr:uid="{94329445-F648-4E10-BD21-D3B467B1D303}"/>
-    <hyperlink ref="AH4" r:id="rId9" location="wasteManagementCategories" display="CATEGORY_1_CODE" xr:uid="{8F0155CB-37EC-4CEC-9EB0-B85C65274EA0}"/>
+    <hyperlink ref="AH4" r:id="rId9" location="wasteManagementCategories" xr:uid="{8F0155CB-37EC-4CEC-9EB0-B85C65274EA0}"/>
     <hyperlink ref="AJ4" r:id="rId10" location="wasteManagementCategories" display="CATEGORY_2_CODE" xr:uid="{4AA42787-D2A9-4627-B1FB-A30392A207EB}"/>
     <hyperlink ref="AL4" r:id="rId11" location="wasteManagementCategories" display="CATEGORY_3_CODE" xr:uid="{1E0ACA01-E9CF-41A3-B227-90B65C435EBC}"/>
     <hyperlink ref="AN4" r:id="rId12" location="wasteManagementCategories" display="CATEGORY_4_CODE" xr:uid="{80DD5EEA-21EE-47E6-8164-69AF6D6A721F}"/>
-    <hyperlink ref="AI4" r:id="rId13" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_1_CODE" xr:uid="{734552DB-2913-470A-98E7-9E5085684410}"/>
+    <hyperlink ref="AI4" r:id="rId13" location="wasteDisposalMethods" xr:uid="{734552DB-2913-470A-98E7-9E5085684410}"/>
     <hyperlink ref="AK4" r:id="rId14" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_2_CODE" xr:uid="{435FF06B-B974-4B37-BA60-C79659E1631E}"/>
     <hyperlink ref="AM4" r:id="rId15" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_3_CODE" xr:uid="{B45A5879-026B-4247-B2B8-15EF712B3716}"/>
     <hyperlink ref="AO4" r:id="rId16" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_4_CODE" xr:uid="{5B7BDC52-01F7-456B-A7FF-5F257DD246CF}"/>
@@ -35494,7 +35893,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="7"/>
@@ -35509,101 +35908,101 @@
       <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>69</v>
+      <c r="A2" s="76" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="84" t="s">
-        <v>172</v>
+      <c r="B2" s="79" t="s">
+        <v>157</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="84" t="s">
-        <v>173</v>
+      <c r="C2" s="81"/>
+      <c r="D2" s="79" t="s">
+        <v>158</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="86"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="101" t="s">
-        <v>75</v>
+      <c r="A3" s="82"/>
+      <c r="B3" s="96" t="s">
+        <v>70</v>
       </c>
-      <c r="C3" s="101" t="s">
-        <v>76</v>
+      <c r="C3" s="96" t="s">
+        <v>71</v>
       </c>
-      <c r="D3" s="101" t="s">
-        <v>77</v>
+      <c r="D3" s="96" t="s">
+        <v>72</v>
       </c>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101" t="s">
-        <v>174</v>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96" t="s">
+        <v>159</v>
       </c>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101" t="s">
-        <v>175</v>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101" t="s">
-        <v>179</v>
+      <c r="A4" s="82"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96" t="s">
+        <v>164</v>
       </c>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101" t="s">
-        <v>178</v>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96" t="s">
+        <v>163</v>
       </c>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101" t="s">
-        <v>177</v>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96" t="s">
+        <v>162</v>
       </c>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101" t="s">
-        <v>176</v>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96" t="s">
+        <v>161</v>
       </c>
-      <c r="K4" s="101"/>
-      <c r="L4" s="101"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="82"/>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="45" t="s">
+      <c r="A5" s="77"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="56" t="s">
-        <v>78</v>
+      <c r="E5" s="51" t="s">
+        <v>205</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="56" t="s">
-        <v>78</v>
+      <c r="G5" s="51" t="s">
+        <v>205</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="56" t="s">
-        <v>79</v>
+      <c r="I5" s="51" t="s">
+        <v>205</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="56" t="s">
-        <v>79</v>
+      <c r="K5" s="51" t="s">
+        <v>205</v>
       </c>
-      <c r="L5" s="45" t="s">
-        <v>80</v>
+      <c r="L5" s="44" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -38407,7 +38806,7 @@
       <c r="L205" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OIA2juXsQVr9S2oP2mybawOifHzCkVXtWAdDfZJ2K3RMDe4SYTT0Jit/7m2eczthvGnOsPbITjE52MRfvCrPMA==" saltValue="DWrHcNm1oKnbWvyYitlxgA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="D2:L2"/>
     <mergeCell ref="A2:A5"/>
@@ -38454,7 +38853,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -38479,133 +38878,133 @@
       <c r="V1" s="7"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>69</v>
+      <c r="A2" s="76" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>71</v>
+      <c r="B2" s="76" t="s">
+        <v>66</v>
       </c>
-      <c r="C2" s="77" t="s">
-        <v>180</v>
+      <c r="C2" s="72" t="s">
+        <v>165</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="107" t="s">
-        <v>181</v>
+      <c r="D2" s="73"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="100" t="s">
+        <v>166</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="102" t="s">
-        <v>98</v>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="97" t="s">
+        <v>89</v>
       </c>
-      <c r="K2" s="113" t="s">
-        <v>186</v>
+      <c r="K2" s="108" t="s">
+        <v>171</v>
       </c>
-      <c r="L2" s="101" t="s">
-        <v>82</v>
+      <c r="L2" s="96" t="s">
+        <v>75</v>
       </c>
-      <c r="M2" s="94" t="s">
-        <v>83</v>
+      <c r="M2" s="89" t="s">
+        <v>76</v>
       </c>
-      <c r="N2" s="101" t="s">
-        <v>84</v>
+      <c r="N2" s="96" t="s">
+        <v>77</v>
       </c>
-      <c r="O2" s="84"/>
-      <c r="P2" s="81" t="s">
-        <v>85</v>
+      <c r="O2" s="79"/>
+      <c r="P2" s="76" t="s">
+        <v>78</v>
       </c>
-      <c r="Q2" s="86" t="s">
-        <v>86</v>
+      <c r="Q2" s="81" t="s">
+        <v>79</v>
       </c>
-      <c r="R2" s="110" t="s">
-        <v>187</v>
+      <c r="R2" s="96" t="s">
+        <v>172</v>
       </c>
-      <c r="S2" s="110"/>
-      <c r="T2" s="110"/>
-      <c r="U2" s="110"/>
-      <c r="V2" s="110"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="115" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="77" t="s">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="83"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="94" t="s">
-        <v>87</v>
+      <c r="D3" s="72" t="s">
+        <v>54</v>
       </c>
-      <c r="S3" s="101" t="s">
-        <v>188</v>
+      <c r="E3" s="78"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="99" t="s">
+        <v>80</v>
       </c>
-      <c r="T3" s="101"/>
-      <c r="U3" s="101" t="s">
-        <v>189</v>
+      <c r="S3" s="96" t="s">
+        <v>173</v>
       </c>
-      <c r="V3" s="101"/>
+      <c r="T3" s="96"/>
+      <c r="U3" s="96" t="s">
+        <v>174</v>
+      </c>
+      <c r="V3" s="96"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="42" t="s">
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="41" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
-      <c r="I4" s="60" t="s">
-        <v>185</v>
+      <c r="I4" s="54" t="s">
+        <v>170</v>
       </c>
-      <c r="J4" s="103"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="49" t="s">
-        <v>88</v>
+      <c r="J4" s="98"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="46" t="s">
+        <v>81</v>
       </c>
-      <c r="O4" s="59" t="s">
-        <v>89</v>
+      <c r="O4" s="53" t="s">
+        <v>82</v>
       </c>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="53" t="s">
-        <v>90</v>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="50" t="s">
+        <v>83</v>
       </c>
-      <c r="T4" s="53" t="s">
-        <v>91</v>
+      <c r="T4" s="50" t="s">
+        <v>84</v>
       </c>
-      <c r="U4" s="44" t="s">
-        <v>190</v>
+      <c r="U4" s="43" t="s">
+        <v>175</v>
       </c>
-      <c r="V4" s="44" t="s">
-        <v>191</v>
+      <c r="V4" s="43" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -43409,14 +43808,9 @@
       <c r="V204" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HegNjEUG0JGCK7Em0JYKFfbaDXofSI/eoHWk8rSNZhCuxxgrRfFxzqmKDw+rgM8g2AEjX7hW0V65tqpclq3eIA==" saltValue="dNae070C6OTNQ7yDYKjQHg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:T3"/>
@@ -43429,6 +43823,11 @@
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="P2:P4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 I4 F4 G4 H4 U4 V4" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -43436,13 +43835,13 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" location="schoolSightingCues" display="CUE_1_CODE" xr:uid="{06828AB2-F8FD-4727-81EB-1B9C3E1606EA}"/>
+    <hyperlink ref="F4" r:id="rId1" location="schoolSightingCues" xr:uid="{06828AB2-F8FD-4727-81EB-1B9C3E1606EA}"/>
     <hyperlink ref="G4" r:id="rId2" location="schoolSightingCues" display="CUE_2_CODE" xr:uid="{088A8BB6-B9F0-4388-804D-7EE868064B75}"/>
     <hyperlink ref="H4" r:id="rId3" location="schoolSightingCues" display="CUE_3_CODE" xr:uid="{B514EC62-1682-489E-80EC-DDD4C9F7091B}"/>
     <hyperlink ref="I4" r:id="rId4" location="schoolSightingCues" display="CUE_4_CODE" xr:uid="{9761634D-193D-4BB7-9DBB-2E57BEE8C3AD}"/>
-    <hyperlink ref="K2:K4" r:id="rId5" location="schoolDetectionMethods" display="FIRST_DETECTION_METHOD_CODE" xr:uid="{53EDB860-963D-4D65-B421-454C98452ABF}"/>
-    <hyperlink ref="V4" r:id="rId6" location="FADtailDesigns" display="TAIL_DESIGN_CODE" xr:uid="{4EC548E9-585E-4A0F-8A11-B2D8DE7871DC}"/>
-    <hyperlink ref="U4" r:id="rId7" location="FADraftDesigns" display="RAFT_DESIGN_CODE" xr:uid="{56C6FE4F-AE5D-4D49-879C-6D4A0BF75DFF}"/>
+    <hyperlink ref="K2:K4" r:id="rId5" location="schoolDetectionMethods" display="FIRST_DETECTION_METHOD" xr:uid="{53EDB860-963D-4D65-B421-454C98452ABF}"/>
+    <hyperlink ref="V4" r:id="rId6" location="FADtailDesigns" xr:uid="{4EC548E9-585E-4A0F-8A11-B2D8DE7871DC}"/>
+    <hyperlink ref="U4" r:id="rId7" location="FADraftDesigns" xr:uid="{56C6FE4F-AE5D-4D49-879C-6D4A0BF75DFF}"/>
     <hyperlink ref="J2:J4" r:id="rId8" location="schoolTypeCategories" display="SCHOOL_TYPES" xr:uid="{8EC575CB-432D-43D0-8C91-3FACD4044FFB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -43466,33 +43865,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
-        <v>92</v>
+      <c r="A1" s="110" t="s">
+        <v>207</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
-        <v>69</v>
+      <c r="A2" s="41" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="42" t="s">
-        <v>71</v>
+      <c r="B2" s="41" t="s">
+        <v>66</v>
       </c>
-      <c r="C2" s="42" t="s">
-        <v>93</v>
+      <c r="C2" s="41" t="s">
+        <v>85</v>
       </c>
-      <c r="D2" s="46" t="s">
-        <v>192</v>
+      <c r="D2" s="45" t="s">
+        <v>177</v>
       </c>
-      <c r="E2" s="42" t="s">
-        <v>94</v>
+      <c r="E2" s="41" t="s">
+        <v>208</v>
       </c>
-      <c r="F2" s="42" t="s">
-        <v>95</v>
+      <c r="F2" s="41" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -45096,7 +45495,7 @@
       <c r="F202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kviV1SZRnQko8ezco/44rWDpyPVJvrbA6GYXl6ikqHqao1OSEmfHNyEdJQTk0awshCQvmkR1NuK7VUgYncNMcQ==" saltValue="h3WPTOpyhj/BFNU0j0oJPA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -45106,7 +45505,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" location="cetaceansAndWhaleSharks" display="SPECIES_CODE" xr:uid="{F9440529-0B3C-4E2C-9C30-02C136FF531F}"/>
+    <hyperlink ref="D2" r:id="rId1" location="cetaceansAndWhaleSharks" xr:uid="{F9440529-0B3C-4E2C-9C30-02C136FF531F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45135,7 +45534,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -45150,59 +45549,59 @@
       <c r="L1" s="8"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>69</v>
+      <c r="A2" s="76" t="s">
+        <v>65</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>71</v>
+      <c r="B2" s="76" t="s">
+        <v>66</v>
       </c>
-      <c r="C2" s="81" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="102" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" s="117" t="s">
+      <c r="C2" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="118"/>
-      <c r="G2" s="102" t="s">
-        <v>194</v>
+      <c r="D2" s="97" t="s">
+        <v>177</v>
       </c>
-      <c r="H2" s="81" t="s">
-        <v>193</v>
+      <c r="E2" s="111" t="s">
+        <v>63</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="F2" s="112"/>
+      <c r="G2" s="97" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="76" t="s">
+        <v>178</v>
+      </c>
+      <c r="I2" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="83"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="52" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="52" t="s">
-        <v>66</v>
+      <c r="F3" s="49" t="s">
+        <v>62</v>
       </c>
-      <c r="G3" s="103"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="52" t="s">
-        <v>195</v>
+      <c r="G3" s="98"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="49" t="s">
+        <v>180</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="61" t="s">
-        <v>64</v>
+      <c r="K3" s="55" t="s">
+        <v>205</v>
       </c>
-      <c r="L3" s="52" t="s">
-        <v>196</v>
+      <c r="L3" s="49" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -48006,7 +48405,7 @@
       <c r="L203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UKy/9FtM0qE00vQznJsrAB6qNs4GW8BQPbqIcWB/O1BV/Zo2g6FqcmjtYLjBLHAOlTWuzmOBMkW75s7THcQJ1g==" saltValue="oLVNnQ9vZNGxIvvoNMp/5A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="I2:L2"/>
     <mergeCell ref="D2:D3"/>
@@ -48023,8 +48422,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{779410D5-0433-4C34-84B6-98A10CA2B249}"/>
-    <hyperlink ref="L3" r:id="rId2" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{EB80831C-DDCE-4E4D-A605-160D23E19E90}"/>
+    <hyperlink ref="I3" r:id="rId1" location="fishProcessingTypes" xr:uid="{779410D5-0433-4C34-84B6-98A10CA2B249}"/>
+    <hyperlink ref="L3" r:id="rId2" location="weightEstimationMethods" xr:uid="{EB80831C-DDCE-4E4D-A605-160D23E19E90}"/>
     <hyperlink ref="E3" r:id="rId3" location="typesOfFate" xr:uid="{F8152E0B-B9D5-4E81-A374-4985E0AF2D58}"/>
     <hyperlink ref="F3" r:id="rId4" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
     <hyperlink ref="D2:D3" r:id="rId5" location="allSpecies" display="SPECIES" xr:uid="{6CBAC676-A508-4773-8413-1235C4C5E5A3}"/>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B3E72E-1566-43C2-8877-CBC356D750BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363D2B9D-778B-46AB-A30B-0DD6DF30AD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28920" yWindow="450" windowWidth="27705" windowHeight="15090" tabRatio="879" firstSheet="2" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -530,19 +530,10 @@
     <t>MESH SIZE</t>
   </si>
   <si>
-    <t>MAX BRAIL CAPACITY</t>
-  </si>
-  <si>
     <t>MID NET STRETCHED</t>
   </si>
   <si>
     <t>BUNT STRETCHED</t>
-  </si>
-  <si>
-    <t>MAX DEPTH</t>
-  </si>
-  <si>
-    <t>MAX LENGTH</t>
   </si>
   <si>
     <t>START SETTING</t>
@@ -678,6 +669,15 @@
   </si>
   <si>
     <t>DESTINATION</t>
+  </si>
+  <si>
+    <t>MAXIMUM LENGTH</t>
+  </si>
+  <si>
+    <t>MAXIMUM DEPTH</t>
+  </si>
+  <si>
+    <t>MAXIMUM BRAIL CAPACITY</t>
   </si>
 </sst>
 </file>
@@ -1198,6 +1198,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1270,14 +1273,49 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1319,14 +1357,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1339,17 +1369,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1360,9 +1379,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1379,26 +1397,8 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1737,24 +1737,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="15"/>
@@ -1804,15 +1804,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="21"/>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="65"/>
+      <c r="D8" s="66"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="65" t="s">
+      <c r="F8" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="65"/>
+      <c r="G8" s="66"/>
       <c r="H8" s="23"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1994,11 +1994,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="21"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="68"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="69"/>
       <c r="H26" s="23"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2098,61 +2098,61 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="113" t="s">
+      <c r="C2" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="113" t="s">
+      <c r="D2" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="97" t="s">
-        <v>179</v>
+      <c r="E2" s="91" t="s">
+        <v>176</v>
       </c>
-      <c r="F2" s="88" t="s">
-        <v>188</v>
+      <c r="F2" s="98" t="s">
+        <v>185</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="99" t="s">
-        <v>189</v>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="107" t="s">
+        <v>186</v>
       </c>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99" t="s">
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="103" t="s">
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="79" t="s">
+      <c r="R2" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="81"/>
-      <c r="T2" s="79" t="s">
-        <v>187</v>
+      <c r="S2" s="82"/>
+      <c r="T2" s="80" t="s">
+        <v>184</v>
       </c>
-      <c r="U2" s="80"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="96" t="s">
-        <v>186</v>
+      <c r="U2" s="81"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="106" t="s">
+        <v>183</v>
       </c>
-      <c r="X2" s="96"/>
+      <c r="X2" s="106"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="114"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="98"/>
+      <c r="A3" s="119"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="93"/>
       <c r="F3" s="45" t="s">
         <v>19</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>37</v>
       </c>
       <c r="H3" s="45" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I3" s="41" t="s">
         <v>47</v>
@@ -2172,21 +2172,21 @@
         <v>37</v>
       </c>
       <c r="L3" s="40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>47</v>
       </c>
       <c r="N3" s="40" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="O3" s="44" t="s">
         <v>36</v>
       </c>
       <c r="P3" s="56" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
-      <c r="Q3" s="104"/>
+      <c r="Q3" s="90"/>
       <c r="R3" s="47" t="s">
         <v>59</v>
       </c>
@@ -2200,13 +2200,13 @@
         <v>39</v>
       </c>
       <c r="V3" s="44" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="W3" s="40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="X3" s="40" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -7472,7 +7472,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -7488,61 +7488,61 @@
       <c r="M1" s="14"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="113" t="s">
+      <c r="C2" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="113" t="s">
+      <c r="D2" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="103" t="s">
+      <c r="E2" s="88" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" s="88" t="s">
+        <v>189</v>
+      </c>
+      <c r="G2" s="88" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="89" t="s">
         <v>191</v>
       </c>
-      <c r="F2" s="103" t="s">
-        <v>192</v>
-      </c>
-      <c r="G2" s="103" t="s">
-        <v>193</v>
-      </c>
-      <c r="H2" s="116" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="115" t="s">
-        <v>194</v>
-      </c>
-      <c r="J2" s="116" t="s">
+      <c r="J2" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="116" t="s">
+      <c r="K2" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="91" t="s">
-        <v>186</v>
+      <c r="L2" s="101" t="s">
+        <v>183</v>
       </c>
-      <c r="M2" s="91"/>
+      <c r="M2" s="101"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="114"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
+      <c r="A3" s="119"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
       <c r="L3" s="40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M3" s="40" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -10548,11 +10548,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="BGDYvh08S3NYZIuspsRRCAicI1Gp8B4hCVX6TD3PYP3B6k2058cKh0vrrp9OQ+vPcDsnDczSdbeeSJcJFOUPXA==" saltValue="U5shOM/WfotH/IVdI6hz3g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="E2:E3"/>
@@ -10560,6 +10555,11 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H2:H3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 G2:G3 I2:I3 E2:E3 L3 M3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -10640,10 +10640,10 @@
         <v>43</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -13278,7 +13278,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -13300,7 +13300,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F2" s="50" t="s">
         <v>91</v>
@@ -14980,117 +14980,117 @@
       <c r="X1" s="8"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69" t="s">
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="69"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="72" t="s">
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="72" t="s">
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69"/>
-      <c r="V3" s="69"/>
-      <c r="W3" s="69"/>
-      <c r="X3" s="69"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="70"/>
+      <c r="U3" s="70"/>
+      <c r="V3" s="70"/>
+      <c r="W3" s="70"/>
+      <c r="X3" s="70"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="69"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="70" t="s">
+      <c r="A4" s="70"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="71"/>
-      <c r="F4" s="70" t="s">
+      <c r="E4" s="72"/>
+      <c r="F4" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="71"/>
-      <c r="H4" s="76" t="s">
+      <c r="G4" s="72"/>
+      <c r="H4" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="74" t="s">
+      <c r="I4" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="J4" s="75"/>
-      <c r="K4" s="70" t="s">
+      <c r="J4" s="76"/>
+      <c r="K4" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="L4" s="71"/>
-      <c r="M4" s="76" t="s">
+      <c r="L4" s="72"/>
+      <c r="M4" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="N4" s="69" t="s">
+      <c r="N4" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69" t="s">
+      <c r="O4" s="70"/>
+      <c r="P4" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="79" t="s">
+      <c r="Q4" s="70"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="70"/>
+      <c r="T4" s="70"/>
+      <c r="U4" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="V4" s="80"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="81"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="82"/>
     </row>
     <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="69"/>
+      <c r="A5" s="70"/>
       <c r="B5" s="41" t="s">
         <v>92</v>
       </c>
@@ -15109,7 +15109,7 @@
       <c r="G5" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="77"/>
+      <c r="H5" s="78"/>
       <c r="I5" s="40" t="s">
         <v>114</v>
       </c>
@@ -15122,7 +15122,7 @@
       <c r="L5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="77"/>
+      <c r="M5" s="78"/>
       <c r="N5" s="41" t="s">
         <v>5</v>
       </c>
@@ -20334,7 +20334,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RdNrOAn/lQMbMlrvotSd6e7DAP6LRqnMQsSQdK2ijNoYLV6uZuPnsrPuGGdEV+gbuZ9hwJUmPp3VbLE6xYZ72A==" saltValue="8ZiNB57QGOGYw7UGazEnig==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kuraIphfBcjZ2nHiigUoBx9E5Jz+h7+0bz47tq+vlXnhlBdiMjPoHdZkgU9MsIUPHl1S+9z35QqCZfKvYAu2VA==" saltValue="iN+qBwmj3LDfsG6tTAfGtg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -20419,87 +20419,87 @@
       <c r="P1" s="8"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="87"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
       <c r="G2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="117"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="103" t="s">
-        <v>201</v>
+      <c r="H2" s="84"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="88" t="s">
+        <v>198</v>
       </c>
-      <c r="K2" s="97" t="s">
+      <c r="K2" s="91" t="s">
         <v>123</v>
       </c>
-      <c r="L2" s="85" t="s">
+      <c r="L2" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="87"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="97"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="69" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="95" t="s">
-        <v>199</v>
+      <c r="C3" s="105" t="s">
+        <v>196</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="90" t="s">
+      <c r="E3" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="96" t="s">
+      <c r="F3" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="92" t="s">
+      <c r="G3" s="102" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="118" t="s">
-        <v>200</v>
+      <c r="I3" s="86" t="s">
+        <v>197</v>
       </c>
-      <c r="J3" s="115"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="88" t="s">
+      <c r="J3" s="89"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="98" t="s">
         <v>124</v>
       </c>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88" t="s">
+      <c r="M3" s="98"/>
+      <c r="N3" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="88"/>
-      <c r="P3" s="89" t="s">
+      <c r="O3" s="98"/>
+      <c r="P3" s="99" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="77"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="98"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="93"/>
       <c r="L4" s="41" t="s">
         <v>3</v>
       </c>
@@ -20512,7 +20512,7 @@
       <c r="O4" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="P4" s="89"/>
+      <c r="P4" s="99"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -24115,13 +24115,8 @@
       <c r="P204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bfwcZBaZ/SEpauMzvnRVd4A28z1cS1DkAIJnucm/zY9+/BV9GBCfb1hNoT3BC7EfOAKKln0AkgUeOJAdZmGg0A==" saltValue="vcjCV3XhbNlYrDAn3hdkSQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="O3vPd5vM4N/Qh7B6qHZd426iarnVuOzAMFoRd4rVrG3TYR7D813UKsBbjt/FHVt++j2pUvdy4VeHDazqXO/KsQ==" saltValue="x4iNhhhTzYRRYu28b3Rbjw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="A2:A4"/>
     <mergeCell ref="L2:P2"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="P3:P4"/>
@@ -24134,6 +24129,11 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 O4 H3:H4 J2:K2" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -24193,47 +24193,47 @@
       <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88" t="s">
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="72" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="76" t="s">
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="76" t="s">
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="77" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="77"/>
+      <c r="A4" s="78"/>
       <c r="B4" s="40" t="s">
         <v>114</v>
       </c>
@@ -24246,7 +24246,7 @@
       <c r="E4" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="77"/>
+      <c r="F4" s="78"/>
       <c r="G4" s="40" t="s">
         <v>114</v>
       </c>
@@ -24259,7 +24259,7 @@
       <c r="J4" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="77"/>
+      <c r="K4" s="78"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -26981,175 +26981,175 @@
       <c r="AO1" s="7"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="79" t="s">
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="82"/>
+      <c r="U2" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="81"/>
-      <c r="AH2" s="79" t="s">
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="81"/>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="81"/>
+      <c r="AE2" s="81"/>
+      <c r="AF2" s="81"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="AI2" s="80"/>
-      <c r="AJ2" s="80"/>
-      <c r="AK2" s="80"/>
-      <c r="AL2" s="80"/>
-      <c r="AM2" s="80"/>
-      <c r="AN2" s="80"/>
-      <c r="AO2" s="81"/>
+      <c r="AI2" s="81"/>
+      <c r="AJ2" s="81"/>
+      <c r="AK2" s="81"/>
+      <c r="AL2" s="81"/>
+      <c r="AM2" s="81"/>
+      <c r="AN2" s="81"/>
+      <c r="AO2" s="82"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="90" t="s">
-        <v>202</v>
+      <c r="A3" s="94"/>
+      <c r="B3" s="100" t="s">
+        <v>199</v>
       </c>
-      <c r="C3" s="100" t="s">
+      <c r="C3" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="109" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="103" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="99" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99" t="s">
-        <v>131</v>
-      </c>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="101" t="s">
-        <v>206</v>
-      </c>
-      <c r="L3" s="96" t="s">
+      <c r="L3" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="99" t="s">
+      <c r="M3" s="106"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="106"/>
+      <c r="P3" s="107" t="s">
         <v>137</v>
       </c>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="96" t="s">
+      <c r="Q3" s="107"/>
+      <c r="R3" s="107"/>
+      <c r="S3" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="96"/>
-      <c r="U3" s="99" t="s">
+      <c r="T3" s="106"/>
+      <c r="U3" s="107" t="s">
         <v>141</v>
       </c>
-      <c r="V3" s="99" t="s">
+      <c r="V3" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="W3" s="99" t="s">
+      <c r="W3" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="X3" s="99" t="s">
+      <c r="X3" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" s="99" t="s">
+      <c r="Y3" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Z3" s="99" t="s">
+      <c r="Z3" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="AA3" s="99" t="s">
+      <c r="AA3" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="AB3" s="99" t="s">
+      <c r="AB3" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="AC3" s="99" t="s">
+      <c r="AC3" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="AD3" s="99" t="s">
+      <c r="AD3" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="AE3" s="99" t="s">
+      <c r="AE3" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AF3" s="99" t="s">
+      <c r="AF3" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="AG3" s="99" t="s">
+      <c r="AG3" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="AH3" s="96" t="s">
+      <c r="AH3" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="AI3" s="96"/>
-      <c r="AJ3" s="96" t="s">
+      <c r="AI3" s="106"/>
+      <c r="AJ3" s="106" t="s">
         <v>152</v>
       </c>
-      <c r="AK3" s="96"/>
-      <c r="AL3" s="96" t="s">
+      <c r="AK3" s="106"/>
+      <c r="AL3" s="106" t="s">
         <v>153</v>
       </c>
-      <c r="AM3" s="96"/>
-      <c r="AN3" s="96" t="s">
+      <c r="AM3" s="106"/>
+      <c r="AN3" s="106" t="s">
         <v>154</v>
       </c>
-      <c r="AO3" s="96"/>
+      <c r="AO3" s="106"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="77"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="104"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="90"/>
       <c r="E4" s="50" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="120" t="s">
-        <v>204</v>
+      <c r="G4" s="59" t="s">
+        <v>201</v>
       </c>
-      <c r="H4" s="120" t="s">
+      <c r="H4" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="120" t="s">
+      <c r="I4" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="120" t="s">
-        <v>204</v>
+      <c r="J4" s="59" t="s">
+        <v>201</v>
       </c>
-      <c r="K4" s="102"/>
+      <c r="K4" s="110"/>
       <c r="L4" s="40" t="s">
         <v>132</v>
       </c>
@@ -27175,21 +27175,21 @@
         <v>18</v>
       </c>
       <c r="T4" s="51" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="99"/>
-      <c r="X4" s="99"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="99"/>
-      <c r="AA4" s="99"/>
-      <c r="AB4" s="99"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="99"/>
-      <c r="AE4" s="99"/>
-      <c r="AF4" s="99"/>
-      <c r="AG4" s="99"/>
+      <c r="U4" s="107"/>
+      <c r="V4" s="107"/>
+      <c r="W4" s="107"/>
+      <c r="X4" s="107"/>
+      <c r="Y4" s="107"/>
+      <c r="Z4" s="107"/>
+      <c r="AA4" s="107"/>
+      <c r="AB4" s="107"/>
+      <c r="AC4" s="107"/>
+      <c r="AD4" s="107"/>
+      <c r="AE4" s="107"/>
+      <c r="AF4" s="107"/>
+      <c r="AG4" s="107"/>
       <c r="AH4" s="52" t="s">
         <v>143</v>
       </c>
@@ -35816,22 +35816,8 @@
       <c r="AO204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JacJblqysVn4VlodL3cUZIOB9Nry7+tfevwii5NIAWEA2sxBjghxk+OgRjF/SuUA1DLt+bB7HT5LyH8oN4ka6Q==" saltValue="mhMw97y/oUl8/Qxr6rgwXQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QEQd2x0BKHbPsCCaNKPWr4HTNrPyaNjaEkhTFqmOR7qEW7lhdXdsDzn/18LwB+BtaIdU1miotO/Ku4vF690czA==" saltValue="EPC4iVtkM6J5UbKwOSWluA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="X3:X4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="U2:AG2"/>
@@ -35848,6 +35834,20 @@
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="AN3:AO3"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="X3:X4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN4 D3:D4 L4 M4 N4 O4 P4 Q4 R4 AH4 AI4 AJ4 AK4 AL4 AM4 AO4" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35888,7 +35888,7 @@
     <col min="2" max="3" width="18.5703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="20.5703125" customWidth="1"/>
+    <col min="12" max="12" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
@@ -35908,98 +35908,98 @@
       <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="82"/>
+      <c r="D2" s="80" t="s">
         <v>158</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="82"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="96" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96" t="s">
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106" t="s">
         <v>159</v>
       </c>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96" t="s">
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="94"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="106"/>
+      <c r="J4" s="106" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96" t="s">
-        <v>163</v>
-      </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96" t="s">
-        <v>161</v>
-      </c>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="77"/>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="44" t="s">
+      <c r="A5" s="78"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="51" t="s">
-        <v>205</v>
+      <c r="E5" s="57" t="s">
+        <v>202</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="51" t="s">
-        <v>205</v>
+      <c r="G5" s="57" t="s">
+        <v>202</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="51" t="s">
-        <v>205</v>
+      <c r="I5" s="57" t="s">
+        <v>202</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="51" t="s">
-        <v>205</v>
+      <c r="K5" s="57" t="s">
+        <v>202</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>73</v>
@@ -38806,7 +38806,7 @@
       <c r="L205" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OIA2juXsQVr9S2oP2mybawOifHzCkVXtWAdDfZJ2K3RMDe4SYTT0Jit/7m2eczthvGnOsPbITjE52MRfvCrPMA==" saltValue="DWrHcNm1oKnbWvyYitlxgA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="t43DLs+s5NR3jDRJjGFNrGXdd0zh6ig4+D6iaOgaTgwQCtZa1klKK01BY/Aj5GsBKodHv1cSKsVMcorIrbKhgw==" saltValue="DsbiSSsnv29CJQyWru+yRQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="D2:L2"/>
     <mergeCell ref="A2:A5"/>
@@ -38878,91 +38878,91 @@
       <c r="V1" s="7"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="72" t="s">
-        <v>165</v>
+      <c r="C2" s="73" t="s">
+        <v>162</v>
       </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="100" t="s">
-        <v>166</v>
+      <c r="D2" s="74"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="108" t="s">
+        <v>163</v>
       </c>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="97" t="s">
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="108" t="s">
+      <c r="K2" s="113" t="s">
+        <v>168</v>
+      </c>
+      <c r="L2" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="99" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="80"/>
+      <c r="P2" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="R2" s="106" t="s">
+        <v>169</v>
+      </c>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="94"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="79"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="94"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="107" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3" s="106" t="s">
+        <v>170</v>
+      </c>
+      <c r="T3" s="106"/>
+      <c r="U3" s="106" t="s">
         <v>171</v>
       </c>
-      <c r="L2" s="96" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" s="89" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" s="96" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" s="79"/>
-      <c r="P2" s="76" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="R2" s="96" t="s">
-        <v>172</v>
-      </c>
-      <c r="S2" s="96"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="96"/>
-      <c r="V2" s="96"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="105" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="99" t="s">
-        <v>80</v>
-      </c>
-      <c r="S3" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96" t="s">
-        <v>174</v>
-      </c>
-      <c r="V3" s="96"/>
+      <c r="V3" s="106"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="77"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="70"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="71"/>
       <c r="D4" s="41" t="s">
         <v>0</v>
       </c>
@@ -38970,30 +38970,30 @@
         <v>1</v>
       </c>
       <c r="F4" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="H4" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="I4" s="54" t="s">
-        <v>170</v>
-      </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="89"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="99"/>
       <c r="N4" s="46" t="s">
         <v>81</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="99"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="107"/>
       <c r="S4" s="50" t="s">
         <v>83</v>
       </c>
@@ -39001,10 +39001,10 @@
         <v>84</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="V4" s="43" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -43808,9 +43808,14 @@
       <c r="V204" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HegNjEUG0JGCK7Em0JYKFfbaDXofSI/eoHWk8rSNZhCuxxgrRfFxzqmKDw+rgM8g2AEjX7hW0V65tqpclq3eIA==" saltValue="dNae070C6OTNQ7yDYKjQHg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="DH4pbwpBCgOVxJ9KK8YMUqoGVi4hN4h0sZoI4bzxOwYd6s3rgpQnpSBPYhaWIv/lB5Wz8frrYtZ8i1ITmBBXew==" saltValue="K66eZwZ2YOSlOz/j5lhrvw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:T3"/>
@@ -43823,11 +43828,6 @@
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="P2:P4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 I4 F4 G4 H4 U4 V4" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -43865,14 +43865,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
-        <v>207</v>
+      <c r="A1" s="115" t="s">
+        <v>204</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -43885,10 +43885,10 @@
         <v>85</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F2" s="41" t="s">
         <v>86</v>
@@ -45495,7 +45495,7 @@
       <c r="F202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kviV1SZRnQko8ezco/44rWDpyPVJvrbA6GYXl6ikqHqao1OSEmfHNyEdJQTk0awshCQvmkR1NuK7VUgYncNMcQ==" saltValue="h3WPTOpyhj/BFNU0j0oJPA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FN5XjCkfoJMzNB3xxSMxF5fTBE47EIi4lyn8towZTKfC6UgUKWnx0SjqUB0dvx+fMO28pkDJTfvcixTOGR4P/g==" saltValue="PlngWBfIMMySzBcBNAG5ng==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -45549,59 +45549,59 @@
       <c r="L1" s="8"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="97" t="s">
-        <v>177</v>
+      <c r="D2" s="91" t="s">
+        <v>174</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="112"/>
-      <c r="G2" s="97" t="s">
-        <v>179</v>
+      <c r="F2" s="117"/>
+      <c r="G2" s="91" t="s">
+        <v>176</v>
       </c>
-      <c r="H2" s="76" t="s">
-        <v>178</v>
+      <c r="H2" s="77" t="s">
+        <v>175</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="78"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="98"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="49" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="98"/>
-      <c r="H3" s="77"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="49" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J3" s="48" t="s">
         <v>18</v>
       </c>
       <c r="K3" s="55" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L3" s="49" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -48405,7 +48405,7 @@
       <c r="L203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="UKy/9FtM0qE00vQznJsrAB6qNs4GW8BQPbqIcWB/O1BV/Zo2g6FqcmjtYLjBLHAOlTWuzmOBMkW75s7THcQJ1g==" saltValue="oLVNnQ9vZNGxIvvoNMp/5A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BGhIRZNXhHaWJYiU7Xlb4CwauylZ3rZdEH/3xrzCZbWI3WIAAuTgy6kEv7npV936xqH+cyCevlkWl26lZ9H7aw==" saltValue="ykBltnH/IwlrQJ7k84BDuA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="I2:L2"/>
     <mergeCell ref="D2:D3"/>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02300241-30E4-4E40-863C-BE866FA80704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C5ED1F-3147-4840-80A8-3224711601CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29490" yWindow="1020" windowWidth="26505" windowHeight="14100" tabRatio="879" firstSheet="2" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C5ED1F-3147-4840-80A8-3224711601CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9E1262-C190-437F-826D-2562D7344DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="29490" yWindow="1020" windowWidth="26505" windowHeight="14100" tabRatio="879" firstSheet="2" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -22,8 +23,8 @@
     <sheet name="E-SET" sheetId="7" r:id="rId7"/>
     <sheet name="E-SET-CETACEANS" sheetId="24" r:id="rId8"/>
     <sheet name="E-SET-CATCHES" sheetId="15" r:id="rId9"/>
-    <sheet name="E-SET-CATCHES-SPECIMEN" sheetId="16" r:id="rId10"/>
-    <sheet name="E-SET-CATCHES-SPECIMEN-SSI" sheetId="17" r:id="rId11"/>
+    <sheet name="E-SET-CATCH-SPECIMENS" sheetId="16" r:id="rId10"/>
+    <sheet name="E-SET-CATCH-SPECIMENS-SSI" sheetId="17" r:id="rId11"/>
     <sheet name="E-SET-TAG-DETAILS" sheetId="19" r:id="rId12"/>
     <sheet name="D-ACTIVITIES" sheetId="25" r:id="rId13"/>
   </sheets>
@@ -246,9 +247,6 @@
   </si>
   <si>
     <t>NET</t>
-  </si>
-  <si>
-    <t>VALUE_MT</t>
   </si>
   <si>
     <t>SCHOOL_SIZE_T</t>
@@ -636,6 +634,9 @@
   </si>
   <si>
     <t>WELL</t>
+  </si>
+  <si>
+    <t>VALUE_T</t>
   </si>
 </sst>
 </file>
@@ -1136,6 +1137,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1207,6 +1211,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1280,18 +1296,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1304,9 +1308,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1316,6 +1317,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1330,9 +1334,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1672,36 +1673,36 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="53" t="s">
-        <v>97</v>
+      <c r="B2" s="54" t="s">
+        <v>96</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>58</v>
@@ -1720,7 +1721,7 @@
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="13"/>
       <c r="C6" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -1739,26 +1740,26 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="59" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" s="59"/>
+      <c r="G8" s="60"/>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
       <c r="C9" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="14"/>
       <c r="F9" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="15"/>
@@ -1766,12 +1767,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="13"/>
       <c r="C10" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="15"/>
@@ -1788,7 +1789,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="14"/>
@@ -1828,7 +1829,7 @@
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="13"/>
       <c r="C16" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
@@ -1848,7 +1849,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13"/>
       <c r="C18" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="14"/>
@@ -1859,7 +1860,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="13"/>
       <c r="C19" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="14"/>
@@ -1881,7 +1882,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="13"/>
       <c r="C21" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="14"/>
@@ -1929,11 +1930,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="62"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2004,57 +2005,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="110" t="s">
+      <c r="C1" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="76" t="s">
-        <v>165</v>
+      <c r="E1" s="80" t="s">
+        <v>164</v>
       </c>
-      <c r="F1" s="83" t="s">
+      <c r="F1" s="87" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="101" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="100" t="s">
-        <v>172</v>
-      </c>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100" t="s">
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="97" t="s">
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="73" t="s">
+      <c r="R1" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="75"/>
-      <c r="T1" s="73" t="s">
-        <v>170</v>
+      <c r="S1" s="76"/>
+      <c r="T1" s="74" t="s">
+        <v>169</v>
       </c>
-      <c r="U1" s="74"/>
-      <c r="V1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="111"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="82"/>
       <c r="F2" s="37" t="s">
         <v>19</v>
       </c>
@@ -2062,7 +2063,7 @@
         <v>37</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I2" s="33" t="s">
         <v>45</v>
@@ -2074,21 +2075,21 @@
         <v>37</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M2" s="36" t="s">
         <v>45</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="P2" s="48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
-      <c r="Q2" s="99"/>
+      <c r="Q2" s="79"/>
       <c r="R2" s="39" t="s">
         <v>53</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>39</v>
       </c>
       <c r="V2" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -6908,17 +6909,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F0tc7B77v7QjLsOz0RLL7MWtNCPBw2o4Z9f2YID1JxL/5n/IHv5nh1k9azF4NV4h1VsWAZfQTfWlFcYB76PlMA==" saltValue="n01OBaL5NKfbkpK2LmYd9A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="T1:V1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 J2 L2 N2 Q1:Q2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
@@ -6966,52 +6967,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="110" t="s">
+      <c r="C1" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="97" t="s">
+      <c r="E1" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" s="77" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="97" t="s">
+      <c r="G1" s="77" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="97" t="s">
+      <c r="H1" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="H1" s="112" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="98" t="s">
-        <v>176</v>
-      </c>
-      <c r="J1" s="112" t="s">
+      <c r="J1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="112" t="s">
+      <c r="K1" s="113" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="111"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -9616,17 +9617,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7AjhL+fqXAsFucLZgoF2uPzgppBK+T/XTUzkX/JwpgqEiyXl3lYNCR44gk+4O6ySKgm58zlH7twzGxSoUOj8WQ==" saltValue="905c+jUO58aUTtAhHe6Qyg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 G1:G2 I1:I2 E1:E2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -9685,19 +9686,19 @@
         <v>19</v>
       </c>
       <c r="H1" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="I1" s="42" t="s">
-        <v>194</v>
+      <c r="J1" s="42" t="s">
+        <v>176</v>
       </c>
-      <c r="J1" s="42" t="s">
+      <c r="K1" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="K1" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="L1" s="113" t="s">
-        <v>195</v>
+      <c r="L1" s="53" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -12544,10 +12545,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -14196,125 +14197,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="4"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63" t="s">
+      <c r="E3" s="70"/>
+      <c r="F3" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="66"/>
+      <c r="H3" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="70"/>
+      <c r="K3" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="66"/>
+      <c r="M3" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="4"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="63"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="66" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="63"/>
-      <c r="W2" s="63"/>
-      <c r="X2" s="63"/>
-      <c r="Y2" s="4"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="68" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="69"/>
-      <c r="F3" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" s="65"/>
-      <c r="H3" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="68" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="69"/>
-      <c r="K3" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="65"/>
-      <c r="M3" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="63" t="s">
+      <c r="O3" s="64"/>
+      <c r="P3" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63" t="s">
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="W3" s="75"/>
+      <c r="X3" s="76"/>
     </row>
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="63"/>
+      <c r="A4" s="64"/>
       <c r="B4" s="33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="36" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>4</v>
@@ -14325,9 +14326,9 @@
       <c r="G4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="71"/>
+      <c r="H4" s="72"/>
       <c r="I4" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J4" s="32" t="s">
         <v>4</v>
@@ -14338,7 +14339,7 @@
       <c r="L4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="71"/>
+      <c r="M4" s="72"/>
       <c r="N4" s="33" t="s">
         <v>5</v>
       </c>
@@ -14361,16 +14362,16 @@
         <v>10</v>
       </c>
       <c r="U4" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="V4" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="W4" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="X4" s="32" t="s">
         <v>110</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -14664,7 +14665,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -19615,100 +19616,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="92" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="93"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="97" t="s">
-        <v>182</v>
+      <c r="H1" s="97"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="77" t="s">
+        <v>181</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="80" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="86"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="83"/>
+      <c r="B2" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="99" t="s">
+        <v>180</v>
+      </c>
+      <c r="J2" s="78"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="L1" s="80" t="s">
-        <v>96</v>
-      </c>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="82"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="90" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="91" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="87" t="s">
-        <v>103</v>
-      </c>
-      <c r="H2" s="88" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="95" t="s">
-        <v>181</v>
-      </c>
-      <c r="J2" s="98"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="83" t="s">
+      <c r="M2" s="87"/>
+      <c r="N2" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83" t="s">
-        <v>114</v>
-      </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="84" t="s">
+      <c r="O2" s="87"/>
+      <c r="P2" s="88" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="78"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="82"/>
       <c r="L3" s="33" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N3" s="33" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
-      <c r="P3" s="84"/>
+      <c r="P3" s="88"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -23313,6 +23314,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="vByIra6iNLt4HMISOkzwwknbnfaLgU5KtvTbTvu/JJDOfSKOghwnr7ZJnPbcH2fp8hgyEEDP45EpmaEvUcD2OA==" saltValue="16gLCNiakQa/5+DiuMjcyw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="K1:K3"/>
     <mergeCell ref="A1:A3"/>
@@ -23329,7 +23331,6 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -23374,49 +23375,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="87" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83" t="s">
-        <v>117</v>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="83"/>
+      <c r="B2" s="67" t="s">
+        <v>100</v>
       </c>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="70" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="66" t="s">
-        <v>101</v>
+      <c r="G2" s="67" t="s">
+        <v>100</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="70" t="s">
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="71" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>4</v>
@@ -23427,9 +23428,9 @@
       <c r="E3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="71"/>
+      <c r="F3" s="72"/>
       <c r="G3" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H3" s="32" t="s">
         <v>4</v>
@@ -23440,7 +23441,7 @@
       <c r="J3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="71"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -26117,156 +26118,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="73" t="s">
+      <c r="B1" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="75"/>
-      <c r="AH1" s="73" t="s">
-        <v>131</v>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="74" t="s">
+        <v>143</v>
       </c>
-      <c r="AI1" s="74"/>
-      <c r="AJ1" s="74"/>
-      <c r="AK1" s="74"/>
-      <c r="AL1" s="74"/>
-      <c r="AM1" s="74"/>
-      <c r="AN1" s="74"/>
-      <c r="AO1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
+      <c r="Y1" s="75"/>
+      <c r="Z1" s="75"/>
+      <c r="AA1" s="75"/>
+      <c r="AB1" s="75"/>
+      <c r="AC1" s="75"/>
+      <c r="AD1" s="75"/>
+      <c r="AE1" s="75"/>
+      <c r="AF1" s="75"/>
+      <c r="AG1" s="76"/>
+      <c r="AH1" s="74" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI1" s="75"/>
+      <c r="AJ1" s="75"/>
+      <c r="AK1" s="75"/>
+      <c r="AL1" s="75"/>
+      <c r="AM1" s="75"/>
+      <c r="AN1" s="75"/>
+      <c r="AO1" s="76"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="85" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="102" t="s">
         <v>183</v>
       </c>
-      <c r="C2" s="101" t="s">
-        <v>184</v>
+      <c r="D2" s="77" t="s">
+        <v>117</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="E2" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100" t="s">
-        <v>120</v>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="103" t="s">
+        <v>186</v>
       </c>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="102" t="s">
-        <v>187</v>
+      <c r="L2" s="95" t="s">
+        <v>124</v>
       </c>
-      <c r="L2" s="91" t="s">
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="101" t="s">
         <v>125</v>
       </c>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="91" t="s">
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="91"/>
-      <c r="U2" s="100" t="s">
-        <v>130</v>
+      <c r="T2" s="95"/>
+      <c r="U2" s="101" t="s">
+        <v>129</v>
       </c>
-      <c r="V2" s="100" t="s">
+      <c r="V2" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="100" t="s">
+      <c r="W2" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="100" t="s">
+      <c r="X2" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="100" t="s">
+      <c r="Y2" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="100" t="s">
+      <c r="Z2" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="100" t="s">
+      <c r="AA2" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="100" t="s">
+      <c r="AB2" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="100" t="s">
+      <c r="AC2" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="100" t="s">
+      <c r="AD2" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="100" t="s">
+      <c r="AE2" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="100" t="s">
+      <c r="AF2" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="100" t="s">
+      <c r="AG2" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="91" t="s">
+      <c r="AH2" s="95" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI2" s="95"/>
+      <c r="AJ2" s="95" t="s">
         <v>140</v>
       </c>
-      <c r="AI2" s="91"/>
-      <c r="AJ2" s="91" t="s">
+      <c r="AK2" s="95"/>
+      <c r="AL2" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="AK2" s="91"/>
-      <c r="AL2" s="91" t="s">
+      <c r="AM2" s="95"/>
+      <c r="AN2" s="95" t="s">
         <v>142</v>
       </c>
-      <c r="AM2" s="91"/>
-      <c r="AN2" s="91" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO2" s="91"/>
+      <c r="AO2" s="95"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="99"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="79"/>
       <c r="E3" s="42" t="s">
         <v>20</v>
       </c>
@@ -26274,7 +26275,7 @@
         <v>21</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H3" s="51" t="s">
         <v>20</v>
@@ -26283,72 +26284,72 @@
         <v>21</v>
       </c>
       <c r="J3" s="51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
-      <c r="K3" s="103"/>
+      <c r="K3" s="104"/>
       <c r="L3" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="N3" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="O3" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="O3" s="32" t="s">
-        <v>124</v>
+      <c r="P3" s="35" t="s">
+        <v>126</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="Q3" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="Q3" s="35" t="s">
+      <c r="R3" s="35" t="s">
         <v>128</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>129</v>
       </c>
       <c r="S3" s="36" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
-      <c r="U3" s="100"/>
-      <c r="V3" s="100"/>
-      <c r="W3" s="100"/>
-      <c r="X3" s="100"/>
-      <c r="Y3" s="100"/>
-      <c r="Z3" s="100"/>
-      <c r="AA3" s="100"/>
-      <c r="AB3" s="100"/>
-      <c r="AC3" s="100"/>
-      <c r="AD3" s="100"/>
-      <c r="AE3" s="100"/>
-      <c r="AF3" s="100"/>
-      <c r="AG3" s="100"/>
+      <c r="U3" s="101"/>
+      <c r="V3" s="101"/>
+      <c r="W3" s="101"/>
+      <c r="X3" s="101"/>
+      <c r="Y3" s="101"/>
+      <c r="Z3" s="101"/>
+      <c r="AA3" s="101"/>
+      <c r="AB3" s="101"/>
+      <c r="AC3" s="101"/>
+      <c r="AD3" s="101"/>
+      <c r="AE3" s="101"/>
+      <c r="AF3" s="101"/>
+      <c r="AG3" s="101"/>
       <c r="AH3" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI3" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="AI3" s="35" t="s">
+      <c r="AJ3" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="AJ3" s="35" t="s">
+      <c r="AK3" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AL3" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="AL3" s="35" t="s">
+      <c r="AM3" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="AM3" s="35" t="s">
+      <c r="AN3" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="AN3" s="35" t="s">
+      <c r="AO3" s="35" t="s">
         <v>138</v>
-      </c>
-      <c r="AO3" s="35" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
@@ -34954,20 +34955,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="QMCtlxTdGMeqat8mqK+Cr1Fx43bg5wNSEIC6CaFaY0KIvb4EIpIjm6obel/9Z0Dv1oF2vEXJtDbPbO1sewkcAA==" saltValue="PmNUggfK+1j4qc6GrFpb8Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="X2:X3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -34984,6 +34971,20 @@
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="AN2:AO2"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3 D2:D3 L3 M3 N3 O3 P3 Q3 R3 AH3 AI3 AJ3 AK3 AL3 AM3 AO3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35028,101 +35029,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="74" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="76"/>
+      <c r="D1" s="74" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="73" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="76"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="83"/>
+      <c r="B2" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="95" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="75"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="91" t="s">
-        <v>63</v>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95" t="s">
+        <v>191</v>
       </c>
-      <c r="C2" s="91" t="s">
-        <v>64</v>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="83"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95" t="s">
+        <v>189</v>
       </c>
-      <c r="D2" s="91" t="s">
-        <v>65</v>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95" t="s">
+        <v>190</v>
       </c>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91" t="s">
+      <c r="G3" s="95"/>
+      <c r="H3" s="95" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95" t="s">
         <v>148</v>
       </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="79"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91" t="s">
-        <v>190</v>
-      </c>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91" t="s">
-        <v>191</v>
-      </c>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91" t="s">
-        <v>150</v>
-      </c>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91" t="s">
-        <v>149</v>
-      </c>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="49" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F4" s="49" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J4" s="49" t="s">
         <v>18</v>
       </c>
       <c r="K4" s="49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -37926,7 +37927,7 @@
       <c r="L204" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dO5zYkjCt6LQgCp4Gf9XtauF/GqDh0D4gLU7NdhK3eHG1l1O2Jco9T8NDJwr0kjrtNHrX9T/FiuNjtXmQQtk1w==" saltValue="ZtUpuys5qJVA//HJfBbH+A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0b9R3e/9LkSgcpyzrZ2U3a5t0I0I5ykUo6zzefVGIHDw+IAwk1LwhhoACycRMhaFL5RpOUMpCBjExFBrctDRNg==" saltValue="2fMSlqclAhc2wpF2yjz/9A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="A1:A4"/>
@@ -37972,91 +37973,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" s="68"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="102" t="s">
         <v>151</v>
-      </c>
-      <c r="D1" s="67"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="101" t="s">
-        <v>152</v>
       </c>
       <c r="G1" s="105"/>
       <c r="H1" s="105"/>
       <c r="I1" s="105"/>
-      <c r="J1" s="76" t="s">
-        <v>79</v>
+      <c r="J1" s="80" t="s">
+        <v>78</v>
       </c>
       <c r="K1" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="L1" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="74"/>
+      <c r="P1" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" s="95" t="s">
         <v>157</v>
       </c>
-      <c r="L1" s="91" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="91" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="91" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="73"/>
-      <c r="P1" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q1" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="R1" s="91" t="s">
-        <v>158</v>
-      </c>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="104" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="68"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="69"/>
       <c r="G2" s="106"/>
       <c r="H2" s="106"/>
       <c r="I2" s="106"/>
-      <c r="J2" s="77"/>
+      <c r="J2" s="81"/>
       <c r="K2" s="107"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="100" t="s">
-        <v>72</v>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="101" t="s">
+        <v>71</v>
       </c>
-      <c r="S2" s="91" t="s">
+      <c r="S2" s="95" t="s">
+        <v>158</v>
+      </c>
+      <c r="T2" s="95"/>
+      <c r="U2" s="95" t="s">
         <v>159</v>
       </c>
-      <c r="T2" s="91"/>
-      <c r="U2" s="91" t="s">
-        <v>160</v>
-      </c>
-      <c r="V2" s="91"/>
+      <c r="V2" s="95"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="65"/>
       <c r="D3" s="33" t="s">
         <v>0</v>
       </c>
@@ -38064,41 +38065,41 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="H3" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="I3" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="I3" s="46" t="s">
-        <v>156</v>
+      <c r="J3" s="82"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="38" t="s">
+        <v>72</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="38" t="s">
+      <c r="O3" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="45" t="s">
+      <c r="P3" s="72"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="100"/>
-      <c r="S3" s="42" t="s">
+      <c r="T3" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="T3" s="42" t="s">
-        <v>76</v>
-      </c>
       <c r="U3" s="35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="V3" s="35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -42905,6 +42906,11 @@
   <sheetProtection algorithmName="SHA-512" hashValue="lB47MHjN7Q2DdsILtEIzmsVgF/RGH4fl4xMJSJCt+pfGM3g82GbEDtt7bi2H3b59LuCUpowHsRtb+ERWIIPhnQ==" saltValue="jdC1iYmDqqf8XUqPiuEltA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:T2"/>
@@ -42917,11 +42923,6 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K3 I3 F3 G3 H3 U3 V3" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -42966,16 +42967,16 @@
         <v>60</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -44614,59 +44615,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="C1" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="76" t="s">
+      <c r="D1" s="80" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="110"/>
+      <c r="G1" s="80" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="71" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="108" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="76" t="s">
-        <v>165</v>
-      </c>
-      <c r="H1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="72"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="73"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="71"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="78"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="41" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="71"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="72"/>
       <c r="I2" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J2" s="40" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L2" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9E1262-C190-437F-826D-2562D7344DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5D5C19-000B-4596-83CF-794B7537EDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
@@ -1067,9 +1067,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1212,6 +1209,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1279,23 +1293,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1336,6 +1333,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1673,24 +1671,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="56"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="59"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
@@ -1740,15 +1738,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="60"/>
+      <c r="D8" s="59"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="60"/>
+      <c r="G8" s="59"/>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1870,7 +1868,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="13"/>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="24" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="23"/>
@@ -1881,7 +1879,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="13"/>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="113" t="s">
         <v>93</v>
       </c>
       <c r="D21" s="23"/>
@@ -1930,11 +1928,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="63"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1951,7 +1949,7 @@
       <c r="D28" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ttuikl6SGMUK0RmKP8ZHj/8oHZ+lV5VHL9m/8ozKHh0FHyC3HzjMJRfhBm321hHclq1Nx6r12KkNIjTl28bJuw==" saltValue="NL2doltTOA5WyZ9sLm8ajw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="P0eXBbLvNd0cwngj0IqgYIKi11uTa+db62OefGJfTWaPpfLcaxz8FvVz+3mMRTapmMh2nJWPSsqxK98QOftsmA==" saltValue="NZ9w+CGcrvuXg+Z3QjY9xw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -1966,9 +1964,10 @@
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="entities" xr:uid="{CAE9B0E0-EE52-4322-8FFE-6D92F0A66DA9}"/>
     <hyperlink ref="C20" r:id="rId2" location="fleets" xr:uid="{4EFD096A-72A5-4FBE-9D0C-5EB5ED0A5D58}"/>
+    <hyperlink ref="C21" r:id="rId3" location="sourcesRO" xr:uid="{79E92487-400C-4D87-9E38-90FB82B14B98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -2005,104 +2004,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="111" t="s">
+      <c r="D1" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="91" t="s">
         <v>170</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="101" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="100" t="s">
         <v>171</v>
       </c>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101" t="s">
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="77" t="s">
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="74" t="s">
+      <c r="R1" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="76"/>
-      <c r="T1" s="74" t="s">
+      <c r="S1" s="75"/>
+      <c r="T1" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="U1" s="75"/>
-      <c r="V1" s="76"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="75"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="112"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="37" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="J2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="N2" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="48" t="s">
+      <c r="P2" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="39" t="s">
+      <c r="Q2" s="83"/>
+      <c r="R2" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="S2" s="52" t="s">
+      <c r="S2" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="T2" s="48" t="s">
+      <c r="T2" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="48" t="s">
+      <c r="U2" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="36" t="s">
+      <c r="V2" s="35" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6967,52 +6966,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="111" t="s">
+      <c r="D1" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="81" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="81" t="s">
         <v>173</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="81" t="s">
         <v>174</v>
       </c>
-      <c r="H1" s="113" t="s">
+      <c r="H1" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="78" t="s">
+      <c r="I1" s="82" t="s">
         <v>175</v>
       </c>
-      <c r="J1" s="113" t="s">
+      <c r="J1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="113" t="s">
+      <c r="K1" s="112" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="112"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
+      <c r="A2" s="111"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -9664,40 +9663,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="J1" s="42" t="s">
+      <c r="J1" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="K1" s="42" t="s">
+      <c r="K1" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="L1" s="53" t="s">
+      <c r="L1" s="52" t="s">
         <v>194</v>
       </c>
     </row>
@@ -12532,22 +12531,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="35" t="s">
         <v>79</v>
       </c>
     </row>
@@ -14197,180 +14196,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64" t="s">
+      <c r="C1" s="63"/>
+      <c r="D1" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="64"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="64"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="67" t="s">
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="64"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="64"/>
-      <c r="U2" s="64"/>
-      <c r="V2" s="64"/>
-      <c r="W2" s="64"/>
-      <c r="X2" s="64"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="63"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69" t="s">
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="65" t="s">
+      <c r="E3" s="69"/>
+      <c r="F3" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="66"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="65"/>
+      <c r="H3" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="69" t="s">
+      <c r="I3" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="70"/>
-      <c r="K3" s="65" t="s">
+      <c r="J3" s="69"/>
+      <c r="K3" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="L3" s="66"/>
-      <c r="M3" s="71" t="s">
+      <c r="L3" s="65"/>
+      <c r="M3" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="64" t="s">
+      <c r="N3" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64" t="s">
+      <c r="O3" s="63"/>
+      <c r="P3" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="74" t="s">
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="V3" s="75"/>
-      <c r="W3" s="75"/>
-      <c r="X3" s="76"/>
+      <c r="V3" s="74"/>
+      <c r="W3" s="74"/>
+      <c r="X3" s="75"/>
     </row>
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
-      <c r="B4" s="33" t="s">
+      <c r="A4" s="63"/>
+      <c r="B4" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="72"/>
-      <c r="I4" s="32" t="s">
+      <c r="H4" s="71"/>
+      <c r="I4" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="72"/>
-      <c r="N4" s="33" t="s">
+      <c r="M4" s="71"/>
+      <c r="N4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="O4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="33" t="s">
+      <c r="P4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="33" t="s">
+      <c r="Q4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="36" t="s">
+      <c r="R4" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="36" t="s">
+      <c r="S4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="33" t="s">
+      <c r="T4" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="U4" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="V4" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="W4" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="X4" s="32" t="s">
+      <c r="X4" s="31" t="s">
         <v>110</v>
       </c>
     </row>
@@ -19616,100 +19615,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="96" t="s">
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="97"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="77" t="s">
+      <c r="H1" s="77"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="81" t="s">
         <v>181</v>
       </c>
-      <c r="K1" s="80" t="s">
+      <c r="K1" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="84" t="s">
+      <c r="L1" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="86"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="90"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="98" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="89" t="s">
+      <c r="E2" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="95" t="s">
+      <c r="F2" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="91" t="s">
+      <c r="G2" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="92" t="s">
+      <c r="H2" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="87" t="s">
+      <c r="J2" s="82"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87" t="s">
+      <c r="M2" s="91"/>
+      <c r="N2" s="91" t="s">
         <v>113</v>
       </c>
-      <c r="O2" s="87"/>
-      <c r="P2" s="88" t="s">
+      <c r="O2" s="91"/>
+      <c r="P2" s="92" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="33" t="s">
+      <c r="A3" s="71"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="N3" s="33" t="s">
+      <c r="N3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="37" t="s">
+      <c r="O3" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="P3" s="88"/>
+      <c r="P3" s="92"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -23312,12 +23311,8 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vByIra6iNLt4HMISOkzwwknbnfaLgU5KtvTbTvu/JJDOfSKOghwnr7ZJnPbcH2fp8hgyEEDP45EpmaEvUcD2OA==" saltValue="16gLCNiakQa/5+DiuMjcyw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Hbw1kM2GZdKiXn+tZ2jTENxb+s/WuKBOS35p7Hczzc8mzknealDwavQKvnmoI0NQ4e6Cl68C/s3alEC/HGJgTQ==" saltValue="phbtvlo1TeohYtjp0VwRjg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K3"/>
-    <mergeCell ref="A1:A3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:P3"/>
@@ -23331,6 +23326,10 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="A1:A3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -23375,73 +23374,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="67" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="71" t="s">
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="71" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="70" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="32" t="s">
+      <c r="A3" s="71"/>
+      <c r="B3" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="72"/>
-      <c r="G3" s="32" t="s">
+      <c r="F3" s="71"/>
+      <c r="G3" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="72"/>
+      <c r="K3" s="71"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -26118,237 +26117,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="74" t="s">
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="73" t="s">
         <v>143</v>
       </c>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="75"/>
-      <c r="Z1" s="75"/>
-      <c r="AA1" s="75"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="75"/>
-      <c r="AD1" s="75"/>
-      <c r="AE1" s="75"/>
-      <c r="AF1" s="75"/>
-      <c r="AG1" s="76"/>
-      <c r="AH1" s="74" t="s">
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="75"/>
+      <c r="AH1" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="AI1" s="75"/>
-      <c r="AJ1" s="75"/>
-      <c r="AK1" s="75"/>
-      <c r="AL1" s="75"/>
-      <c r="AM1" s="75"/>
-      <c r="AN1" s="75"/>
-      <c r="AO1" s="76"/>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
+      <c r="AM1" s="74"/>
+      <c r="AN1" s="74"/>
+      <c r="AO1" s="75"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="89" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="93" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="102" t="s">
+      <c r="C2" s="101" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="101" t="s">
+      <c r="E2" s="100" t="s">
         <v>118</v>
       </c>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101" t="s">
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="103" t="s">
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="102" t="s">
         <v>186</v>
       </c>
-      <c r="L2" s="95" t="s">
+      <c r="L2" s="99" t="s">
         <v>124</v>
       </c>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="101" t="s">
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="95" t="s">
+      <c r="Q2" s="100"/>
+      <c r="R2" s="100"/>
+      <c r="S2" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="95"/>
-      <c r="U2" s="101" t="s">
+      <c r="T2" s="99"/>
+      <c r="U2" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="V2" s="101" t="s">
+      <c r="V2" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="101" t="s">
+      <c r="W2" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="101" t="s">
+      <c r="X2" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="101" t="s">
+      <c r="Y2" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="101" t="s">
+      <c r="Z2" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="101" t="s">
+      <c r="AA2" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="101" t="s">
+      <c r="AB2" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="101" t="s">
+      <c r="AC2" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="101" t="s">
+      <c r="AD2" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="101" t="s">
+      <c r="AE2" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="101" t="s">
+      <c r="AF2" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="101" t="s">
+      <c r="AG2" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="95" t="s">
+      <c r="AH2" s="99" t="s">
         <v>139</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="95" t="s">
+      <c r="AI2" s="99"/>
+      <c r="AJ2" s="99" t="s">
         <v>140</v>
       </c>
-      <c r="AK2" s="95"/>
-      <c r="AL2" s="95" t="s">
+      <c r="AK2" s="99"/>
+      <c r="AL2" s="99" t="s">
         <v>141</v>
       </c>
-      <c r="AM2" s="95"/>
-      <c r="AN2" s="95" t="s">
+      <c r="AM2" s="99"/>
+      <c r="AN2" s="99" t="s">
         <v>142</v>
       </c>
-      <c r="AO2" s="95"/>
+      <c r="AO2" s="99"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="42" t="s">
+      <c r="A3" s="71"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="K3" s="104"/>
-      <c r="L3" s="32" t="s">
+      <c r="K3" s="103"/>
+      <c r="L3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="P3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="Q3" s="35" t="s">
+      <c r="Q3" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="R3" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="S3" s="36" t="s">
+      <c r="S3" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="43" t="s">
+      <c r="T3" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="U3" s="101"/>
-      <c r="V3" s="101"/>
-      <c r="W3" s="101"/>
-      <c r="X3" s="101"/>
-      <c r="Y3" s="101"/>
-      <c r="Z3" s="101"/>
-      <c r="AA3" s="101"/>
-      <c r="AB3" s="101"/>
-      <c r="AC3" s="101"/>
-      <c r="AD3" s="101"/>
-      <c r="AE3" s="101"/>
-      <c r="AF3" s="101"/>
-      <c r="AG3" s="101"/>
-      <c r="AH3" s="44" t="s">
+      <c r="U3" s="100"/>
+      <c r="V3" s="100"/>
+      <c r="W3" s="100"/>
+      <c r="X3" s="100"/>
+      <c r="Y3" s="100"/>
+      <c r="Z3" s="100"/>
+      <c r="AA3" s="100"/>
+      <c r="AB3" s="100"/>
+      <c r="AC3" s="100"/>
+      <c r="AD3" s="100"/>
+      <c r="AE3" s="100"/>
+      <c r="AF3" s="100"/>
+      <c r="AG3" s="100"/>
+      <c r="AH3" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="AI3" s="35" t="s">
+      <c r="AI3" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="AJ3" s="35" t="s">
+      <c r="AJ3" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="AL3" s="35" t="s">
+      <c r="AL3" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="AM3" s="35" t="s">
+      <c r="AM3" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="AN3" s="35" t="s">
+      <c r="AN3" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="AO3" s="35" t="s">
+      <c r="AO3" s="34" t="s">
         <v>138</v>
       </c>
     </row>
@@ -35029,100 +35028,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="74" t="s">
+      <c r="C1" s="75"/>
+      <c r="D1" s="73" t="s">
         <v>146</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="76"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="75"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="95" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95" t="s">
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99" t="s">
         <v>147</v>
       </c>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95" t="s">
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99" t="s">
         <v>189</v>
       </c>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95" t="s">
+      <c r="E3" s="99"/>
+      <c r="F3" s="99" t="s">
         <v>190</v>
       </c>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95" t="s">
+      <c r="G3" s="99"/>
+      <c r="H3" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95" t="s">
+      <c r="I3" s="99"/>
+      <c r="J3" s="99" t="s">
         <v>148</v>
       </c>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="49" t="s">
+      <c r="A4" s="71"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="I4" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="J4" s="49" t="s">
+      <c r="J4" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="49" t="s">
+      <c r="K4" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="35" t="s">
         <v>195</v>
       </c>
     </row>
@@ -37973,132 +37972,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="102" t="s">
+      <c r="D1" s="67"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="101" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="80" t="s">
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="107" t="s">
+      <c r="K1" s="106" t="s">
         <v>156</v>
       </c>
-      <c r="L1" s="95" t="s">
+      <c r="L1" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="95" t="s">
+      <c r="M1" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="95" t="s">
+      <c r="N1" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="74"/>
-      <c r="P1" s="71" t="s">
+      <c r="O1" s="73"/>
+      <c r="P1" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="76" t="s">
+      <c r="Q1" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="R1" s="95" t="s">
+      <c r="R1" s="99" t="s">
         <v>157</v>
       </c>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="108" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="101" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="S2" s="95" t="s">
+      <c r="S2" s="99" t="s">
         <v>158</v>
       </c>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95" t="s">
+      <c r="T2" s="99"/>
+      <c r="U2" s="99" t="s">
         <v>159</v>
       </c>
-      <c r="V2" s="95"/>
+      <c r="V2" s="99"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="I3" s="46" t="s">
+      <c r="I3" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="J3" s="82"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="38" t="s">
+      <c r="J3" s="86"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="45" t="s">
+      <c r="O3" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="42" t="s">
+      <c r="P3" s="71"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="100"/>
+      <c r="S3" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="T3" s="42" t="s">
+      <c r="T3" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="U3" s="35" t="s">
+      <c r="U3" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="V3" s="35" t="s">
+      <c r="V3" s="34" t="s">
         <v>161</v>
       </c>
     </row>
@@ -42960,22 +42959,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="32" t="s">
         <v>77</v>
       </c>
     </row>
@@ -44615,58 +44614,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="109" t="s">
+      <c r="E1" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="110"/>
-      <c r="G1" s="80" t="s">
+      <c r="F1" s="109"/>
+      <c r="G1" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="70" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="73"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="72"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="72"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="41" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="41" t="s">
+      <c r="G2" s="86"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="40" t="s">
         <v>166</v>
       </c>
     </row>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9CB524-A607-824C-A72F-CF2B2221863D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C27B0E-B8F9-1840-8F20-671DEDC7FB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="28840" windowHeight="16600" tabRatio="879" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="28840" windowHeight="16600" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="195">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -223,9 +223,6 @@
   </si>
   <si>
     <t>FATE</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
   </si>
   <si>
     <t>OBSERVED_TRIP_ID</t>
@@ -1209,6 +1206,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1281,18 +1290,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1305,6 +1302,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1314,9 +1314,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1671,7 +1668,7 @@
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" s="53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="54"/>
@@ -1692,17 +1689,17 @@
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>58</v>
+      <c r="G4" s="11">
+        <v>4</v>
       </c>
       <c r="H4" s="12"/>
     </row>
@@ -1718,7 +1715,7 @@
     <row r="6" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
       <c r="C6" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -1738,12 +1735,12 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="13"/>
       <c r="C8" s="59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="14"/>
       <c r="F8" s="59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" s="59"/>
       <c r="H8" s="15"/>
@@ -1751,12 +1748,12 @@
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="13"/>
       <c r="C9" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="14"/>
       <c r="F9" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="15"/>
@@ -1764,12 +1761,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="13"/>
       <c r="C10" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="15"/>
@@ -1786,7 +1783,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="14"/>
@@ -1826,7 +1823,7 @@
     <row r="16" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
       <c r="C16" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
@@ -1846,7 +1843,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="14"/>
@@ -1857,7 +1854,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
       <c r="C19" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="14"/>
@@ -1879,7 +1876,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="13"/>
       <c r="C21" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="14"/>
@@ -1948,7 +1945,7 @@
       <c r="D28" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JuauQ3QxDUnElbWqChvsY13zB/xw9SCqAArj0Y7svyRxI2OYoPv3Itjfk3RA4DB2Gl/CD4usS6oqSGRrrm5K6w==" saltValue="gYKQpSU71jWATJ6py1JeDg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OJWCnuZmqEkdlWngWd/Nu3n9tRFQF/E/jMYcpdSRStsR42RQe9XmdwL3KhmYwpaZN6JNMRWPiagIYn4jIwnJ8Q==" saltValue="F18nRm2Sq3ltI/mfgkFZZw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2005,28 +2002,28 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="C1" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="110" t="s">
+      <c r="D1" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="110" t="s">
-        <v>62</v>
+      <c r="E1" s="76" t="s">
+        <v>163</v>
       </c>
-      <c r="E1" s="97" t="s">
-        <v>164</v>
+      <c r="F1" s="83" t="s">
+        <v>169</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="100" t="s">
         <v>170</v>
-      </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="100" t="s">
-        <v>171</v>
       </c>
       <c r="K1" s="100"/>
       <c r="L1" s="100"/>
@@ -2036,7 +2033,7 @@
       </c>
       <c r="O1" s="100"/>
       <c r="P1" s="100"/>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="97" t="s">
         <v>38</v>
       </c>
       <c r="R1" s="73" t="s">
@@ -2044,7 +2041,7 @@
       </c>
       <c r="S1" s="75"/>
       <c r="T1" s="73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U1" s="74"/>
       <c r="V1" s="75"/>
@@ -2054,7 +2051,7 @@
       <c r="B2" s="111"/>
       <c r="C2" s="111"/>
       <c r="D2" s="111"/>
-      <c r="E2" s="99"/>
+      <c r="E2" s="78"/>
       <c r="F2" s="36" t="s">
         <v>19</v>
       </c>
@@ -2062,7 +2059,7 @@
         <v>37</v>
       </c>
       <c r="H2" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>45</v>
@@ -2074,21 +2071,21 @@
         <v>37</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M2" s="35" t="s">
         <v>45</v>
       </c>
       <c r="N2" s="31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O2" s="35" t="s">
         <v>36</v>
       </c>
       <c r="P2" s="45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
-      <c r="Q2" s="96"/>
+      <c r="Q2" s="99"/>
       <c r="R2" s="38" t="s">
         <v>53</v>
       </c>
@@ -2102,7 +2099,7 @@
         <v>39</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
@@ -6908,17 +6905,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F0tc7B77v7QjLsOz0RLL7MWtNCPBw2o4Z9f2YID1JxL/5n/IHv5nh1k9azF4NV4h1VsWAZfQTfWlFcYB76PlMA==" saltValue="n01OBaL5NKfbkpK2LmYd9A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 J2 L2 N2 Q1:Q2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
@@ -6967,31 +6964,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="C1" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="110" t="s">
+      <c r="D1" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="110" t="s">
-        <v>62</v>
+      <c r="E1" s="97" t="s">
+        <v>171</v>
       </c>
-      <c r="E1" s="94" t="s">
+      <c r="F1" s="97" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="94" t="s">
+      <c r="G1" s="97" t="s">
         <v>173</v>
-      </c>
-      <c r="G1" s="94" t="s">
-        <v>174</v>
       </c>
       <c r="H1" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="95" t="s">
-        <v>175</v>
+      <c r="I1" s="98" t="s">
+        <v>174</v>
       </c>
       <c r="J1" s="112" t="s">
         <v>43</v>
@@ -7005,13 +7002,13 @@
       <c r="B2" s="111"/>
       <c r="C2" s="111"/>
       <c r="D2" s="111"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
@@ -9616,17 +9613,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7AjhL+fqXAsFucLZgoF2uPzgppBK+T/XTUzkX/JwpgqEiyXl3lYNCR44gk+4O6ySKgm58zlH7twzGxSoUOj8WQ==" saltValue="905c+jUO58aUTtAhHe6Qyg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 G1:G2 I1:I2 E1:E2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -9664,16 +9661,16 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="C1" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="D1" s="47" t="s">
         <v>61</v>
-      </c>
-      <c r="D1" s="47" t="s">
-        <v>62</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>40</v>
@@ -9685,19 +9682,19 @@
         <v>19</v>
       </c>
       <c r="H1" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="I1" s="40" t="s">
-        <v>193</v>
+      <c r="J1" s="40" t="s">
+        <v>175</v>
       </c>
-      <c r="J1" s="40" t="s">
+      <c r="K1" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="K1" s="40" t="s">
-        <v>177</v>
-      </c>
       <c r="L1" s="50" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -12532,7 +12529,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="35" t="s">
         <v>49</v>
@@ -12544,10 +12541,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -14197,14 +14194,14 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E1" s="63"/>
       <c r="F1" s="63"/>
@@ -14216,7 +14213,7 @@
       <c r="L1" s="63"/>
       <c r="M1" s="63"/>
       <c r="N1" s="63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O1" s="63"/>
       <c r="P1" s="63"/>
@@ -14266,40 +14263,40 @@
       <c r="B3" s="63"/>
       <c r="C3" s="63"/>
       <c r="D3" s="68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" s="69"/>
       <c r="F3" s="64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G3" s="65"/>
       <c r="H3" s="70" t="s">
         <v>49</v>
       </c>
       <c r="I3" s="68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J3" s="69"/>
       <c r="K3" s="64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L3" s="65"/>
       <c r="M3" s="70" t="s">
         <v>49</v>
       </c>
       <c r="N3" s="63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O3" s="63"/>
       <c r="P3" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q3" s="63"/>
       <c r="R3" s="63"/>
       <c r="S3" s="63"/>
       <c r="T3" s="63"/>
       <c r="U3" s="73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="V3" s="74"/>
       <c r="W3" s="74"/>
@@ -14308,13 +14305,13 @@
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="63"/>
       <c r="B4" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="35" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" s="31" t="s">
         <v>4</v>
@@ -14327,7 +14324,7 @@
       </c>
       <c r="H4" s="71"/>
       <c r="I4" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="31" t="s">
         <v>4</v>
@@ -14361,16 +14358,16 @@
         <v>10</v>
       </c>
       <c r="U4" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="V4" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="V4" s="31" t="s">
+      <c r="W4" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="W4" s="31" t="s">
+      <c r="X4" s="31" t="s">
         <v>109</v>
-      </c>
-      <c r="X4" s="31" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -14664,7 +14661,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -19616,99 +19613,99 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="89" t="s">
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="90"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="94" t="s">
-        <v>181</v>
+      <c r="H1" s="93"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="97" t="s">
+        <v>180</v>
       </c>
-      <c r="K1" s="97" t="s">
-        <v>111</v>
+      <c r="K1" s="76" t="s">
+        <v>110</v>
       </c>
-      <c r="L1" s="77" t="s">
-        <v>95</v>
+      <c r="L1" s="80" t="s">
+        <v>94</v>
       </c>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="79"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="82"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="76"/>
+      <c r="A2" s="79"/>
       <c r="B2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="87" t="s">
-        <v>179</v>
+      <c r="C2" s="90" t="s">
+        <v>178</v>
       </c>
       <c r="D2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="84" t="s">
-        <v>102</v>
+      <c r="G2" s="87" t="s">
+        <v>101</v>
       </c>
-      <c r="H2" s="85" t="s">
+      <c r="H2" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="92" t="s">
-        <v>180</v>
+      <c r="I2" s="95" t="s">
+        <v>179</v>
       </c>
-      <c r="J2" s="95"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="80" t="s">
+      <c r="J2" s="98"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="83" t="s">
+        <v>111</v>
+      </c>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80" t="s">
-        <v>113</v>
-      </c>
-      <c r="O2" s="80"/>
-      <c r="P2" s="81" t="s">
+      <c r="O2" s="83"/>
+      <c r="P2" s="84" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="71"/>
       <c r="B3" s="63"/>
-      <c r="C3" s="87"/>
+      <c r="C3" s="90"/>
       <c r="D3" s="63"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="99"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="78"/>
       <c r="L3" s="32" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N3" s="32" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
-      <c r="P3" s="81"/>
+      <c r="P3" s="84"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -23313,6 +23310,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Hbw1kM2GZdKiXn+tZ2jTENxb+s/WuKBOS35p7Hczzc8mzknealDwavQKvnmoI0NQ4e6Cl68C/s3alEC/HGJgTQ==" saltValue="phbtvlo1TeohYtjp0VwRjg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="J1:J3"/>
     <mergeCell ref="K1:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="L1:P1"/>
@@ -23329,7 +23327,6 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J1:J3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -23375,27 +23372,27 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="76"/>
+      <c r="A2" s="79"/>
       <c r="B2" s="66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" s="67"/>
       <c r="D2" s="67"/>
@@ -23404,7 +23401,7 @@
         <v>49</v>
       </c>
       <c r="G2" s="66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H2" s="67"/>
       <c r="I2" s="67"/>
@@ -23416,7 +23413,7 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="71"/>
       <c r="B3" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="31" t="s">
         <v>4</v>
@@ -23429,7 +23426,7 @@
       </c>
       <c r="F3" s="71"/>
       <c r="G3" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H3" s="31" t="s">
         <v>4</v>
@@ -26117,10 +26114,10 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A1" s="70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C1" s="74"/>
       <c r="D1" s="74"/>
@@ -26141,7 +26138,7 @@
       <c r="S1" s="74"/>
       <c r="T1" s="75"/>
       <c r="U1" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V1" s="74"/>
       <c r="W1" s="74"/>
@@ -26156,7 +26153,7 @@
       <c r="AF1" s="74"/>
       <c r="AG1" s="75"/>
       <c r="AH1" s="73" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AI1" s="74"/>
       <c r="AJ1" s="74"/>
@@ -26167,46 +26164,46 @@
       <c r="AO1" s="75"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="76"/>
-      <c r="B2" s="82" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="85" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="101" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="101" t="s">
-        <v>183</v>
-      </c>
-      <c r="D2" s="94" t="s">
-        <v>117</v>
+      <c r="D2" s="97" t="s">
+        <v>116</v>
       </c>
       <c r="E2" s="100" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F2" s="100"/>
       <c r="G2" s="100"/>
       <c r="H2" s="100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I2" s="100"/>
       <c r="J2" s="100"/>
       <c r="K2" s="102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
-      <c r="L2" s="88" t="s">
+      <c r="L2" s="91" t="s">
+        <v>123</v>
+      </c>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="100" t="s">
         <v>124</v>
-      </c>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="100" t="s">
-        <v>125</v>
       </c>
       <c r="Q2" s="100"/>
       <c r="R2" s="100"/>
-      <c r="S2" s="88" t="s">
+      <c r="S2" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="88"/>
+      <c r="T2" s="91"/>
       <c r="U2" s="100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="V2" s="100" t="s">
         <v>23</v>
@@ -26244,28 +26241,28 @@
       <c r="AG2" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="88" t="s">
+      <c r="AH2" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91" t="s">
         <v>139</v>
       </c>
-      <c r="AI2" s="88"/>
-      <c r="AJ2" s="88" t="s">
+      <c r="AK2" s="91"/>
+      <c r="AL2" s="91" t="s">
         <v>140</v>
       </c>
-      <c r="AK2" s="88"/>
-      <c r="AL2" s="88" t="s">
+      <c r="AM2" s="91"/>
+      <c r="AN2" s="91" t="s">
         <v>141</v>
       </c>
-      <c r="AM2" s="88"/>
-      <c r="AN2" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="AO2" s="88"/>
+      <c r="AO2" s="91"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A3" s="71"/>
-      <c r="B3" s="83"/>
+      <c r="B3" s="86"/>
       <c r="C3" s="68"/>
-      <c r="D3" s="96"/>
+      <c r="D3" s="99"/>
       <c r="E3" s="40" t="s">
         <v>20</v>
       </c>
@@ -26273,7 +26270,7 @@
         <v>21</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H3" s="48" t="s">
         <v>20</v>
@@ -26282,35 +26279,35 @@
         <v>21</v>
       </c>
       <c r="J3" s="48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K3" s="103"/>
       <c r="L3" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="M3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="M3" s="31" t="s">
+      <c r="N3" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="O3" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="O3" s="31" t="s">
-        <v>123</v>
+      <c r="P3" s="34" t="s">
+        <v>125</v>
       </c>
-      <c r="P3" s="34" t="s">
+      <c r="Q3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="Q3" s="34" t="s">
+      <c r="R3" s="34" t="s">
         <v>127</v>
-      </c>
-      <c r="R3" s="34" t="s">
-        <v>128</v>
       </c>
       <c r="S3" s="35" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="U3" s="100"/>
       <c r="V3" s="100"/>
@@ -26326,28 +26323,28 @@
       <c r="AF3" s="100"/>
       <c r="AG3" s="100"/>
       <c r="AH3" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI3" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="AI3" s="34" t="s">
+      <c r="AJ3" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="AJ3" s="34" t="s">
+      <c r="AK3" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="AK3" s="34" t="s">
+      <c r="AL3" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="AL3" s="34" t="s">
+      <c r="AM3" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="AM3" s="34" t="s">
+      <c r="AN3" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="AN3" s="34" t="s">
+      <c r="AO3" s="34" t="s">
         <v>137</v>
-      </c>
-      <c r="AO3" s="34" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -34953,6 +34950,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="QMCtlxTdGMeqat8mqK+Cr1Fx43bg5wNSEIC6CaFaY0KIvb4EIpIjm6obel/9Z0Dv1oF2vEXJtDbPbO1sewkcAA==" saltValue="PmNUggfK+1j4qc6GrFpb8Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="X2:X3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -34969,20 +34980,6 @@
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="AN2:AO2"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3 D2:D3 L3 M3 N3 O3 P3 Q3 R3 AH3 AI3 AJ3 AK3 AL3 AM3 AO3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35028,14 +35025,14 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="73" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C1" s="75"/>
       <c r="D1" s="73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E1" s="74"/>
       <c r="F1" s="74"/>
@@ -35047,81 +35044,81 @@
       <c r="L1" s="75"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="76"/>
-      <c r="B2" s="88" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="91" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="D2" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="88" t="s">
-        <v>65</v>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91" t="s">
+        <v>146</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88" t="s">
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="79"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91" t="s">
+        <v>189</v>
+      </c>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91" t="s">
         <v>147</v>
       </c>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="76"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88" t="s">
-        <v>189</v>
-      </c>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88" t="s">
-        <v>190</v>
-      </c>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88" t="s">
-        <v>149</v>
-      </c>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88" t="s">
-        <v>148</v>
-      </c>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="71"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
       <c r="D4" s="46" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H4" s="46" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J4" s="46" t="s">
         <v>18</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L4" s="35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -37972,56 +37969,56 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="70" t="s">
-        <v>60</v>
-      </c>
       <c r="C1" s="66" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1" s="67"/>
       <c r="E1" s="72"/>
       <c r="F1" s="101" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="97" t="s">
-        <v>78</v>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="76" t="s">
+        <v>77</v>
       </c>
-      <c r="K1" s="106" t="s">
-        <v>156</v>
+      <c r="K1" s="107" t="s">
+        <v>155</v>
       </c>
-      <c r="L1" s="88" t="s">
+      <c r="L1" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="88" t="s">
+      <c r="N1" s="91" t="s">
         <v>67</v>
-      </c>
-      <c r="N1" s="88" t="s">
-        <v>68</v>
       </c>
       <c r="O1" s="73"/>
       <c r="P1" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="75" t="s">
-        <v>70</v>
+      <c r="R1" s="91" t="s">
+        <v>156</v>
       </c>
-      <c r="R1" s="88" t="s">
-        <v>157</v>
-      </c>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="107" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="104" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="66" t="s">
@@ -38029,28 +38026,28 @@
       </c>
       <c r="E2" s="72"/>
       <c r="F2" s="68"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
       <c r="O2" s="73"/>
-      <c r="P2" s="76"/>
+      <c r="P2" s="79"/>
       <c r="Q2" s="75"/>
       <c r="R2" s="100" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
-      <c r="S2" s="88" t="s">
+      <c r="S2" s="91" t="s">
+        <v>157</v>
+      </c>
+      <c r="T2" s="91"/>
+      <c r="U2" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88" t="s">
-        <v>159</v>
-      </c>
-      <c r="V2" s="88"/>
+      <c r="V2" s="91"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="71"/>
@@ -38063,41 +38060,41 @@
         <v>1</v>
       </c>
       <c r="F3" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="H3" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="I3" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="I3" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="J3" s="99"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
       <c r="N3" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O3" s="43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P3" s="71"/>
       <c r="Q3" s="75"/>
       <c r="R3" s="100"/>
       <c r="S3" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="T3" s="40" t="s">
-        <v>75</v>
-      </c>
       <c r="U3" s="34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V3" s="34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -42904,11 +42901,6 @@
   <sheetProtection algorithmName="SHA-512" hashValue="lB47MHjN7Q2DdsILtEIzmsVgF/RGH4fl4xMJSJCt+pfGM3g82GbEDtt7bi2H3b59LuCUpowHsRtb+ERWIIPhnQ==" saltValue="jdC1iYmDqqf8XUqPiuEltA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:T2"/>
@@ -42921,6 +42913,11 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="P1:P3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K3 I3 F3 G3 H3 U3 V3" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -42959,22 +42956,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="32" t="s">
-        <v>60</v>
-      </c>
       <c r="C1" s="32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -44613,26 +44610,26 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="C1" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="97" t="s">
-        <v>162</v>
+      <c r="D1" s="76" t="s">
+        <v>161</v>
       </c>
       <c r="E1" s="108" t="s">
         <v>57</v>
       </c>
       <c r="F1" s="109"/>
-      <c r="G1" s="97" t="s">
-        <v>164</v>
+      <c r="G1" s="76" t="s">
+        <v>163</v>
       </c>
       <c r="H1" s="70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I1" s="66" t="s">
         <v>35</v>
@@ -44644,23 +44641,23 @@
       <c r="A2" s="71"/>
       <c r="B2" s="71"/>
       <c r="C2" s="71"/>
-      <c r="D2" s="99"/>
+      <c r="D2" s="78"/>
       <c r="E2" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="99"/>
+      <c r="G2" s="78"/>
       <c r="H2" s="71"/>
       <c r="I2" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J2" s="52" t="s">
         <v>36</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -11,7 +11,7 @@
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCD133D-7224-4E04-93EA-25A03D08B21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="5" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -1205,6 +1205,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1281,14 +1289,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1301,6 +1301,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1310,9 +1313,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2012,15 +2012,15 @@
       <c r="D1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="E1" s="80" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="85" t="s">
+      <c r="F1" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
       <c r="J1" s="99" t="s">
         <v>170</v>
       </c>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="O1" s="99"/>
       <c r="P1" s="99"/>
-      <c r="Q1" s="75" t="s">
+      <c r="Q1" s="77" t="s">
         <v>38</v>
       </c>
       <c r="R1" s="72" t="s">
@@ -2050,7 +2050,7 @@
       <c r="B2" s="110"/>
       <c r="C2" s="110"/>
       <c r="D2" s="110"/>
-      <c r="E2" s="80"/>
+      <c r="E2" s="82"/>
       <c r="F2" s="36" t="s">
         <v>19</v>
       </c>
@@ -2084,7 +2084,7 @@
       <c r="P2" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="Q2" s="77"/>
+      <c r="Q2" s="79"/>
       <c r="R2" s="38" t="s">
         <v>53</v>
       </c>
@@ -6904,17 +6904,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F0tc7B77v7QjLsOz0RLL7MWtNCPBw2o4Z9f2YID1JxL/5n/IHv5nh1k9azF4NV4h1VsWAZfQTfWlFcYB76PlMA==" saltValue="n01OBaL5NKfbkpK2LmYd9A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 J2 L2 N2 Q1:Q2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
@@ -6974,19 +6974,19 @@
       <c r="D1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="77" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="77" t="s">
         <v>173</v>
       </c>
       <c r="H1" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="78" t="s">
         <v>174</v>
       </c>
       <c r="J1" s="111" t="s">
@@ -7001,13 +7001,13 @@
       <c r="B2" s="110"/>
       <c r="C2" s="110"/>
       <c r="D2" s="110"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -9612,17 +9612,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7AjhL+fqXAsFucLZgoF2uPzgppBK+T/XTUzkX/JwpgqEiyXl3lYNCR44gk+4O6ySKgm58zlH7twzGxSoUOj8WQ==" saltValue="905c+jUO58aUTtAhHe6Qyg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 G1:G2 I1:I2 E1:E2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -19614,84 +19614,84 @@
       <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="94" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="95"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="75" t="s">
+      <c r="H1" s="97"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="77" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="78" t="s">
+      <c r="K1" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="82" t="s">
+      <c r="L1" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="84"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="86"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
+      <c r="A2" s="83"/>
       <c r="B2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="C2" s="94" t="s">
         <v>178</v>
       </c>
       <c r="D2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="87" t="s">
+      <c r="E2" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="93" t="s">
+      <c r="F2" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="89" t="s">
+      <c r="G2" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="90" t="s">
+      <c r="H2" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="75" t="s">
         <v>179</v>
       </c>
-      <c r="J2" s="76"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="85" t="s">
+      <c r="J2" s="78"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85" t="s">
+      <c r="M2" s="87"/>
+      <c r="N2" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="O2" s="85"/>
-      <c r="P2" s="86" t="s">
+      <c r="O2" s="87"/>
+      <c r="P2" s="88" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="70"/>
       <c r="B3" s="62"/>
-      <c r="C3" s="92"/>
+      <c r="C3" s="94"/>
       <c r="D3" s="62"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="80"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="82"/>
       <c r="L3" s="32" t="s">
         <v>3</v>
       </c>
@@ -19704,7 +19704,7 @@
       <c r="O3" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="P3" s="86"/>
+      <c r="P3" s="88"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -23309,6 +23309,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Hbw1kM2GZdKiXn+tZ2jTENxb+s/WuKBOS35p7Hczzc8mzknealDwavQKvnmoI0NQ4e6Cl68C/s3alEC/HGJgTQ==" saltValue="phbtvlo1TeohYtjp0VwRjg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="G1:I1"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="K1:K3"/>
@@ -23325,7 +23326,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -23373,23 +23373,23 @@
       <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85" t="s">
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
+      <c r="A2" s="83"/>
       <c r="B2" s="65" t="s">
         <v>99</v>
       </c>
@@ -26163,14 +26163,14 @@
       <c r="AO1" s="74"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="87" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="89" t="s">
         <v>181</v>
       </c>
       <c r="C2" s="100" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="77" t="s">
         <v>116</v>
       </c>
       <c r="E2" s="99" t="s">
@@ -26186,21 +26186,21 @@
       <c r="K2" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="93" t="s">
+      <c r="L2" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
       <c r="P2" s="99" t="s">
         <v>124</v>
       </c>
       <c r="Q2" s="99"/>
       <c r="R2" s="99"/>
-      <c r="S2" s="93" t="s">
+      <c r="S2" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="93"/>
+      <c r="T2" s="95"/>
       <c r="U2" s="99" t="s">
         <v>128</v>
       </c>
@@ -26240,28 +26240,28 @@
       <c r="AG2" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="93" t="s">
+      <c r="AH2" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="AI2" s="93"/>
-      <c r="AJ2" s="93" t="s">
+      <c r="AI2" s="95"/>
+      <c r="AJ2" s="95" t="s">
         <v>139</v>
       </c>
-      <c r="AK2" s="93"/>
-      <c r="AL2" s="93" t="s">
+      <c r="AK2" s="95"/>
+      <c r="AL2" s="95" t="s">
         <v>140</v>
       </c>
-      <c r="AM2" s="93"/>
-      <c r="AN2" s="93" t="s">
+      <c r="AM2" s="95"/>
+      <c r="AN2" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="AO2" s="93"/>
+      <c r="AO2" s="95"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="70"/>
-      <c r="B3" s="88"/>
+      <c r="B3" s="90"/>
       <c r="C3" s="67"/>
-      <c r="D3" s="77"/>
+      <c r="D3" s="79"/>
       <c r="E3" s="40" t="s">
         <v>20</v>
       </c>
@@ -34949,6 +34949,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="QMCtlxTdGMeqat8mqK+Cr1Fx43bg5wNSEIC6CaFaY0KIvb4EIpIjm6obel/9Z0Dv1oF2vEXJtDbPbO1sewkcAA==" saltValue="PmNUggfK+1j4qc6GrFpb8Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="X2:X3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -34965,20 +34979,6 @@
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="AN2:AO2"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3 D2:D3 L3 M3 N3 O3 P3 Q3 R3 AH3 AI3 AJ3 AK3 AL3 AM3 AO3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35043,55 +35043,55 @@
       <c r="L1" s="74"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="93" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="93" t="s">
+      <c r="D2" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93" t="s">
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="81"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93" t="s">
+      <c r="A3" s="83"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93" t="s">
+      <c r="E3" s="95"/>
+      <c r="F3" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93" t="s">
+      <c r="G3" s="95"/>
+      <c r="H3" s="95" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93" t="s">
+      <c r="I3" s="95"/>
+      <c r="J3" s="95" t="s">
         <v>147</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="70"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="46" t="s">
         <v>18</v>
       </c>
@@ -37981,22 +37981,22 @@
       <c r="F1" s="100" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="78" t="s">
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="105" t="s">
+      <c r="K1" s="106" t="s">
         <v>155</v>
       </c>
-      <c r="L1" s="93" t="s">
+      <c r="L1" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="93" t="s">
+      <c r="M1" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="93" t="s">
+      <c r="N1" s="95" t="s">
         <v>67</v>
       </c>
       <c r="O1" s="72"/>
@@ -38006,18 +38006,18 @@
       <c r="Q1" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="93" t="s">
+      <c r="R1" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="93"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="106" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="103" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="65" t="s">
@@ -38025,28 +38025,28 @@
       </c>
       <c r="E2" s="71"/>
       <c r="F2" s="67"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
       <c r="O2" s="72"/>
-      <c r="P2" s="81"/>
+      <c r="P2" s="83"/>
       <c r="Q2" s="74"/>
       <c r="R2" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="93" t="s">
+      <c r="S2" s="95" t="s">
         <v>157</v>
       </c>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93" t="s">
+      <c r="T2" s="95"/>
+      <c r="U2" s="95" t="s">
         <v>158</v>
       </c>
-      <c r="V2" s="93"/>
+      <c r="V2" s="95"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="70"/>
@@ -38070,10 +38070,10 @@
       <c r="I3" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="J3" s="80"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
       <c r="N3" s="37" t="s">
         <v>71</v>
       </c>
@@ -42900,11 +42900,6 @@
   <sheetProtection algorithmName="SHA-512" hashValue="lB47MHjN7Q2DdsILtEIzmsVgF/RGH4fl4xMJSJCt+pfGM3g82GbEDtt7bi2H3b59LuCUpowHsRtb+ERWIIPhnQ==" saltValue="jdC1iYmDqqf8XUqPiuEltA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:T2"/>
@@ -42917,6 +42912,11 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="P1:P3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K3 I3 F3 G3 H3 U3 V3" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -44617,14 +44617,14 @@
       <c r="C1" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="80" t="s">
         <v>161</v>
       </c>
       <c r="E1" s="107" t="s">
         <v>57</v>
       </c>
       <c r="F1" s="108"/>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="80" t="s">
         <v>163</v>
       </c>
       <c r="H1" s="69" t="s">
@@ -44640,14 +44640,14 @@
       <c r="A2" s="70"/>
       <c r="B2" s="70"/>
       <c r="C2" s="70"/>
-      <c r="D2" s="80"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="80"/>
+      <c r="G2" s="82"/>
       <c r="H2" s="70"/>
       <c r="I2" s="39" t="s">
         <v>164</v>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCD133D-7224-4E04-93EA-25A03D08B21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D5E3E8-453B-4A2C-AF46-C5CD0E8D6358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="5" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="1" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -1133,6 +1133,27 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1187,23 +1208,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1236,9 +1251,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1278,18 +1290,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1301,9 +1301,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1313,6 +1310,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1666,24 +1666,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="64"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
@@ -1733,15 +1733,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="58"/>
+      <c r="D8" s="65"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="58"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,11 +1923,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="61"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="68"/>
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2012,15 +2012,15 @@
       <c r="D1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="91" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
       <c r="J1" s="99" t="s">
         <v>170</v>
       </c>
@@ -2032,25 +2032,25 @@
       </c>
       <c r="O1" s="99"/>
       <c r="P1" s="99"/>
-      <c r="Q1" s="77" t="s">
+      <c r="Q1" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="72" t="s">
+      <c r="R1" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="74"/>
-      <c r="T1" s="72" t="s">
+      <c r="S1" s="54"/>
+      <c r="T1" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="U1" s="73"/>
-      <c r="V1" s="74"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="54"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="110"/>
       <c r="B2" s="110"/>
       <c r="C2" s="110"/>
       <c r="D2" s="110"/>
-      <c r="E2" s="82"/>
+      <c r="E2" s="87"/>
       <c r="F2" s="36" t="s">
         <v>19</v>
       </c>
@@ -2084,7 +2084,7 @@
       <c r="P2" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="Q2" s="79"/>
+      <c r="Q2" s="84"/>
       <c r="R2" s="38" t="s">
         <v>53</v>
       </c>
@@ -6904,17 +6904,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F0tc7B77v7QjLsOz0RLL7MWtNCPBw2o4Z9f2YID1JxL/5n/IHv5nh1k9azF4NV4h1VsWAZfQTfWlFcYB76PlMA==" saltValue="n01OBaL5NKfbkpK2LmYd9A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 J2 L2 N2 Q1:Q2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
@@ -6974,19 +6974,19 @@
       <c r="D1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="82" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="82" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="82" t="s">
         <v>173</v>
       </c>
       <c r="H1" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="78" t="s">
+      <c r="I1" s="83" t="s">
         <v>174</v>
       </c>
       <c r="J1" s="111" t="s">
@@ -7001,13 +7001,13 @@
       <c r="B2" s="110"/>
       <c r="C2" s="110"/>
       <c r="D2" s="110"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -9612,17 +9612,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7AjhL+fqXAsFucLZgoF2uPzgppBK+T/XTUzkX/JwpgqEiyXl3lYNCR44gk+4O6ySKgm58zlH7twzGxSoUOj8WQ==" saltValue="905c+jUO58aUTtAhHe6Qyg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 G1:G2 I1:I2 E1:E2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -14192,117 +14192,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62" t="s">
+      <c r="C1" s="69"/>
+      <c r="D1" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+      <c r="W1" s="69"/>
+      <c r="X1" s="69"/>
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="65" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
+      <c r="W2" s="69"/>
+      <c r="X2" s="69"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="67" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="68"/>
-      <c r="F3" s="63" t="s">
+      <c r="E3" s="75"/>
+      <c r="F3" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="69" t="s">
+      <c r="G3" s="71"/>
+      <c r="H3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="63" t="s">
+      <c r="J3" s="75"/>
+      <c r="K3" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="L3" s="64"/>
-      <c r="M3" s="69" t="s">
+      <c r="L3" s="71"/>
+      <c r="M3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="62" t="s">
+      <c r="N3" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62" t="s">
+      <c r="O3" s="69"/>
+      <c r="P3" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="72" t="s">
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="74"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="54"/>
     </row>
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="32" t="s">
         <v>79</v>
       </c>
@@ -14321,7 +14321,7 @@
       <c r="G4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="70"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="31" t="s">
         <v>101</v>
       </c>
@@ -14334,7 +14334,7 @@
       <c r="L4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="70"/>
+      <c r="M4" s="57"/>
       <c r="N4" s="32" t="s">
         <v>5</v>
       </c>
@@ -19546,7 +19546,7 @@
       <c r="X203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fVXWKxCR1qucAQa6utO/4fH1F9wUY8AODxxzlBRDtPgG4CCzIk4q2AsxwP756/R3QOL3Tba6UWhQjPmYXErNnw==" saltValue="wSFRtfCqKPzFlyH4k1jV2Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="46cFSM56bLsmreV25TOiQafDrffmltOeOr94Dy1gL5MIFPqeCQ/DibKgaNfsqxG+JnG4jGVm0+m2KMmbRCGwkA==" saltValue="GjrQooXRWNGpm6VKJS3d+A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="N3:O3"/>
@@ -19565,7 +19565,7 @@
     <mergeCell ref="U3:X3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5 W4 D4 E4 I4 J4 U4 V4 X4" xr:uid="{90961E5D-833B-4418-801E-6853BBBDB445}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X4 W4 D4 E4 I4 J4 U4 V4" xr:uid="{90961E5D-833B-4418-801E-6853BBBDB445}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19611,87 +19611,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="96" t="s">
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="97"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="77" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="82" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="80" t="s">
+      <c r="K1" s="85" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="84" t="s">
+      <c r="L1" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="86"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="90"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="62" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="98" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="89" t="s">
+      <c r="E2" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="95" t="s">
+      <c r="F2" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="91" t="s">
+      <c r="G2" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="92" t="s">
+      <c r="H2" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="87" t="s">
+      <c r="J2" s="83"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="91" t="s">
         <v>111</v>
       </c>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87" t="s">
+      <c r="M2" s="91"/>
+      <c r="N2" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="O2" s="87"/>
-      <c r="P2" s="88" t="s">
+      <c r="O2" s="91"/>
+      <c r="P2" s="92" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="82"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="87"/>
       <c r="L3" s="32" t="s">
         <v>3</v>
       </c>
@@ -19704,7 +19704,7 @@
       <c r="O3" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="P3" s="88"/>
+      <c r="P3" s="92"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -23309,11 +23309,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Hbw1kM2GZdKiXn+tZ2jTENxb+s/WuKBOS35p7Hczzc8mzknealDwavQKvnmoI0NQ4e6Cl68C/s3alEC/HGJgTQ==" saltValue="phbtvlo1TeohYtjp0VwRjg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K3"/>
-    <mergeCell ref="A1:A3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:P3"/>
@@ -23326,6 +23321,11 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="A1:A3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -23370,47 +23370,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="65" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="69" t="s">
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="69" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="55" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
+      <c r="A3" s="57"/>
       <c r="B3" s="31" t="s">
         <v>101</v>
       </c>
@@ -23423,7 +23423,7 @@
       <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="70"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="31" t="s">
         <v>101</v>
       </c>
@@ -23436,7 +23436,7 @@
       <c r="J3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="70"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -26112,65 +26112,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="72" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="74"/>
-      <c r="AH1" s="72" t="s">
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="AI1" s="73"/>
-      <c r="AJ1" s="73"/>
-      <c r="AK1" s="73"/>
-      <c r="AL1" s="73"/>
-      <c r="AM1" s="73"/>
-      <c r="AN1" s="73"/>
-      <c r="AO1" s="74"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="54"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="89" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="93" t="s">
         <v>181</v>
       </c>
       <c r="C2" s="100" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="82" t="s">
         <v>116</v>
       </c>
       <c r="E2" s="99" t="s">
@@ -26186,21 +26186,21 @@
       <c r="K2" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="95" t="s">
+      <c r="L2" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
       <c r="P2" s="99" t="s">
         <v>124</v>
       </c>
       <c r="Q2" s="99"/>
       <c r="R2" s="99"/>
-      <c r="S2" s="95" t="s">
+      <c r="S2" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="95"/>
+      <c r="T2" s="58"/>
       <c r="U2" s="99" t="s">
         <v>128</v>
       </c>
@@ -26240,28 +26240,28 @@
       <c r="AG2" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="95" t="s">
+      <c r="AH2" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="95" t="s">
+      <c r="AI2" s="58"/>
+      <c r="AJ2" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="AK2" s="95"/>
-      <c r="AL2" s="95" t="s">
+      <c r="AK2" s="58"/>
+      <c r="AL2" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="AM2" s="95"/>
-      <c r="AN2" s="95" t="s">
+      <c r="AM2" s="58"/>
+      <c r="AN2" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="AO2" s="95"/>
+      <c r="AO2" s="58"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="79"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="40" t="s">
         <v>20</v>
       </c>
@@ -34949,20 +34949,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="QMCtlxTdGMeqat8mqK+Cr1Fx43bg5wNSEIC6CaFaY0KIvb4EIpIjm6obel/9Z0Dv1oF2vEXJtDbPbO1sewkcAA==" saltValue="PmNUggfK+1j4qc6GrFpb8Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="X2:X3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -34979,6 +34965,20 @@
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="AN2:AO2"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3 D2:D3 L3 M3 N3 O3 P3 Q3 R3 AH3 AI3 AJ3 AK3 AL3 AM3 AO3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35023,75 +35023,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="72" t="s">
+      <c r="C1" s="54"/>
+      <c r="D1" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="74"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="95" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95" t="s">
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95" t="s">
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95" t="s">
+      <c r="A3" s="56"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95" t="s">
+      <c r="E3" s="58"/>
+      <c r="F3" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95" t="s">
+      <c r="I3" s="58"/>
+      <c r="J3" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
+      <c r="A4" s="57"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
       <c r="D4" s="46" t="s">
         <v>18</v>
       </c>
@@ -37967,91 +37967,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="72" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="71"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="76"/>
       <c r="F1" s="100" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="80" t="s">
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="106" t="s">
+      <c r="K1" s="105" t="s">
         <v>155</v>
       </c>
-      <c r="L1" s="95" t="s">
+      <c r="L1" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="95" t="s">
+      <c r="M1" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="95" t="s">
+      <c r="N1" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="72"/>
-      <c r="P1" s="69" t="s">
+      <c r="O1" s="52"/>
+      <c r="P1" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" s="74" t="s">
+      <c r="Q1" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="95" t="s">
+      <c r="R1" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="103" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="74"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="54"/>
       <c r="R2" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="95" t="s">
+      <c r="S2" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95" t="s">
+      <c r="T2" s="58"/>
+      <c r="U2" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="V2" s="95"/>
+      <c r="V2" s="58"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="63"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="70"/>
       <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
@@ -38070,18 +38070,18 @@
       <c r="I3" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="J3" s="82"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
       <c r="N3" s="37" t="s">
         <v>71</v>
       </c>
       <c r="O3" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="74"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="54"/>
       <c r="R3" s="99"/>
       <c r="S3" s="40" t="s">
         <v>73</v>
@@ -42900,6 +42900,11 @@
   <sheetProtection algorithmName="SHA-512" hashValue="lB47MHjN7Q2DdsILtEIzmsVgF/RGH4fl4xMJSJCt+pfGM3g82GbEDtt7bi2H3b59LuCUpowHsRtb+ERWIIPhnQ==" saltValue="jdC1iYmDqqf8XUqPiuEltA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:T2"/>
@@ -42912,11 +42917,6 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K3 I3 F3 G3 H3 U3 V3" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -44608,47 +44608,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="85" t="s">
         <v>161</v>
       </c>
       <c r="E1" s="107" t="s">
         <v>57</v>
       </c>
       <c r="F1" s="108"/>
-      <c r="G1" s="80" t="s">
+      <c r="G1" s="85" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="66"/>
-      <c r="K1" s="71"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="76"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="82"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="87"/>
       <c r="E2" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="70"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="57"/>
       <c r="I2" s="39" t="s">
         <v>164</v>
       </c>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CD2C99-E983-3C43-B5AE-6D8B9309DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE63883-4D61-D34E-B6FE-8123EF3F31A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" tabRatio="879" firstSheet="5" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="13160" yWindow="740" windowWidth="16240" windowHeight="16680" tabRatio="879" firstSheet="10" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -1121,6 +1121,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1191,6 +1194,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1274,9 +1280,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1289,9 +1292,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1301,6 +1301,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1316,9 +1319,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1657,24 +1657,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="57"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="7"/>
@@ -1724,15 +1724,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="13"/>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="57"/>
+      <c r="D8" s="58"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="57" t="s">
+      <c r="F8" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="57"/>
+      <c r="G8" s="58"/>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -1843,7 +1843,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
-      <c r="C19" s="111" t="s">
+      <c r="C19" s="51" t="s">
         <v>91</v>
       </c>
       <c r="D19" s="23"/>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="13"/>
-      <c r="C20" s="111" t="s">
+      <c r="C20" s="51" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="23"/>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="13"/>
-      <c r="C21" s="111" t="s">
+      <c r="C21" s="51" t="s">
         <v>92</v>
       </c>
       <c r="D21" s="23"/>
@@ -1914,11 +1914,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="13"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="60"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="61"/>
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -1991,57 +1991,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="94" t="s">
+      <c r="E1" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="98" t="s">
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="99" t="s">
         <v>170</v>
       </c>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98" t="s">
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="91" t="s">
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="71" t="s">
+      <c r="R1" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="73"/>
-      <c r="T1" s="71" t="s">
+      <c r="S1" s="74"/>
+      <c r="T1" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="U1" s="72"/>
-      <c r="V1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="74"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="109"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="96"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="98"/>
       <c r="F2" s="35" t="s">
         <v>19</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="P2" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="Q2" s="93"/>
+      <c r="Q2" s="95"/>
       <c r="R2" s="37" t="s">
         <v>53</v>
       </c>
@@ -6893,19 +6893,19 @@
       <c r="V202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TDZ1Wnw7HxbzIsDdR0hujcwULW+Y5BQa8vWRrKgtSQmsHFEOywBaR5rZwgPD7EZZ//BPqjX8bdvqso0mge1MbQ==" saltValue="WEcr+aUYjI1gj0u8t2tapQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BTexII7owVy7UQbHfXi/pyJQyZY+TVM2NUjbJHtKkRwH9qU3D0asKSbCPlNE3BE//D65VD7VqTSzNJRUsWzKQw==" saltValue="9Bv0Uc7e1ZSaTefnMGuLyA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 J2 L2 N2 Q1:Q2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
@@ -6953,52 +6953,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="91" t="s">
+      <c r="E1" s="93" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="91" t="s">
+      <c r="F1" s="93" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="110" t="s">
+      <c r="H1" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="92" t="s">
+      <c r="I1" s="94" t="s">
         <v>174</v>
       </c>
-      <c r="J1" s="110" t="s">
+      <c r="J1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="110" t="s">
+      <c r="K1" s="111" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="109"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
@@ -9601,19 +9601,19 @@
       <c r="K202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="twrMROuzpJOsQY/6ad5TVgDasexs4qjkp/OGna1A5v0C1Ud6aAU9bfxdkS+572j/32/u/2cJYQBGDqg665OEZA==" saltValue="c6VL/CbE9nQMbWkkqKolfw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/i8ttRawHFE0bDsLHk0X3DAZnREwIVUNut+wCnlTtUXkhO/z6EY5v2kRXopEus0UfjIHrMc29E3tZKRlwPN6dQ==" saltValue="ZTcyu138evLLcD0f3mUgnw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 G1:G2 I1:I2 E1:E2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -12488,7 +12488,7 @@
       <c r="L201" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="y0C7I7v0RqbKlmBWNVuDVUaMuyID/fTPcTWCMtZ1d4gET20TYqW9yrFw/c023xDIHsCoMkKPJq/Ikiiu6brlYQ==" saltValue="zChWOL15tO+m+oMpk3oa8w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="atCsfaQ/Wqa05oY0/VI6TFi+I2NXWNTJgSm76H37XWGla1PXU95wuw4Y7lxV3gUUgepEXdCeLWyl2wtd/jFNBQ==" saltValue="bBGMR4jLd0WwJNjJRc35BQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -14138,7 +14138,7 @@
       <c r="F201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GgmkDoCG3msrwr5f3FgBA2iitCKqcE2pzflAdZIUYO+mUrZnCxwhXHJcANJ+mtgViCp9iekdIDTiw4fMePAy6w==" saltValue="L1wm4S525pg+l9V7Bm79Sw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{A7F07E3F-7588-4A6B-9139-C33F06BE5D6F}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -14183,117 +14183,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61" t="s">
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
-      <c r="W1" s="61"/>
-      <c r="X1" s="61"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="64" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="64" t="s">
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="66" t="s">
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="67"/>
-      <c r="F3" s="62" t="s">
+      <c r="E3" s="68"/>
+      <c r="F3" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="68" t="s">
+      <c r="G3" s="64"/>
+      <c r="H3" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="66" t="s">
+      <c r="I3" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="J3" s="67"/>
-      <c r="K3" s="62" t="s">
+      <c r="J3" s="68"/>
+      <c r="K3" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="L3" s="63"/>
-      <c r="M3" s="68" t="s">
+      <c r="L3" s="64"/>
+      <c r="M3" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="61" t="s">
+      <c r="N3" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="O3" s="61"/>
-      <c r="P3" s="61" t="s">
+      <c r="O3" s="62"/>
+      <c r="P3" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="61"/>
-      <c r="U3" s="71" t="s">
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="74"/>
     </row>
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="61"/>
+      <c r="A4" s="62"/>
       <c r="B4" s="31" t="s">
         <v>79</v>
       </c>
@@ -14312,7 +14312,7 @@
       <c r="G4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="69"/>
+      <c r="H4" s="70"/>
       <c r="I4" s="30" t="s">
         <v>101</v>
       </c>
@@ -14325,7 +14325,7 @@
       <c r="L4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="69"/>
+      <c r="M4" s="70"/>
       <c r="N4" s="31" t="s">
         <v>5</v>
       </c>
@@ -19537,7 +19537,7 @@
       <c r="X203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OQf7dEodnoyZE+n4KmJ1ecGinbEhrIl1FaqyWrUQR+BR06ZQZnFjdrvcGnDDHsTR8X1F44LracBHsMixYOQHEg==" saltValue="oundXDzR508srUQkzF1jng==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OX7GrxYBmDfUfGIrcwfDd5IGVdwAAAWfk0+59K9FBJAXwWKCUKsXmbDZw/6vwhU06ZqEo49vAi9qELR2JF48pw==" saltValue="eV0DDzoKy3HLgjvIF+sk3g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="N3:O3"/>
@@ -19602,87 +19602,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="86" t="s">
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="91" t="s">
+      <c r="H1" s="89"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="93" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="94" t="s">
+      <c r="K1" s="96" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="74" t="s">
+      <c r="L1" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="76"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="78"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="97"/>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="82" t="s">
+      <c r="H2" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="91" t="s">
         <v>179</v>
       </c>
-      <c r="J2" s="92"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="77" t="s">
+      <c r="J2" s="94"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77" t="s">
+      <c r="M2" s="79"/>
+      <c r="N2" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78" t="s">
+      <c r="O2" s="79"/>
+      <c r="P2" s="80" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="69"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="96"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="98"/>
       <c r="L3" s="31" t="s">
         <v>3</v>
       </c>
@@ -19695,7 +19695,7 @@
       <c r="O3" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="P3" s="78"/>
+      <c r="P3" s="80"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -23298,8 +23298,9 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+W9g6qSIHynTg0TqYCeXecw49/I5FE8DfSKFNeZFZjcWbPhA45vdCUcLpf/9/3YdGQiSuv1y7uhGGFr9XOMCwQ==" saltValue="HzFjR1vn3WI0/R0SM3gRqQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ypyoobc0IMiFdv0nKqzOh3acPZcndwCUBsTgOroSOIeoClJWdTuY3LtW7nXX7TL0JoutT2WJDIW3JVWK87zuUw==" saltValue="s+CLOox3+O9kbG7AiXx2bQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="K1:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
@@ -23316,7 +23317,6 @@
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -23361,47 +23361,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77" t="s">
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="97"/>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="68" t="s">
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="68" t="s">
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="69" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="69"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="30" t="s">
         <v>101</v>
       </c>
@@ -23414,7 +23414,7 @@
       <c r="E3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="69"/>
+      <c r="F3" s="70"/>
       <c r="G3" s="30" t="s">
         <v>101</v>
       </c>
@@ -23427,7 +23427,7 @@
       <c r="J3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="69"/>
+      <c r="K3" s="70"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -26030,7 +26030,7 @@
       <c r="K203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3SjN4YGB0noxXRUGTCjXeeSir29Bbvw2J29Rodir9SZAdKos9d9MfzFHI7dl9nCcGcMapB75lpr+YmLSHGiOwA==" saltValue="fCiBEWwohi6JYhmLvXAo8A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CiF+XI5+gclt/XuwcbcQ2oiMG9gliHmMz0UxdJsKdDNqWC80JzqMjaWq6XyyCm3dZFTP9hrYXoffWtCFCGWsew==" saltValue="kZROxBoU8+eOL2e3t272+Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:F1"/>
@@ -26103,156 +26103,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="71" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="71" t="s">
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
-      <c r="AM1" s="72"/>
-      <c r="AN1" s="72"/>
-      <c r="AO1" s="73"/>
+      <c r="AI1" s="73"/>
+      <c r="AJ1" s="73"/>
+      <c r="AK1" s="73"/>
+      <c r="AL1" s="73"/>
+      <c r="AM1" s="73"/>
+      <c r="AN1" s="73"/>
+      <c r="AO1" s="74"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="97"/>
-      <c r="B2" s="79" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="81" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="91" t="s">
+      <c r="D2" s="93" t="s">
         <v>116</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E2" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98" t="s">
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="100" t="s">
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="85" t="s">
+      <c r="L2" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="98" t="s">
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="99" t="s">
         <v>124</v>
       </c>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="85" t="s">
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="85"/>
-      <c r="U2" s="98" t="s">
+      <c r="T2" s="87"/>
+      <c r="U2" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="V2" s="98" t="s">
+      <c r="V2" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="98" t="s">
+      <c r="W2" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="98" t="s">
+      <c r="X2" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="98" t="s">
+      <c r="Y2" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="98" t="s">
+      <c r="Z2" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="98" t="s">
+      <c r="AA2" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="98" t="s">
+      <c r="AB2" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="98" t="s">
+      <c r="AC2" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="98" t="s">
+      <c r="AD2" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="98" t="s">
+      <c r="AE2" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="98" t="s">
+      <c r="AF2" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="98" t="s">
+      <c r="AG2" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="85" t="s">
+      <c r="AH2" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="AI2" s="85"/>
-      <c r="AJ2" s="85" t="s">
+      <c r="AI2" s="87"/>
+      <c r="AJ2" s="87" t="s">
         <v>139</v>
       </c>
-      <c r="AK2" s="85"/>
-      <c r="AL2" s="85" t="s">
+      <c r="AK2" s="87"/>
+      <c r="AL2" s="87" t="s">
         <v>140</v>
       </c>
-      <c r="AM2" s="85"/>
-      <c r="AN2" s="85" t="s">
+      <c r="AM2" s="87"/>
+      <c r="AN2" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="AO2" s="85"/>
+      <c r="AO2" s="87"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A3" s="69"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="93"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="95"/>
       <c r="E3" s="39" t="s">
         <v>20</v>
       </c>
@@ -26271,7 +26271,7 @@
       <c r="J3" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="K3" s="101"/>
+      <c r="K3" s="102"/>
       <c r="L3" s="30" t="s">
         <v>119</v>
       </c>
@@ -26299,19 +26299,19 @@
       <c r="T3" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="U3" s="98"/>
-      <c r="V3" s="98"/>
-      <c r="W3" s="98"/>
-      <c r="X3" s="98"/>
-      <c r="Y3" s="98"/>
-      <c r="Z3" s="98"/>
-      <c r="AA3" s="98"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="98"/>
-      <c r="AD3" s="98"/>
-      <c r="AE3" s="98"/>
-      <c r="AF3" s="98"/>
-      <c r="AG3" s="98"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99"/>
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="99"/>
+      <c r="AA3" s="99"/>
+      <c r="AB3" s="99"/>
+      <c r="AC3" s="99"/>
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="99"/>
+      <c r="AG3" s="99"/>
       <c r="AH3" s="41" t="s">
         <v>130</v>
       </c>
@@ -34938,22 +34938,8 @@
       <c r="AO203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9FVytzHoG+zFCCIl7lSocfUaHC8Fmfxgk5WKgEGxf/4h6yTJwtWAu00apGs3B+jzfmJKn8wV6yaTpotfcftl6A==" saltValue="Wfy9RK7QITfAJS/eTGpo7A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="j1EowgYHCEOA0SF1kqoB+dQTybyCCq9EPPslVGHQc3yhm1IPYeAMkjIiI1oNkUYexZxa+Yeg5+STpW3jf+91FA==" saltValue="e5x8kCdm0wv7SScaGKq6Bg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="X2:X3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -34970,6 +34956,20 @@
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="AN2:AO2"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3 D2:D3 L3 M3 N3 O3 P3 Q3 R3 AH3 AI3 AJ3 AK3 AL3 AM3 AO3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -35014,75 +35014,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="72" t="s">
         <v>144</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="71" t="s">
+      <c r="C1" s="74"/>
+      <c r="D1" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="74"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="97"/>
-      <c r="B2" s="85" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87" t="s">
         <v>146</v>
       </c>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85" t="s">
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="97"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85" t="s">
+      <c r="A3" s="75"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85" t="s">
+      <c r="E3" s="87"/>
+      <c r="F3" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85" t="s">
+      <c r="G3" s="87"/>
+      <c r="H3" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85" t="s">
+      <c r="I3" s="87"/>
+      <c r="J3" s="87" t="s">
         <v>147</v>
       </c>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="69"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
       <c r="D4" s="45" t="s">
         <v>18</v>
       </c>
@@ -37958,91 +37958,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="65"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="99" t="s">
+      <c r="D1" s="66"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="100" t="s">
         <v>150</v>
       </c>
       <c r="G1" s="103"/>
       <c r="H1" s="103"/>
       <c r="I1" s="103"/>
-      <c r="J1" s="94" t="s">
+      <c r="J1" s="96" t="s">
         <v>77</v>
       </c>
       <c r="K1" s="105" t="s">
         <v>155</v>
       </c>
-      <c r="L1" s="85" t="s">
+      <c r="L1" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="85" t="s">
+      <c r="M1" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="85" t="s">
+      <c r="N1" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="71"/>
-      <c r="P1" s="68" t="s">
+      <c r="O1" s="72"/>
+      <c r="P1" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" s="73" t="s">
+      <c r="Q1" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="85" t="s">
+      <c r="R1" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="102" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="66"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="67"/>
       <c r="G2" s="104"/>
       <c r="H2" s="104"/>
       <c r="I2" s="104"/>
-      <c r="J2" s="95"/>
+      <c r="J2" s="97"/>
       <c r="K2" s="105"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="98" t="s">
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="85" t="s">
+      <c r="S2" s="87" t="s">
         <v>157</v>
       </c>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85" t="s">
+      <c r="T2" s="87"/>
+      <c r="U2" s="87" t="s">
         <v>158</v>
       </c>
-      <c r="V2" s="85"/>
+      <c r="V2" s="87"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="69"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="62"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="63"/>
       <c r="D3" s="31" t="s">
         <v>0</v>
       </c>
@@ -38061,19 +38061,19 @@
       <c r="I3" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="J3" s="96"/>
+      <c r="J3" s="98"/>
       <c r="K3" s="105"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
       <c r="N3" s="36" t="s">
         <v>71</v>
       </c>
       <c r="O3" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="98"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="99"/>
       <c r="S3" s="39" t="s">
         <v>73</v>
       </c>
@@ -42888,9 +42888,14 @@
       <c r="V203" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qKD4vd4h24fKnrHB7u2RRGrmrEVifAJW0C6nAOktU9xhRMem+Ss6T4HYKfYwm9V7eoYh+OhynTDJrZoV8yqVlQ==" saltValue="J4AWLl7l9tYOydYnDbQZng==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SUEhtek1xjdHrbhxzS10tklKE6LDK3INEq0x/apGRQZ4wd8qhkNkaK2pjf/Dc5DheFyyovwYwOOIRWqRZcbsIA==" saltValue="mUomoVIUflQXJbTqgskr3A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:T2"/>
@@ -42903,11 +42908,6 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K3 I3 F3 G3 H3 U3 V3" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -44565,7 +44565,7 @@
       <c r="F201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="e1AkfKExnlIbkes80uFwXa/2oWS1bq6NRDq7kbrdpvAf9pFWCuR584OwDE3iwy1QjwSrKdNSvHqHNSRyvJjUrQ==" saltValue="nxdw0MlMQdOByQmFDg+cpA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="G6ZwYN709Jy1AWIWQxAxVplHZP5uP/NiiAIMHJ1doR9/7pTBWAVy2vieUW0vMIWYxyRbT7D7xiLCv9S3N8yYaQ==" saltValue="uuk0pmAMVaL17oFOYQ/XcQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{9A958104-A80B-4B1E-AB96-42BA504F7B3D}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -44599,47 +44599,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="94" t="s">
+      <c r="D1" s="96" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="107"/>
-      <c r="G1" s="94" t="s">
+      <c r="F1" s="108"/>
+      <c r="G1" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="I1" s="64" t="s">
+      <c r="I1" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="65"/>
-      <c r="K1" s="70"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="71"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="96"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="98"/>
       <c r="E2" s="38" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="96"/>
-      <c r="H2" s="69"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="70"/>
       <c r="I2" s="38" t="s">
         <v>164</v>
       </c>
@@ -47251,7 +47251,7 @@
       <c r="K202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JFuclsymJORKm7S11LGZtCiu9YOq5vDJHr7XWUdZwfLX81yieBeD9fwLCYvtdHExnHVfx0KoFAkm4uR9EHvuLA==" saltValue="Tz1W/Pn9imdqajr69bBJNw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="biM3hQ9dM1A5u/RxSB562TW4yxWEk6vulqv0tQSe2LcMaZZ1lcSXb0H68uZfOZMLAlgvdIThzGzJ5Wi4dVDVMw==" saltValue="EStA3YCmrX8SwBZvXPl2Xg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="D1:D2"/>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE63883-4D61-D34E-B6FE-8123EF3F31A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DE6AEF-7995-B64C-B764-9637601A340E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="13160" yWindow="740" windowWidth="16240" windowHeight="16680" tabRatio="879" firstSheet="10" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16380" tabRatio="879" firstSheet="1" activeTab="4" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -994,7 +994,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1319,6 +1319,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14138,7 +14141,7 @@
       <c r="F201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bSliHqJ5EQ8eQgeRA8sv66irJTtOSg2Dpyv1czukCBLCPP3mvckfqDxnsbMeTzr3ypfyirn8i1xOz/6LVG9EzQ==" saltValue="anAW88Zh6pNEamPd5ppVcw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{A7F07E3F-7588-4A6B-9139-C33F06BE5D6F}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -26192,43 +26195,43 @@
         <v>22</v>
       </c>
       <c r="T2" s="87"/>
-      <c r="U2" s="99" t="s">
+      <c r="U2" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="V2" s="99" t="s">
+      <c r="V2" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="99" t="s">
+      <c r="W2" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="99" t="s">
+      <c r="X2" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="99" t="s">
+      <c r="Y2" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="99" t="s">
+      <c r="Z2" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="99" t="s">
+      <c r="AA2" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="99" t="s">
+      <c r="AB2" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="99" t="s">
+      <c r="AC2" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="99" t="s">
+      <c r="AD2" s="112" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="99" t="s">
+      <c r="AE2" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="99" t="s">
+      <c r="AF2" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="99" t="s">
+      <c r="AG2" s="112" t="s">
         <v>33</v>
       </c>
       <c r="AH2" s="87" t="s">
@@ -26299,19 +26302,19 @@
       <c r="T3" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="99"/>
-      <c r="AC3" s="99"/>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="99"/>
-      <c r="AG3" s="99"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="112"/>
+      <c r="AA3" s="112"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="112"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="112"/>
       <c r="AH3" s="41" t="s">
         <v>130</v>
       </c>
@@ -34938,7 +34941,7 @@
       <c r="AO203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="j1EowgYHCEOA0SF1kqoB+dQTybyCCq9EPPslVGHQc3yhm1IPYeAMkjIiI1oNkUYexZxa+Yeg5+STpW3jf+91FA==" saltValue="e5x8kCdm0wv7SScaGKq6Bg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KMk8iFoN3zdbSamIO5QoI5vr+1ZauOEkrFW9jZqT8WXmnzjv2f5XRCKnMtp2ZZV6ao+qLTzPyt4DPIWOB9bWBA==" saltValue="6784kBKSj4D5BGLAkX4o/w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
@@ -34993,6 +34996,19 @@
     <hyperlink ref="AK3" r:id="rId14" location="wasteDisposalMethods" xr:uid="{435FF06B-B974-4B37-BA60-C79659E1631E}"/>
     <hyperlink ref="AM3" r:id="rId15" location="wasteDisposalMethods" xr:uid="{B45A5879-026B-4247-B2B8-15EF712B3716}"/>
     <hyperlink ref="AO3" r:id="rId16" location="wasteDisposalMethods" xr:uid="{5B7BDC52-01F7-456B-A7FF-5F257DD246CF}"/>
+    <hyperlink ref="U2:U3" r:id="rId17" location="logicalResponses" display="GNSS" xr:uid="{0C54855B-EE89-3A4C-86C4-ACF5E4C75DAC}"/>
+    <hyperlink ref="V2:V3" r:id="rId18" location="logicalResponses" display="VMS" xr:uid="{50130A42-06AC-344C-A952-13CEF9A19A23}"/>
+    <hyperlink ref="W2:W3" r:id="rId19" location="logicalResponses" display="AIS" xr:uid="{0BEB6884-11C3-4243-94A5-A9621E73B42E}"/>
+    <hyperlink ref="X2:X3" r:id="rId20" location="logicalResponses" display="RADARS" xr:uid="{EBC0223E-F8D4-DD44-86AA-5F86FE1083B1}"/>
+    <hyperlink ref="Y2:Y3" r:id="rId21" location="logicalResponses" display="TRACK_PLOTTER" xr:uid="{335AFB17-3F23-CE4E-AAE6-A4577D524164}"/>
+    <hyperlink ref="Z2:Z3" r:id="rId22" location="logicalResponses" display="DEPTH_SOUNDER" xr:uid="{4BC4BA9F-B868-5043-85AE-2C9F814DADBE}"/>
+    <hyperlink ref="AA2:AA3" r:id="rId23" location="logicalResponses" display="SONAR" xr:uid="{A61005C8-0E92-6748-A094-D871532DFDDE}"/>
+    <hyperlink ref="AB2:AB3" r:id="rId24" location="logicalResponses" display="DOPPLER_CURRENT_METER" xr:uid="{21BC4BC6-3B25-3B46-90C0-8090946055B7}"/>
+    <hyperlink ref="AC2:AC3" r:id="rId25" location="logicalResponses" display="XBT" xr:uid="{AC4FA5EB-6FCE-7D43-AA1A-9005D3DA860A}"/>
+    <hyperlink ref="AD2:AD3" r:id="rId26" location="logicalResponses" display="VHF_RADIOS" xr:uid="{5845561F-5164-2147-B482-77DA149A0912}"/>
+    <hyperlink ref="AE2:AE3" r:id="rId27" location="logicalResponses" display="HF_RADIOS" xr:uid="{EB82E40F-2B32-1945-B47E-2E1091B9748F}"/>
+    <hyperlink ref="AF2:AF3" r:id="rId28" location="logicalResponses" display="SATELLITE_COMM" xr:uid="{56717ED3-15A3-574B-8C8C-564EF8A6C0D1}"/>
+    <hyperlink ref="AG2:AG3" r:id="rId29" location="logicalResponses" display="FIS" xr:uid="{3633A0CE-F9DD-A042-9FC1-0F10ECFE7D67}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DE6AEF-7995-B64C-B764-9637601A340E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C112324-41FB-0F46-A14C-06EE8319A6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16380" tabRatio="879" firstSheet="1" activeTab="4" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16360" tabRatio="879" firstSheet="1" activeTab="5" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -994,7 +994,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1322,6 +1322,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -35051,10 +35054,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="75"/>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="113" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="113" t="s">
         <v>63</v>
       </c>
       <c r="D2" s="87" t="s">
@@ -35075,8 +35078,8 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="75"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
       <c r="D3" s="87" t="s">
         <v>188</v>
       </c>
@@ -35097,8 +35100,8 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="70"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
       <c r="D4" s="45" t="s">
         <v>18</v>
       </c>
@@ -37928,7 +37931,7 @@
       <c r="L204" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0b9R3e/9LkSgcpyzrZ2U3a5t0I0I5ykUo6zzefVGIHDw+IAwk1LwhhoACycRMhaFL5RpOUMpCBjExFBrctDRNg==" saltValue="2fMSlqclAhc2wpF2yjz/9A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6ovehArg0e9iLe13x1bzFJTxaXKKK7Ls6uaVbc2hU33Q3qzwlkEb3XqzZb75+ziaKviLibNLSoJXEDqOtUv5Ow==" saltValue="K49j7WadggjQwrZPE7mjOQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="A1:A4"/>
@@ -37943,6 +37946,10 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B2:B4" r:id="rId1" location="logicalResponses" display="POWER_BLOCK" xr:uid="{AD39E4CE-7A80-A94A-B17D-29AA42A5F254}"/>
+    <hyperlink ref="C2:C4" r:id="rId2" location="logicalResponses" display="PURSE_WINCH" xr:uid="{705F53BB-4871-F740-91FA-64AD096C76CB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C112324-41FB-0F46-A14C-06EE8319A6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE1425F-552F-254F-8F23-79F1C7BC3743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16360" tabRatio="879" firstSheet="1" activeTab="5" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16360" tabRatio="879" firstSheet="1" activeTab="7" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -994,7 +994,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1324,6 +1324,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -38097,10 +38103,10 @@
       <c r="P3" s="70"/>
       <c r="Q3" s="74"/>
       <c r="R3" s="99"/>
-      <c r="S3" s="39" t="s">
+      <c r="S3" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="T3" s="39" t="s">
+      <c r="T3" s="114" t="s">
         <v>74</v>
       </c>
       <c r="U3" s="33" t="s">
@@ -42911,7 +42917,7 @@
       <c r="V203" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SUEhtek1xjdHrbhxzS10tklKE6LDK3INEq0x/apGRQZ4wd8qhkNkaK2pjf/Dc5DheFyyovwYwOOIRWqRZcbsIA==" saltValue="mUomoVIUflQXJbTqgskr3A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LGbLE0X4mphbrvyDB8iHZbZ5jGyiClFuG1okIajSb/6AE438B82i1uIvOTrWorRsJspA6UxPow4rvWi+AhQlIA==" saltValue="1ksA3tQoetcJpOHsQN0vtA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
     <mergeCell ref="C2:C3"/>
@@ -42946,6 +42952,8 @@
     <hyperlink ref="V3" r:id="rId6" location="FADtailDesigns" xr:uid="{4EC548E9-585E-4A0F-8A11-B2D8DE7871DC}"/>
     <hyperlink ref="U3" r:id="rId7" location="FADraftDesigns" xr:uid="{56C6FE4F-AE5D-4D49-879C-6D4A0BF75DFF}"/>
     <hyperlink ref="J1:J3" r:id="rId8" location="schoolTypeCategories" display="SCHOOL_TYPES" xr:uid="{8EC575CB-432D-43D0-8C91-3FACD4044FFB}"/>
+    <hyperlink ref="S3" r:id="rId9" location="logicalResponses" xr:uid="{860C6C50-4466-3940-9B0A-F8CB030221D5}"/>
+    <hyperlink ref="T3" r:id="rId10" location="logicalResponses" xr:uid="{02ADBEB1-CD08-E74C-96CC-90C58B333795}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -42974,7 +42982,7 @@
       <c r="B1" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="115" t="s">
         <v>75</v>
       </c>
       <c r="D1" s="35" t="s">
@@ -42983,7 +42991,7 @@
       <c r="E1" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="115" t="s">
         <v>76</v>
       </c>
     </row>
@@ -44588,7 +44596,7 @@
       <c r="F201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="G6ZwYN709Jy1AWIWQxAxVplHZP5uP/NiiAIMHJ1doR9/7pTBWAVy2vieUW0vMIWYxyRbT7D7xiLCv9S3N8yYaQ==" saltValue="uuk0pmAMVaL17oFOYQ/XcQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UhrGzLwIH2JWpEZUUgcwvaPIu5FPGaxVInDJYWlNOKBbqTKmKl6F4H6+z/aTMLMuHNoEgABRFAKIxGa5DhkC5g==" saltValue="AG5AZvp511RQ1Xg2O8UwZA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{9A958104-A80B-4B1E-AB96-42BA504F7B3D}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -44596,6 +44604,8 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D1" r:id="rId1" location="cetaceansAndWhaleSharks" xr:uid="{F9440529-0B3C-4E2C-9C30-02C136FF531F}"/>
+    <hyperlink ref="C1" r:id="rId2" location="logicalResponses" xr:uid="{45E8DB2A-EC4B-CE4E-8A5C-271AA5DE39FD}"/>
+    <hyperlink ref="F1" r:id="rId3" location="logicalResponses" xr:uid="{0CA90A9C-0AC7-474C-A06E-8C6556CA9097}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE1425F-552F-254F-8F23-79F1C7BC3743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF7B744-D3EA-9342-9A98-97FC8850D4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16360" tabRatio="879" firstSheet="1" activeTab="7" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16360" tabRatio="879" firstSheet="1" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="194">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -184,9 +184,6 @@
   </si>
   <si>
     <t>PHOTO_ID</t>
-  </si>
-  <si>
-    <t>IS_STRAIGHT</t>
   </si>
   <si>
     <t>EMBARKATION</t>
@@ -1670,7 +1667,7 @@
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" s="52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="53"/>
       <c r="D2" s="53"/>
@@ -1691,14 +1688,14 @@
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G4" s="11">
         <v>5</v>
@@ -1717,7 +1714,7 @@
     <row r="6" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
       <c r="C6" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -1737,12 +1734,12 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="13"/>
       <c r="C8" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="58"/>
       <c r="E8" s="14"/>
       <c r="F8" s="58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8" s="58"/>
       <c r="H8" s="15"/>
@@ -1750,12 +1747,12 @@
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="13"/>
       <c r="C9" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="14"/>
       <c r="F9" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="15"/>
@@ -1763,12 +1760,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="13"/>
       <c r="C10" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="15"/>
@@ -1785,7 +1782,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="14"/>
@@ -1796,7 +1793,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="13"/>
       <c r="C13" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="14"/>
@@ -1825,7 +1822,7 @@
     <row r="16" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
       <c r="C16" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
@@ -1845,7 +1842,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="14"/>
@@ -1856,7 +1853,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
       <c r="C19" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="14"/>
@@ -1867,7 +1864,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="13"/>
       <c r="C20" s="51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="14"/>
@@ -1878,7 +1875,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="13"/>
       <c r="C21" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="14"/>
@@ -1907,7 +1904,7 @@
     <row r="24" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
       <c r="C24" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="14"/>
@@ -1975,7 +1972,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:V202"/>
+  <dimension ref="A1:T202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -1986,69 +1983,65 @@
     <col min="6" max="6" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" style="3" customWidth="1"/>
-    <col min="14" max="14" width="19.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.5" style="3" customWidth="1"/>
-    <col min="16" max="16" width="34.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.1640625" style="3"/>
-    <col min="18" max="18" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" style="3" customWidth="1"/>
-    <col min="20" max="20" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.5" style="3" customWidth="1"/>
+    <col min="14" max="14" width="34.5" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.1640625" style="3"/>
+    <col min="16" max="16" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="C1" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="D1" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="109" t="s">
-        <v>61</v>
-      </c>
       <c r="E1" s="96" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F1" s="79" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G1" s="79"/>
       <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="99" t="s">
-        <v>170</v>
+      <c r="I1" s="99" t="s">
+        <v>169</v>
       </c>
+      <c r="J1" s="99"/>
       <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99" t="s">
+      <c r="L1" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="93" t="s">
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="93" t="s">
         <v>38</v>
       </c>
+      <c r="P1" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q1" s="74"/>
       <c r="R1" s="72" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
-      <c r="S1" s="74"/>
-      <c r="T1" s="72" t="s">
-        <v>168</v>
-      </c>
-      <c r="U1" s="73"/>
-      <c r="V1" s="74"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="S1" s="73"/>
+      <c r="T1" s="74"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="110"/>
       <c r="B2" s="110"/>
       <c r="C2" s="110"/>
@@ -2061,50 +2054,44 @@
         <v>37</v>
       </c>
       <c r="H2" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="I2" s="31" t="s">
-        <v>45</v>
+      <c r="O2" s="95"/>
+      <c r="P2" s="37" t="s">
+        <v>52</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="Q2" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="R2" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="O2" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="T2" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="44" t="s">
+      <c r="S2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="34" t="s">
-        <v>187</v>
+      <c r="T2" s="34" t="s">
+        <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2125,10 +2112,8 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2149,10 +2134,8 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2173,10 +2156,8 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2197,10 +2178,8 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2221,10 +2200,8 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2245,10 +2222,8 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2269,10 +2244,8 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2293,10 +2266,8 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2317,10 +2288,8 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2341,10 +2310,8 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2365,10 +2332,8 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2389,10 +2354,8 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2413,10 +2376,8 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2437,10 +2398,8 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2461,10 +2420,8 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2485,10 +2442,8 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2509,10 +2464,8 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2533,10 +2486,8 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2557,10 +2508,8 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2581,10 +2530,8 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2605,10 +2552,8 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2629,10 +2574,8 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2653,10 +2596,8 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2677,10 +2618,8 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2701,10 +2640,8 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2725,10 +2662,8 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2749,10 +2684,8 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2773,10 +2706,8 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2797,10 +2728,8 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2821,10 +2750,8 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2845,10 +2772,8 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2869,10 +2794,8 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2893,10 +2816,8 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2917,10 +2838,8 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2941,10 +2860,8 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="2"/>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2965,10 +2882,8 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2989,10 +2904,8 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="2"/>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3013,10 +2926,8 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="2"/>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3037,10 +2948,8 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3061,10 +2970,8 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="2"/>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3085,10 +2992,8 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="2"/>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3109,10 +3014,8 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="2"/>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3133,10 +3036,8 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="2"/>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3157,10 +3058,8 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3181,10 +3080,8 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="2"/>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3205,10 +3102,8 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="2"/>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3229,10 +3124,8 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="2"/>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3253,10 +3146,8 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="2"/>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3277,10 +3168,8 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="2"/>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3301,10 +3190,8 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
-      <c r="V52" s="2"/>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3325,10 +3212,8 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-      <c r="V53" s="2"/>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3349,10 +3234,8 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="2"/>
-      <c r="V54" s="2"/>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3373,10 +3256,8 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
-      <c r="U55" s="2"/>
-      <c r="V55" s="2"/>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3397,10 +3278,8 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
-      <c r="U56" s="2"/>
-      <c r="V56" s="2"/>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3421,10 +3300,8 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
-      <c r="U57" s="2"/>
-      <c r="V57" s="2"/>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3445,10 +3322,8 @@
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
-      <c r="U58" s="2"/>
-      <c r="V58" s="2"/>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3469,10 +3344,8 @@
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2"/>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3493,10 +3366,8 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
-      <c r="U60" s="2"/>
-      <c r="V60" s="2"/>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3517,10 +3388,8 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
-      <c r="U61" s="2"/>
-      <c r="V61" s="2"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3541,10 +3410,8 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
-      <c r="U62" s="2"/>
-      <c r="V62" s="2"/>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3565,10 +3432,8 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
-      <c r="U63" s="2"/>
-      <c r="V63" s="2"/>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3589,10 +3454,8 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
-      <c r="U64" s="2"/>
-      <c r="V64" s="2"/>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3613,10 +3476,8 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
-      <c r="U65" s="2"/>
-      <c r="V65" s="2"/>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3637,10 +3498,8 @@
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="2"/>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3661,10 +3520,8 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
       <c r="T67" s="2"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3685,10 +3542,8 @@
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3709,10 +3564,8 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3733,10 +3586,8 @@
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="2"/>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3757,10 +3608,8 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="2"/>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3781,10 +3630,8 @@
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
       <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2"/>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3805,10 +3652,8 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
       <c r="T73" s="2"/>
-      <c r="U73" s="2"/>
-      <c r="V73" s="2"/>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3829,10 +3674,8 @@
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
       <c r="T74" s="2"/>
-      <c r="U74" s="2"/>
-      <c r="V74" s="2"/>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3853,10 +3696,8 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
       <c r="T75" s="2"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3877,10 +3718,8 @@
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
       <c r="T76" s="2"/>
-      <c r="U76" s="2"/>
-      <c r="V76" s="2"/>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3901,10 +3740,8 @@
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
       <c r="T77" s="2"/>
-      <c r="U77" s="2"/>
-      <c r="V77" s="2"/>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3925,10 +3762,8 @@
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
       <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3949,10 +3784,8 @@
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
       <c r="T79" s="2"/>
-      <c r="U79" s="2"/>
-      <c r="V79" s="2"/>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3973,10 +3806,8 @@
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
       <c r="T80" s="2"/>
-      <c r="U80" s="2"/>
-      <c r="V80" s="2"/>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3997,10 +3828,8 @@
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
       <c r="T81" s="2"/>
-      <c r="U81" s="2"/>
-      <c r="V81" s="2"/>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4021,10 +3850,8 @@
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
       <c r="T82" s="2"/>
-      <c r="U82" s="2"/>
-      <c r="V82" s="2"/>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4045,10 +3872,8 @@
       <c r="R83" s="2"/>
       <c r="S83" s="2"/>
       <c r="T83" s="2"/>
-      <c r="U83" s="2"/>
-      <c r="V83" s="2"/>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4069,10 +3894,8 @@
       <c r="R84" s="2"/>
       <c r="S84" s="2"/>
       <c r="T84" s="2"/>
-      <c r="U84" s="2"/>
-      <c r="V84" s="2"/>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4093,10 +3916,8 @@
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
       <c r="T85" s="2"/>
-      <c r="U85" s="2"/>
-      <c r="V85" s="2"/>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4117,10 +3938,8 @@
       <c r="R86" s="2"/>
       <c r="S86" s="2"/>
       <c r="T86" s="2"/>
-      <c r="U86" s="2"/>
-      <c r="V86" s="2"/>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4141,10 +3960,8 @@
       <c r="R87" s="2"/>
       <c r="S87" s="2"/>
       <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="2"/>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4165,10 +3982,8 @@
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
       <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="2"/>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4189,10 +4004,8 @@
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
       <c r="T89" s="2"/>
-      <c r="U89" s="2"/>
-      <c r="V89" s="2"/>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4213,10 +4026,8 @@
       <c r="R90" s="2"/>
       <c r="S90" s="2"/>
       <c r="T90" s="2"/>
-      <c r="U90" s="2"/>
-      <c r="V90" s="2"/>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4237,10 +4048,8 @@
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
       <c r="T91" s="2"/>
-      <c r="U91" s="2"/>
-      <c r="V91" s="2"/>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4261,10 +4070,8 @@
       <c r="R92" s="2"/>
       <c r="S92" s="2"/>
       <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
-      <c r="V92" s="2"/>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -4285,10 +4092,8 @@
       <c r="R93" s="2"/>
       <c r="S93" s="2"/>
       <c r="T93" s="2"/>
-      <c r="U93" s="2"/>
-      <c r="V93" s="2"/>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4309,10 +4114,8 @@
       <c r="R94" s="2"/>
       <c r="S94" s="2"/>
       <c r="T94" s="2"/>
-      <c r="U94" s="2"/>
-      <c r="V94" s="2"/>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4333,10 +4136,8 @@
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
       <c r="T95" s="2"/>
-      <c r="U95" s="2"/>
-      <c r="V95" s="2"/>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4357,10 +4158,8 @@
       <c r="R96" s="2"/>
       <c r="S96" s="2"/>
       <c r="T96" s="2"/>
-      <c r="U96" s="2"/>
-      <c r="V96" s="2"/>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4381,10 +4180,8 @@
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
       <c r="T97" s="2"/>
-      <c r="U97" s="2"/>
-      <c r="V97" s="2"/>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4405,10 +4202,8 @@
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
       <c r="T98" s="2"/>
-      <c r="U98" s="2"/>
-      <c r="V98" s="2"/>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4429,10 +4224,8 @@
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
       <c r="T99" s="2"/>
-      <c r="U99" s="2"/>
-      <c r="V99" s="2"/>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4453,10 +4246,8 @@
       <c r="R100" s="2"/>
       <c r="S100" s="2"/>
       <c r="T100" s="2"/>
-      <c r="U100" s="2"/>
-      <c r="V100" s="2"/>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -4477,10 +4268,8 @@
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
       <c r="T101" s="2"/>
-      <c r="U101" s="2"/>
-      <c r="V101" s="2"/>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4501,10 +4290,8 @@
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
       <c r="T102" s="2"/>
-      <c r="U102" s="2"/>
-      <c r="V102" s="2"/>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4525,10 +4312,8 @@
       <c r="R103" s="2"/>
       <c r="S103" s="2"/>
       <c r="T103" s="2"/>
-      <c r="U103" s="2"/>
-      <c r="V103" s="2"/>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4549,10 +4334,8 @@
       <c r="R104" s="2"/>
       <c r="S104" s="2"/>
       <c r="T104" s="2"/>
-      <c r="U104" s="2"/>
-      <c r="V104" s="2"/>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4573,10 +4356,8 @@
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
       <c r="T105" s="2"/>
-      <c r="U105" s="2"/>
-      <c r="V105" s="2"/>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4597,10 +4378,8 @@
       <c r="R106" s="2"/>
       <c r="S106" s="2"/>
       <c r="T106" s="2"/>
-      <c r="U106" s="2"/>
-      <c r="V106" s="2"/>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4621,10 +4400,8 @@
       <c r="R107" s="2"/>
       <c r="S107" s="2"/>
       <c r="T107" s="2"/>
-      <c r="U107" s="2"/>
-      <c r="V107" s="2"/>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4645,10 +4422,8 @@
       <c r="R108" s="2"/>
       <c r="S108" s="2"/>
       <c r="T108" s="2"/>
-      <c r="U108" s="2"/>
-      <c r="V108" s="2"/>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4669,10 +4444,8 @@
       <c r="R109" s="2"/>
       <c r="S109" s="2"/>
       <c r="T109" s="2"/>
-      <c r="U109" s="2"/>
-      <c r="V109" s="2"/>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4693,10 +4466,8 @@
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
       <c r="T110" s="2"/>
-      <c r="U110" s="2"/>
-      <c r="V110" s="2"/>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -4717,10 +4488,8 @@
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
       <c r="T111" s="2"/>
-      <c r="U111" s="2"/>
-      <c r="V111" s="2"/>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -4741,10 +4510,8 @@
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
       <c r="T112" s="2"/>
-      <c r="U112" s="2"/>
-      <c r="V112" s="2"/>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4765,10 +4532,8 @@
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
       <c r="T113" s="2"/>
-      <c r="U113" s="2"/>
-      <c r="V113" s="2"/>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -4789,10 +4554,8 @@
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
       <c r="T114" s="2"/>
-      <c r="U114" s="2"/>
-      <c r="V114" s="2"/>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -4813,10 +4576,8 @@
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
       <c r="T115" s="2"/>
-      <c r="U115" s="2"/>
-      <c r="V115" s="2"/>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -4837,10 +4598,8 @@
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
       <c r="T116" s="2"/>
-      <c r="U116" s="2"/>
-      <c r="V116" s="2"/>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -4861,10 +4620,8 @@
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
       <c r="T117" s="2"/>
-      <c r="U117" s="2"/>
-      <c r="V117" s="2"/>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -4885,10 +4642,8 @@
       <c r="R118" s="2"/>
       <c r="S118" s="2"/>
       <c r="T118" s="2"/>
-      <c r="U118" s="2"/>
-      <c r="V118" s="2"/>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4909,10 +4664,8 @@
       <c r="R119" s="2"/>
       <c r="S119" s="2"/>
       <c r="T119" s="2"/>
-      <c r="U119" s="2"/>
-      <c r="V119" s="2"/>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -4933,10 +4686,8 @@
       <c r="R120" s="2"/>
       <c r="S120" s="2"/>
       <c r="T120" s="2"/>
-      <c r="U120" s="2"/>
-      <c r="V120" s="2"/>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4957,10 +4708,8 @@
       <c r="R121" s="2"/>
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
-      <c r="U121" s="2"/>
-      <c r="V121" s="2"/>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -4981,10 +4730,8 @@
       <c r="R122" s="2"/>
       <c r="S122" s="2"/>
       <c r="T122" s="2"/>
-      <c r="U122" s="2"/>
-      <c r="V122" s="2"/>
-    </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5005,10 +4752,8 @@
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
       <c r="T123" s="2"/>
-      <c r="U123" s="2"/>
-      <c r="V123" s="2"/>
-    </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -5029,10 +4774,8 @@
       <c r="R124" s="2"/>
       <c r="S124" s="2"/>
       <c r="T124" s="2"/>
-      <c r="U124" s="2"/>
-      <c r="V124" s="2"/>
-    </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -5053,10 +4796,8 @@
       <c r="R125" s="2"/>
       <c r="S125" s="2"/>
       <c r="T125" s="2"/>
-      <c r="U125" s="2"/>
-      <c r="V125" s="2"/>
-    </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -5077,10 +4818,8 @@
       <c r="R126" s="2"/>
       <c r="S126" s="2"/>
       <c r="T126" s="2"/>
-      <c r="U126" s="2"/>
-      <c r="V126" s="2"/>
-    </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -5101,10 +4840,8 @@
       <c r="R127" s="2"/>
       <c r="S127" s="2"/>
       <c r="T127" s="2"/>
-      <c r="U127" s="2"/>
-      <c r="V127" s="2"/>
-    </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -5125,10 +4862,8 @@
       <c r="R128" s="2"/>
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
-      <c r="U128" s="2"/>
-      <c r="V128" s="2"/>
-    </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -5149,10 +4884,8 @@
       <c r="R129" s="2"/>
       <c r="S129" s="2"/>
       <c r="T129" s="2"/>
-      <c r="U129" s="2"/>
-      <c r="V129" s="2"/>
-    </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -5173,10 +4906,8 @@
       <c r="R130" s="2"/>
       <c r="S130" s="2"/>
       <c r="T130" s="2"/>
-      <c r="U130" s="2"/>
-      <c r="V130" s="2"/>
-    </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -5197,10 +4928,8 @@
       <c r="R131" s="2"/>
       <c r="S131" s="2"/>
       <c r="T131" s="2"/>
-      <c r="U131" s="2"/>
-      <c r="V131" s="2"/>
-    </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -5221,10 +4950,8 @@
       <c r="R132" s="2"/>
       <c r="S132" s="2"/>
       <c r="T132" s="2"/>
-      <c r="U132" s="2"/>
-      <c r="V132" s="2"/>
-    </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -5245,10 +4972,8 @@
       <c r="R133" s="2"/>
       <c r="S133" s="2"/>
       <c r="T133" s="2"/>
-      <c r="U133" s="2"/>
-      <c r="V133" s="2"/>
-    </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -5269,10 +4994,8 @@
       <c r="R134" s="2"/>
       <c r="S134" s="2"/>
       <c r="T134" s="2"/>
-      <c r="U134" s="2"/>
-      <c r="V134" s="2"/>
-    </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -5293,10 +5016,8 @@
       <c r="R135" s="2"/>
       <c r="S135" s="2"/>
       <c r="T135" s="2"/>
-      <c r="U135" s="2"/>
-      <c r="V135" s="2"/>
-    </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -5317,10 +5038,8 @@
       <c r="R136" s="2"/>
       <c r="S136" s="2"/>
       <c r="T136" s="2"/>
-      <c r="U136" s="2"/>
-      <c r="V136" s="2"/>
-    </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -5341,10 +5060,8 @@
       <c r="R137" s="2"/>
       <c r="S137" s="2"/>
       <c r="T137" s="2"/>
-      <c r="U137" s="2"/>
-      <c r="V137" s="2"/>
-    </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -5365,10 +5082,8 @@
       <c r="R138" s="2"/>
       <c r="S138" s="2"/>
       <c r="T138" s="2"/>
-      <c r="U138" s="2"/>
-      <c r="V138" s="2"/>
-    </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -5389,10 +5104,8 @@
       <c r="R139" s="2"/>
       <c r="S139" s="2"/>
       <c r="T139" s="2"/>
-      <c r="U139" s="2"/>
-      <c r="V139" s="2"/>
-    </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -5413,10 +5126,8 @@
       <c r="R140" s="2"/>
       <c r="S140" s="2"/>
       <c r="T140" s="2"/>
-      <c r="U140" s="2"/>
-      <c r="V140" s="2"/>
-    </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -5437,10 +5148,8 @@
       <c r="R141" s="2"/>
       <c r="S141" s="2"/>
       <c r="T141" s="2"/>
-      <c r="U141" s="2"/>
-      <c r="V141" s="2"/>
-    </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -5461,10 +5170,8 @@
       <c r="R142" s="2"/>
       <c r="S142" s="2"/>
       <c r="T142" s="2"/>
-      <c r="U142" s="2"/>
-      <c r="V142" s="2"/>
-    </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -5485,10 +5192,8 @@
       <c r="R143" s="2"/>
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
-      <c r="U143" s="2"/>
-      <c r="V143" s="2"/>
-    </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -5509,10 +5214,8 @@
       <c r="R144" s="2"/>
       <c r="S144" s="2"/>
       <c r="T144" s="2"/>
-      <c r="U144" s="2"/>
-      <c r="V144" s="2"/>
-    </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -5533,10 +5236,8 @@
       <c r="R145" s="2"/>
       <c r="S145" s="2"/>
       <c r="T145" s="2"/>
-      <c r="U145" s="2"/>
-      <c r="V145" s="2"/>
-    </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -5557,10 +5258,8 @@
       <c r="R146" s="2"/>
       <c r="S146" s="2"/>
       <c r="T146" s="2"/>
-      <c r="U146" s="2"/>
-      <c r="V146" s="2"/>
-    </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5581,10 +5280,8 @@
       <c r="R147" s="2"/>
       <c r="S147" s="2"/>
       <c r="T147" s="2"/>
-      <c r="U147" s="2"/>
-      <c r="V147" s="2"/>
-    </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5605,10 +5302,8 @@
       <c r="R148" s="2"/>
       <c r="S148" s="2"/>
       <c r="T148" s="2"/>
-      <c r="U148" s="2"/>
-      <c r="V148" s="2"/>
-    </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -5629,10 +5324,8 @@
       <c r="R149" s="2"/>
       <c r="S149" s="2"/>
       <c r="T149" s="2"/>
-      <c r="U149" s="2"/>
-      <c r="V149" s="2"/>
-    </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -5653,10 +5346,8 @@
       <c r="R150" s="2"/>
       <c r="S150" s="2"/>
       <c r="T150" s="2"/>
-      <c r="U150" s="2"/>
-      <c r="V150" s="2"/>
-    </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -5677,10 +5368,8 @@
       <c r="R151" s="2"/>
       <c r="S151" s="2"/>
       <c r="T151" s="2"/>
-      <c r="U151" s="2"/>
-      <c r="V151" s="2"/>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -5701,10 +5390,8 @@
       <c r="R152" s="2"/>
       <c r="S152" s="2"/>
       <c r="T152" s="2"/>
-      <c r="U152" s="2"/>
-      <c r="V152" s="2"/>
-    </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -5725,10 +5412,8 @@
       <c r="R153" s="2"/>
       <c r="S153" s="2"/>
       <c r="T153" s="2"/>
-      <c r="U153" s="2"/>
-      <c r="V153" s="2"/>
-    </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -5749,10 +5434,8 @@
       <c r="R154" s="2"/>
       <c r="S154" s="2"/>
       <c r="T154" s="2"/>
-      <c r="U154" s="2"/>
-      <c r="V154" s="2"/>
-    </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -5773,10 +5456,8 @@
       <c r="R155" s="2"/>
       <c r="S155" s="2"/>
       <c r="T155" s="2"/>
-      <c r="U155" s="2"/>
-      <c r="V155" s="2"/>
-    </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -5797,10 +5478,8 @@
       <c r="R156" s="2"/>
       <c r="S156" s="2"/>
       <c r="T156" s="2"/>
-      <c r="U156" s="2"/>
-      <c r="V156" s="2"/>
-    </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -5821,10 +5500,8 @@
       <c r="R157" s="2"/>
       <c r="S157" s="2"/>
       <c r="T157" s="2"/>
-      <c r="U157" s="2"/>
-      <c r="V157" s="2"/>
-    </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -5845,10 +5522,8 @@
       <c r="R158" s="2"/>
       <c r="S158" s="2"/>
       <c r="T158" s="2"/>
-      <c r="U158" s="2"/>
-      <c r="V158" s="2"/>
-    </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -5869,10 +5544,8 @@
       <c r="R159" s="2"/>
       <c r="S159" s="2"/>
       <c r="T159" s="2"/>
-      <c r="U159" s="2"/>
-      <c r="V159" s="2"/>
-    </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -5893,10 +5566,8 @@
       <c r="R160" s="2"/>
       <c r="S160" s="2"/>
       <c r="T160" s="2"/>
-      <c r="U160" s="2"/>
-      <c r="V160" s="2"/>
-    </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -5917,10 +5588,8 @@
       <c r="R161" s="2"/>
       <c r="S161" s="2"/>
       <c r="T161" s="2"/>
-      <c r="U161" s="2"/>
-      <c r="V161" s="2"/>
-    </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -5941,10 +5610,8 @@
       <c r="R162" s="2"/>
       <c r="S162" s="2"/>
       <c r="T162" s="2"/>
-      <c r="U162" s="2"/>
-      <c r="V162" s="2"/>
-    </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -5965,10 +5632,8 @@
       <c r="R163" s="2"/>
       <c r="S163" s="2"/>
       <c r="T163" s="2"/>
-      <c r="U163" s="2"/>
-      <c r="V163" s="2"/>
-    </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -5989,10 +5654,8 @@
       <c r="R164" s="2"/>
       <c r="S164" s="2"/>
       <c r="T164" s="2"/>
-      <c r="U164" s="2"/>
-      <c r="V164" s="2"/>
-    </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -6013,10 +5676,8 @@
       <c r="R165" s="2"/>
       <c r="S165" s="2"/>
       <c r="T165" s="2"/>
-      <c r="U165" s="2"/>
-      <c r="V165" s="2"/>
-    </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -6037,10 +5698,8 @@
       <c r="R166" s="2"/>
       <c r="S166" s="2"/>
       <c r="T166" s="2"/>
-      <c r="U166" s="2"/>
-      <c r="V166" s="2"/>
-    </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -6061,10 +5720,8 @@
       <c r="R167" s="2"/>
       <c r="S167" s="2"/>
       <c r="T167" s="2"/>
-      <c r="U167" s="2"/>
-      <c r="V167" s="2"/>
-    </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -6085,10 +5742,8 @@
       <c r="R168" s="2"/>
       <c r="S168" s="2"/>
       <c r="T168" s="2"/>
-      <c r="U168" s="2"/>
-      <c r="V168" s="2"/>
-    </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -6109,10 +5764,8 @@
       <c r="R169" s="2"/>
       <c r="S169" s="2"/>
       <c r="T169" s="2"/>
-      <c r="U169" s="2"/>
-      <c r="V169" s="2"/>
-    </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -6133,10 +5786,8 @@
       <c r="R170" s="2"/>
       <c r="S170" s="2"/>
       <c r="T170" s="2"/>
-      <c r="U170" s="2"/>
-      <c r="V170" s="2"/>
-    </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -6157,10 +5808,8 @@
       <c r="R171" s="2"/>
       <c r="S171" s="2"/>
       <c r="T171" s="2"/>
-      <c r="U171" s="2"/>
-      <c r="V171" s="2"/>
-    </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -6181,10 +5830,8 @@
       <c r="R172" s="2"/>
       <c r="S172" s="2"/>
       <c r="T172" s="2"/>
-      <c r="U172" s="2"/>
-      <c r="V172" s="2"/>
-    </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -6205,10 +5852,8 @@
       <c r="R173" s="2"/>
       <c r="S173" s="2"/>
       <c r="T173" s="2"/>
-      <c r="U173" s="2"/>
-      <c r="V173" s="2"/>
-    </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -6229,10 +5874,8 @@
       <c r="R174" s="2"/>
       <c r="S174" s="2"/>
       <c r="T174" s="2"/>
-      <c r="U174" s="2"/>
-      <c r="V174" s="2"/>
-    </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -6253,10 +5896,8 @@
       <c r="R175" s="2"/>
       <c r="S175" s="2"/>
       <c r="T175" s="2"/>
-      <c r="U175" s="2"/>
-      <c r="V175" s="2"/>
-    </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -6277,10 +5918,8 @@
       <c r="R176" s="2"/>
       <c r="S176" s="2"/>
       <c r="T176" s="2"/>
-      <c r="U176" s="2"/>
-      <c r="V176" s="2"/>
-    </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -6301,10 +5940,8 @@
       <c r="R177" s="2"/>
       <c r="S177" s="2"/>
       <c r="T177" s="2"/>
-      <c r="U177" s="2"/>
-      <c r="V177" s="2"/>
-    </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -6325,10 +5962,8 @@
       <c r="R178" s="2"/>
       <c r="S178" s="2"/>
       <c r="T178" s="2"/>
-      <c r="U178" s="2"/>
-      <c r="V178" s="2"/>
-    </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -6349,10 +5984,8 @@
       <c r="R179" s="2"/>
       <c r="S179" s="2"/>
       <c r="T179" s="2"/>
-      <c r="U179" s="2"/>
-      <c r="V179" s="2"/>
-    </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -6373,10 +6006,8 @@
       <c r="R180" s="2"/>
       <c r="S180" s="2"/>
       <c r="T180" s="2"/>
-      <c r="U180" s="2"/>
-      <c r="V180" s="2"/>
-    </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -6397,10 +6028,8 @@
       <c r="R181" s="2"/>
       <c r="S181" s="2"/>
       <c r="T181" s="2"/>
-      <c r="U181" s="2"/>
-      <c r="V181" s="2"/>
-    </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -6421,10 +6050,8 @@
       <c r="R182" s="2"/>
       <c r="S182" s="2"/>
       <c r="T182" s="2"/>
-      <c r="U182" s="2"/>
-      <c r="V182" s="2"/>
-    </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -6445,10 +6072,8 @@
       <c r="R183" s="2"/>
       <c r="S183" s="2"/>
       <c r="T183" s="2"/>
-      <c r="U183" s="2"/>
-      <c r="V183" s="2"/>
-    </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -6469,10 +6094,8 @@
       <c r="R184" s="2"/>
       <c r="S184" s="2"/>
       <c r="T184" s="2"/>
-      <c r="U184" s="2"/>
-      <c r="V184" s="2"/>
-    </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -6493,10 +6116,8 @@
       <c r="R185" s="2"/>
       <c r="S185" s="2"/>
       <c r="T185" s="2"/>
-      <c r="U185" s="2"/>
-      <c r="V185" s="2"/>
-    </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -6517,10 +6138,8 @@
       <c r="R186" s="2"/>
       <c r="S186" s="2"/>
       <c r="T186" s="2"/>
-      <c r="U186" s="2"/>
-      <c r="V186" s="2"/>
-    </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -6541,10 +6160,8 @@
       <c r="R187" s="2"/>
       <c r="S187" s="2"/>
       <c r="T187" s="2"/>
-      <c r="U187" s="2"/>
-      <c r="V187" s="2"/>
-    </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -6565,10 +6182,8 @@
       <c r="R188" s="2"/>
       <c r="S188" s="2"/>
       <c r="T188" s="2"/>
-      <c r="U188" s="2"/>
-      <c r="V188" s="2"/>
-    </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -6589,10 +6204,8 @@
       <c r="R189" s="2"/>
       <c r="S189" s="2"/>
       <c r="T189" s="2"/>
-      <c r="U189" s="2"/>
-      <c r="V189" s="2"/>
-    </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -6613,10 +6226,8 @@
       <c r="R190" s="2"/>
       <c r="S190" s="2"/>
       <c r="T190" s="2"/>
-      <c r="U190" s="2"/>
-      <c r="V190" s="2"/>
-    </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -6637,10 +6248,8 @@
       <c r="R191" s="2"/>
       <c r="S191" s="2"/>
       <c r="T191" s="2"/>
-      <c r="U191" s="2"/>
-      <c r="V191" s="2"/>
-    </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -6661,10 +6270,8 @@
       <c r="R192" s="2"/>
       <c r="S192" s="2"/>
       <c r="T192" s="2"/>
-      <c r="U192" s="2"/>
-      <c r="V192" s="2"/>
-    </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -6685,10 +6292,8 @@
       <c r="R193" s="2"/>
       <c r="S193" s="2"/>
       <c r="T193" s="2"/>
-      <c r="U193" s="2"/>
-      <c r="V193" s="2"/>
-    </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -6709,10 +6314,8 @@
       <c r="R194" s="2"/>
       <c r="S194" s="2"/>
       <c r="T194" s="2"/>
-      <c r="U194" s="2"/>
-      <c r="V194" s="2"/>
-    </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -6733,10 +6336,8 @@
       <c r="R195" s="2"/>
       <c r="S195" s="2"/>
       <c r="T195" s="2"/>
-      <c r="U195" s="2"/>
-      <c r="V195" s="2"/>
-    </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -6757,10 +6358,8 @@
       <c r="R196" s="2"/>
       <c r="S196" s="2"/>
       <c r="T196" s="2"/>
-      <c r="U196" s="2"/>
-      <c r="V196" s="2"/>
-    </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -6781,10 +6380,8 @@
       <c r="R197" s="2"/>
       <c r="S197" s="2"/>
       <c r="T197" s="2"/>
-      <c r="U197" s="2"/>
-      <c r="V197" s="2"/>
-    </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -6805,10 +6402,8 @@
       <c r="R198" s="2"/>
       <c r="S198" s="2"/>
       <c r="T198" s="2"/>
-      <c r="U198" s="2"/>
-      <c r="V198" s="2"/>
-    </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -6829,10 +6424,8 @@
       <c r="R199" s="2"/>
       <c r="S199" s="2"/>
       <c r="T199" s="2"/>
-      <c r="U199" s="2"/>
-      <c r="V199" s="2"/>
-    </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -6853,10 +6446,8 @@
       <c r="R200" s="2"/>
       <c r="S200" s="2"/>
       <c r="T200" s="2"/>
-      <c r="U200" s="2"/>
-      <c r="V200" s="2"/>
-    </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -6877,10 +6468,8 @@
       <c r="R201" s="2"/>
       <c r="S201" s="2"/>
       <c r="T201" s="2"/>
-      <c r="U201" s="2"/>
-      <c r="V201" s="2"/>
-    </row>
-    <row r="202" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -6901,44 +6490,42 @@
       <c r="R202" s="2"/>
       <c r="S202" s="2"/>
       <c r="T202" s="2"/>
-      <c r="U202" s="2"/>
-      <c r="V202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BTexII7owVy7UQbHfXi/pyJQyZY+TVM2NUjbJHtKkRwH9qU3D0asKSbCPlNE3BE//D65VD7VqTSzNJRUsWzKQw==" saltValue="9Bv0Uc7e1ZSaTefnMGuLyA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="L1:N1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="O1:O2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 J2 L2 N2 Q1:Q2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 I2 K2 L2 O1:O2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
-    <dataValidation type="custom" sqref="P2" xr:uid="{746A974C-37B7-4392-8C1F-3624962D83AA}">
+    <dataValidation type="custom" sqref="N2" xr:uid="{746A974C-37B7-4392-8C1F-3624962D83AA}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E1:E2" r:id="rId1" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
     <hyperlink ref="H2" r:id="rId2" location="lengthMeasurementTools" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
-    <hyperlink ref="L2" r:id="rId3" location="lengthMeasurementTools" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
+    <hyperlink ref="K2" r:id="rId3" location="lengthMeasurementTools" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
     <hyperlink ref="F2" r:id="rId4" location="lengthMeasurementTypes" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
-    <hyperlink ref="J2" r:id="rId5" location="lengthMeasurementTypes" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
-    <hyperlink ref="N2" r:id="rId6" location="fishProcessingTypes" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
-    <hyperlink ref="Q1:Q2" r:id="rId7" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
-    <hyperlink ref="P2" r:id="rId8" location="weightMeasurementTools" xr:uid="{074E1E59-D343-4222-8E1C-310625164A04}"/>
-    <hyperlink ref="S2" r:id="rId9" location="Maturity_Stages" xr:uid="{E5D44B35-6082-4003-9C14-F412F3AFBAD6}"/>
-    <hyperlink ref="T2" r:id="rId10" location="samplingMethodsForSamplingCollection" xr:uid="{9F653EC4-D647-4197-B661-7CCACA627208}"/>
-    <hyperlink ref="U2" r:id="rId11" location="fishStorageTypes" xr:uid="{AA058992-D2B7-40CE-B6C6-3E8AA47DE46F}"/>
+    <hyperlink ref="I2" r:id="rId5" location="lengthMeasurementTypes" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
+    <hyperlink ref="L2" r:id="rId6" location="fishProcessingTypes" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
+    <hyperlink ref="O1:O2" r:id="rId7" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
+    <hyperlink ref="N2" r:id="rId8" location="weightMeasurementTools" xr:uid="{074E1E59-D343-4222-8E1C-310625164A04}"/>
+    <hyperlink ref="Q2" r:id="rId9" location="Maturity_Stages" xr:uid="{E5D44B35-6082-4003-9C14-F412F3AFBAD6}"/>
+    <hyperlink ref="R2" r:id="rId10" location="samplingMethodsForSamplingCollection" xr:uid="{9F653EC4-D647-4197-B661-7CCACA627208}"/>
+    <hyperlink ref="S2" r:id="rId11" location="fishStorageTypes" xr:uid="{AA058992-D2B7-40CE-B6C6-3E8AA47DE46F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6966,31 +6553,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="C1" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="D1" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="109" t="s">
-        <v>61</v>
+      <c r="E1" s="93" t="s">
+        <v>170</v>
       </c>
-      <c r="E1" s="93" t="s">
+      <c r="F1" s="93" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="93" t="s">
+      <c r="G1" s="93" t="s">
         <v>172</v>
-      </c>
-      <c r="G1" s="93" t="s">
-        <v>173</v>
       </c>
       <c r="H1" s="111" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J1" s="111" t="s">
         <v>43</v>
@@ -9663,16 +9250,16 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="C1" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="D1" s="46" t="s">
         <v>60</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="39" t="s">
         <v>40</v>
@@ -9684,19 +9271,19 @@
         <v>19</v>
       </c>
       <c r="H1" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="I1" s="39" t="s">
-        <v>192</v>
+      <c r="J1" s="39" t="s">
+        <v>174</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="K1" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="K1" s="39" t="s">
-        <v>176</v>
-      </c>
       <c r="L1" s="49" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -12531,10 +12118,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C1" s="34" t="s">
         <v>0</v>
@@ -12543,10 +12130,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -14196,14 +13783,14 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" s="62"/>
       <c r="D1" s="62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E1" s="62"/>
       <c r="F1" s="62"/>
@@ -14215,7 +13802,7 @@
       <c r="L1" s="62"/>
       <c r="M1" s="62"/>
       <c r="N1" s="62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O1" s="62"/>
       <c r="P1" s="62"/>
@@ -14234,14 +13821,14 @@
       <c r="B2" s="62"/>
       <c r="C2" s="62"/>
       <c r="D2" s="65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="66"/>
       <c r="F2" s="66"/>
       <c r="G2" s="66"/>
       <c r="H2" s="71"/>
       <c r="I2" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" s="66"/>
       <c r="K2" s="66"/>
@@ -14265,40 +13852,40 @@
       <c r="B3" s="62"/>
       <c r="C3" s="62"/>
       <c r="D3" s="67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" s="68"/>
       <c r="F3" s="63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="64"/>
       <c r="H3" s="69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I3" s="67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J3" s="68"/>
       <c r="K3" s="63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L3" s="64"/>
       <c r="M3" s="69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" s="62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O3" s="62"/>
       <c r="P3" s="62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q3" s="62"/>
       <c r="R3" s="62"/>
       <c r="S3" s="62"/>
       <c r="T3" s="62"/>
       <c r="U3" s="72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V3" s="73"/>
       <c r="W3" s="73"/>
@@ -14307,13 +13894,13 @@
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="62"/>
       <c r="B4" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>4</v>
@@ -14326,7 +13913,7 @@
       </c>
       <c r="H4" s="70"/>
       <c r="I4" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J4" s="30" t="s">
         <v>4</v>
@@ -14360,16 +13947,16 @@
         <v>10</v>
       </c>
       <c r="U4" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="V4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="V4" s="30" t="s">
+      <c r="W4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="W4" s="30" t="s">
+      <c r="X4" s="30" t="s">
         <v>108</v>
-      </c>
-      <c r="X4" s="30" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -14663,7 +14250,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -19615,7 +19202,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="76" t="s">
         <v>17</v>
@@ -19630,13 +19217,13 @@
       <c r="H1" s="89"/>
       <c r="I1" s="90"/>
       <c r="J1" s="93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K1" s="96" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L1" s="76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M1" s="77"/>
       <c r="N1" s="77"/>
@@ -19649,7 +19236,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D2" s="62" t="s">
         <v>2</v>
@@ -19661,22 +19248,22 @@
         <v>14</v>
       </c>
       <c r="G2" s="83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="84" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="91" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J2" s="94"/>
       <c r="K2" s="97"/>
       <c r="L2" s="79" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M2" s="79"/>
       <c r="N2" s="79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O2" s="79"/>
       <c r="P2" s="80" t="s">
@@ -19699,13 +19286,13 @@
         <v>3</v>
       </c>
       <c r="M3" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N3" s="31" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P3" s="80"/>
     </row>
@@ -23374,17 +22961,17 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C1" s="79"/>
       <c r="D1" s="79"/>
       <c r="E1" s="79"/>
       <c r="F1" s="79"/>
       <c r="G1" s="79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H1" s="79"/>
       <c r="I1" s="79"/>
@@ -23394,28 +22981,28 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="75"/>
       <c r="B2" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="66"/>
       <c r="D2" s="66"/>
       <c r="E2" s="66"/>
       <c r="F2" s="69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="66"/>
       <c r="I2" s="66"/>
       <c r="J2" s="71"/>
       <c r="K2" s="69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="70"/>
       <c r="B3" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" s="30" t="s">
         <v>4</v>
@@ -23428,7 +23015,7 @@
       </c>
       <c r="F3" s="70"/>
       <c r="G3" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>4</v>
@@ -26116,10 +25703,10 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C1" s="73"/>
       <c r="D1" s="73"/>
@@ -26140,7 +25727,7 @@
       <c r="S1" s="73"/>
       <c r="T1" s="74"/>
       <c r="U1" s="72" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V1" s="73"/>
       <c r="W1" s="73"/>
@@ -26155,7 +25742,7 @@
       <c r="AF1" s="73"/>
       <c r="AG1" s="74"/>
       <c r="AH1" s="72" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AI1" s="73"/>
       <c r="AJ1" s="73"/>
@@ -26168,35 +25755,35 @@
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A2" s="75"/>
       <c r="B2" s="81" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="100" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="100" t="s">
-        <v>182</v>
-      </c>
       <c r="D2" s="93" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E2" s="99" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F2" s="99"/>
       <c r="G2" s="99"/>
       <c r="H2" s="99" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I2" s="99"/>
       <c r="J2" s="99"/>
       <c r="K2" s="101" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L2" s="87" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M2" s="87"/>
       <c r="N2" s="87"/>
       <c r="O2" s="87"/>
       <c r="P2" s="99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q2" s="99"/>
       <c r="R2" s="99"/>
@@ -26205,7 +25792,7 @@
       </c>
       <c r="T2" s="87"/>
       <c r="U2" s="112" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V2" s="112" t="s">
         <v>23</v>
@@ -26244,19 +25831,19 @@
         <v>33</v>
       </c>
       <c r="AH2" s="87" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI2" s="87"/>
       <c r="AJ2" s="87" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK2" s="87"/>
       <c r="AL2" s="87" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AM2" s="87"/>
       <c r="AN2" s="87" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AO2" s="87"/>
     </row>
@@ -26272,7 +25859,7 @@
         <v>21</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H3" s="47" t="s">
         <v>20</v>
@@ -26281,35 +25868,35 @@
         <v>21</v>
       </c>
       <c r="J3" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K3" s="102"/>
       <c r="L3" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="M3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="M3" s="30" t="s">
+      <c r="N3" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="O3" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="O3" s="30" t="s">
-        <v>122</v>
+      <c r="P3" s="33" t="s">
+        <v>124</v>
       </c>
-      <c r="P3" s="33" t="s">
+      <c r="Q3" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="Q3" s="33" t="s">
+      <c r="R3" s="33" t="s">
         <v>126</v>
-      </c>
-      <c r="R3" s="33" t="s">
-        <v>127</v>
       </c>
       <c r="S3" s="34" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U3" s="112"/>
       <c r="V3" s="112"/>
@@ -26325,28 +25912,28 @@
       <c r="AF3" s="112"/>
       <c r="AG3" s="112"/>
       <c r="AH3" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI3" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="AI3" s="33" t="s">
+      <c r="AJ3" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="AJ3" s="33" t="s">
+      <c r="AK3" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AK3" s="33" t="s">
+      <c r="AL3" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AL3" s="33" t="s">
+      <c r="AM3" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="AM3" s="33" t="s">
+      <c r="AN3" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="AN3" s="33" t="s">
+      <c r="AO3" s="33" t="s">
         <v>136</v>
-      </c>
-      <c r="AO3" s="33" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -35040,14 +34627,14 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C1" s="74"/>
       <c r="D1" s="72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E1" s="73"/>
       <c r="F1" s="73"/>
@@ -35061,25 +34648,25 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="75"/>
       <c r="B2" s="113" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="113" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="113" t="s">
+      <c r="D2" s="87" t="s">
         <v>63</v>
-      </c>
-      <c r="D2" s="87" t="s">
-        <v>64</v>
       </c>
       <c r="E2" s="87"/>
       <c r="F2" s="87"/>
       <c r="G2" s="87"/>
       <c r="H2" s="87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I2" s="87"/>
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
       <c r="L2" s="87" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -35087,19 +34674,19 @@
       <c r="B3" s="113"/>
       <c r="C3" s="113"/>
       <c r="D3" s="87" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E3" s="87"/>
       <c r="F3" s="87" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G3" s="87"/>
       <c r="H3" s="87" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I3" s="87"/>
       <c r="J3" s="87" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K3" s="87"/>
       <c r="L3" s="87"/>
@@ -35112,28 +34699,28 @@
         <v>18</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F4" s="45" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H4" s="45" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J4" s="45" t="s">
         <v>18</v>
       </c>
       <c r="K4" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -37988,46 +37575,46 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="69" t="s">
-        <v>59</v>
-      </c>
       <c r="C1" s="65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1" s="66"/>
       <c r="E1" s="71"/>
       <c r="F1" s="100" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G1" s="103"/>
       <c r="H1" s="103"/>
       <c r="I1" s="103"/>
       <c r="J1" s="96" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K1" s="105" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L1" s="87" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="87" t="s">
+      <c r="N1" s="87" t="s">
         <v>66</v>
-      </c>
-      <c r="N1" s="87" t="s">
-        <v>67</v>
       </c>
       <c r="O1" s="72"/>
       <c r="P1" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q1" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="Q1" s="74" t="s">
-        <v>69</v>
-      </c>
       <c r="R1" s="87" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S1" s="87"/>
       <c r="T1" s="87"/>
@@ -38038,10 +37625,10 @@
       <c r="A2" s="75"/>
       <c r="B2" s="75"/>
       <c r="C2" s="106" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" s="71"/>
       <c r="F2" s="67"/>
@@ -38057,14 +37644,14 @@
       <c r="P2" s="75"/>
       <c r="Q2" s="74"/>
       <c r="R2" s="99" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S2" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T2" s="87"/>
       <c r="U2" s="87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="V2" s="87"/>
     </row>
@@ -38079,41 +37666,41 @@
         <v>1</v>
       </c>
       <c r="F3" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="H3" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="I3" s="43" t="s">
         <v>153</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>154</v>
       </c>
       <c r="J3" s="98"/>
       <c r="K3" s="105"/>
       <c r="L3" s="87"/>
       <c r="M3" s="87"/>
       <c r="N3" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P3" s="70"/>
       <c r="Q3" s="74"/>
       <c r="R3" s="99"/>
       <c r="S3" s="114" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="T3" s="114" t="s">
-        <v>74</v>
-      </c>
       <c r="U3" s="33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="V3" s="33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -42977,22 +42564,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="31" t="s">
-        <v>59</v>
-      </c>
       <c r="C1" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F1" s="115" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -44633,26 +44220,26 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="C1" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="69" t="s">
-        <v>60</v>
-      </c>
       <c r="D1" s="96" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E1" s="107" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F1" s="108"/>
       <c r="G1" s="96" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H1" s="69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I1" s="65" t="s">
         <v>35</v>
@@ -44669,18 +44256,18 @@
         <v>19</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" s="98"/>
       <c r="H2" s="70"/>
       <c r="I2" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J2" s="50" t="s">
         <v>36</v>
       </c>
       <c r="K2" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF7B744-D3EA-9342-9A98-97FC8850D4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E655CDB6-0B65-AF48-A000-1E7FBFA54934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16360" tabRatio="879" firstSheet="1" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16420" tabRatio="879" firstSheet="9" activeTab="10" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -991,7 +991,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1327,6 +1327,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6573,13 +6579,13 @@
       <c r="G1" s="93" t="s">
         <v>172</v>
       </c>
-      <c r="H1" s="111" t="s">
+      <c r="H1" s="116" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="J1" s="111" t="s">
+      <c r="J1" s="116" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="111" t="s">
@@ -6594,9 +6600,9 @@
       <c r="E2" s="95"/>
       <c r="F2" s="95"/>
       <c r="G2" s="95"/>
-      <c r="H2" s="82"/>
+      <c r="H2" s="117"/>
       <c r="I2" s="95"/>
-      <c r="J2" s="82"/>
+      <c r="J2" s="117"/>
       <c r="K2" s="82"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -9200,7 +9206,7 @@
       <c r="K202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/i8ttRawHFE0bDsLHk0X3DAZnREwIVUNut+wCnlTtUXkhO/z6EY5v2kRXopEus0UfjIHrMc29E3tZKRlwPN6dQ==" saltValue="ZTcyu138evLLcD0f3mUgnw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UEOkJqql+6bXjzeDjXVTayAmYnh9n1oqPSFnV6umLOYr9lZtqV9rKz85k3fGQuh6t2Yr3DiOx//LRdvP061mOQ==" saltValue="+R1cJAk8uUHACXVc/8Bf3w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:I2"/>
@@ -9226,9 +9232,11 @@
     <hyperlink ref="F1" r:id="rId4" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{312D6457-0D67-4610-B478-F5AE649B98F6}"/>
     <hyperlink ref="E1:E2" r:id="rId5" location="individualConditions" display="CONDITION_AT_CAPTURE" xr:uid="{F4906E56-6A88-4C64-867C-2ABD778A70BA}"/>
     <hyperlink ref="F1:F2" r:id="rId6" location="individualConditions" display="CONDITION_AT_RELEASE" xr:uid="{EFA1D569-0D47-49ED-B0FE-53D3A24E5072}"/>
+    <hyperlink ref="H1:H2" r:id="rId7" location="logicalResponses" display="BROUGHT_ONBOARD" xr:uid="{BE2D5C4E-F649-A249-B9E9-4C28A175E0FB}"/>
+    <hyperlink ref="J1:J2" r:id="rId8" location="logicalResponses" display="REVIVAL" xr:uid="{C7306B6C-F527-5849-8C5B-733F17EACDC6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E655CDB6-0B65-AF48-A000-1E7FBFA54934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF65BCDF-65DF-1B4E-B7A8-E00BD04FB54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16420" tabRatio="879" firstSheet="9" activeTab="10" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16420" tabRatio="879" firstSheet="9" activeTab="11" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -9269,10 +9269,10 @@
       <c r="D1" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="114" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="33" t="s">
@@ -12095,7 +12095,7 @@
       <c r="L201" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="atCsfaQ/Wqa05oY0/VI6TFi+I2NXWNTJgSm76H37XWGla1PXU95wuw4Y7lxV3gUUgepEXdCeLWyl2wtd/jFNBQ==" saltValue="bBGMR4jLd0WwJNjJRc35BQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QMw2cG8bGvhh0Fd8tMDI22dYVyFI/+1OdAQh7QlavhKJrDyuSu6VqVJ6uqpP8ZzZ8VOBXTcz3nOpUwlBJ2ge4w==" saltValue="VzeJkKzahBCc5aLAXJwkGA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -12103,6 +12103,8 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="G1" r:id="rId1" location="tagTypes" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
+    <hyperlink ref="E1" r:id="rId2" location="logicalResponses" xr:uid="{4978B5C2-9384-0242-8D3E-118677427F5C}"/>
+    <hyperlink ref="F1" r:id="rId3" location="logicalResponses" xr:uid="{198380F3-20E3-D84F-90EB-5F522A6A7667}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF65BCDF-65DF-1B4E-B7A8-E00BD04FB54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BBF35A-2A31-564A-A9C4-35951F485C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16420" tabRatio="879" firstSheet="9" activeTab="11" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="13740" yWindow="900" windowWidth="15500" windowHeight="16420" tabRatio="879" firstSheet="10" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -1121,6 +1121,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1192,6 +1198,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1265,18 +1283,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1289,6 +1295,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1298,9 +1313,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1315,18 +1327,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1672,24 +1672,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="7"/>
@@ -1739,15 +1739,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="13"/>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="58"/>
+      <c r="D8" s="60"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="58"/>
+      <c r="G8" s="60"/>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -1929,11 +1929,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="13"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="61"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -2004,55 +2004,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="C1" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E1" s="77" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="99" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="101" t="s">
         <v>169</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99" t="s">
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="93" t="s">
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="P1" s="72" t="s">
+      <c r="P1" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="72" t="s">
+      <c r="Q1" s="76"/>
+      <c r="R1" s="74" t="s">
         <v>167</v>
       </c>
-      <c r="S1" s="73"/>
-      <c r="T1" s="74"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="76"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="110"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="98"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="79"/>
       <c r="F2" s="35" t="s">
         <v>19</v>
       </c>
@@ -2080,7 +2080,7 @@
       <c r="N2" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="O2" s="95"/>
+      <c r="O2" s="100"/>
       <c r="P2" s="37" t="s">
         <v>52</v>
       </c>
@@ -6500,17 +6500,17 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="O1:O2"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="L1:N1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="O1:O2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 I2 K2 L2 O1:O2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
@@ -6558,52 +6558,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="C1" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="93" t="s">
+      <c r="E1" s="98" t="s">
         <v>170</v>
       </c>
-      <c r="F1" s="93" t="s">
+      <c r="F1" s="98" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="93" t="s">
+      <c r="G1" s="98" t="s">
         <v>172</v>
       </c>
       <c r="H1" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="94" t="s">
+      <c r="I1" s="99" t="s">
         <v>173</v>
       </c>
       <c r="J1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="111" t="s">
+      <c r="K1" s="115" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="110"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
       <c r="H2" s="117"/>
-      <c r="I2" s="95"/>
+      <c r="I2" s="100"/>
       <c r="J2" s="117"/>
-      <c r="K2" s="82"/>
+      <c r="K2" s="87"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
@@ -9208,17 +9208,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="UEOkJqql+6bXjzeDjXVTayAmYnh9n1oqPSFnV6umLOYr9lZtqV9rKz85k3fGQuh6t2Yr3DiOx//LRdvP061mOQ==" saltValue="+R1cJAk8uUHACXVc/8Bf3w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 G1:G2 I1:I2 E1:E2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -9269,10 +9269,10 @@
       <c r="D1" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="114" t="s">
+      <c r="E1" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="114" t="s">
+      <c r="F1" s="52" t="s">
         <v>41</v>
       </c>
       <c r="G1" s="33" t="s">
@@ -13747,7 +13747,7 @@
       <c r="F201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bSliHqJ5EQ8eQgeRA8sv66irJTtOSg2Dpyv1czukCBLCPP3mvckfqDxnsbMeTzr3ypfyirn8i1xOz/6LVG9EzQ==" saltValue="anAW88Zh6pNEamPd5ppVcw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{A7F07E3F-7588-4A6B-9139-C33F06BE5D6F}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -13792,117 +13792,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62" t="s">
+      <c r="C1" s="64"/>
+      <c r="D1" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="65" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="67" t="s">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="68"/>
-      <c r="F3" s="63" t="s">
+      <c r="E3" s="70"/>
+      <c r="F3" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="69" t="s">
+      <c r="G3" s="66"/>
+      <c r="H3" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="63" t="s">
+      <c r="J3" s="70"/>
+      <c r="K3" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="L3" s="64"/>
-      <c r="M3" s="69" t="s">
+      <c r="L3" s="66"/>
+      <c r="M3" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="62" t="s">
+      <c r="N3" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62" t="s">
+      <c r="O3" s="64"/>
+      <c r="P3" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="72" t="s">
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="74"/>
+      <c r="V3" s="75"/>
+      <c r="W3" s="75"/>
+      <c r="X3" s="76"/>
     </row>
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="62"/>
+      <c r="A4" s="64"/>
       <c r="B4" s="31" t="s">
         <v>78</v>
       </c>
@@ -13921,7 +13921,7 @@
       <c r="G4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="70"/>
+      <c r="H4" s="72"/>
       <c r="I4" s="30" t="s">
         <v>100</v>
       </c>
@@ -13934,7 +13934,7 @@
       <c r="L4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="70"/>
+      <c r="M4" s="72"/>
       <c r="N4" s="31" t="s">
         <v>5</v>
       </c>
@@ -19211,87 +19211,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="88" t="s">
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="89"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="93" t="s">
+      <c r="H1" s="94"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="98" t="s">
         <v>179</v>
       </c>
-      <c r="K1" s="96" t="s">
+      <c r="K1" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="76" t="s">
+      <c r="L1" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="78"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="83"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="75"/>
-      <c r="B2" s="62" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="91" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="87" t="s">
+      <c r="F2" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="I2" s="96" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="94"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="79" t="s">
+      <c r="J2" s="99"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="84" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79" t="s">
+      <c r="M2" s="84"/>
+      <c r="N2" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="O2" s="79"/>
-      <c r="P2" s="80" t="s">
+      <c r="O2" s="84"/>
+      <c r="P2" s="85" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="70"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="98"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="79"/>
       <c r="L3" s="31" t="s">
         <v>3</v>
       </c>
@@ -19304,7 +19304,7 @@
       <c r="O3" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="P3" s="80"/>
+      <c r="P3" s="85"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -19417,7 +19417,6 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -22907,8 +22906,9 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ypyoobc0IMiFdv0nKqzOh3acPZcndwCUBsTgOroSOIeoClJWdTuY3LtW7nXX7TL0JoutT2WJDIW3JVWK87zuUw==" saltValue="s+CLOox3+O9kbG7AiXx2bQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="J1:J3"/>
     <mergeCell ref="K1:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="L1:P1"/>
@@ -22925,7 +22925,6 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J1:J3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -22970,47 +22969,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="84" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84" t="s">
         <v>114</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="75"/>
-      <c r="B2" s="65" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="69" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="69" t="s">
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="71" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="70"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="30" t="s">
         <v>100</v>
       </c>
@@ -23023,7 +23022,7 @@
       <c r="E3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="70"/>
+      <c r="F3" s="72"/>
       <c r="G3" s="30" t="s">
         <v>100</v>
       </c>
@@ -23036,7 +23035,7 @@
       <c r="J3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="70"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -25712,156 +25711,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="74" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="72" t="s">
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="74" t="s">
         <v>141</v>
       </c>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="74"/>
-      <c r="AH1" s="72" t="s">
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
+      <c r="Y1" s="75"/>
+      <c r="Z1" s="75"/>
+      <c r="AA1" s="75"/>
+      <c r="AB1" s="75"/>
+      <c r="AC1" s="75"/>
+      <c r="AD1" s="75"/>
+      <c r="AE1" s="75"/>
+      <c r="AF1" s="75"/>
+      <c r="AG1" s="76"/>
+      <c r="AH1" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="AI1" s="73"/>
-      <c r="AJ1" s="73"/>
-      <c r="AK1" s="73"/>
-      <c r="AL1" s="73"/>
-      <c r="AM1" s="73"/>
-      <c r="AN1" s="73"/>
-      <c r="AO1" s="74"/>
+      <c r="AI1" s="75"/>
+      <c r="AJ1" s="75"/>
+      <c r="AK1" s="75"/>
+      <c r="AL1" s="75"/>
+      <c r="AM1" s="75"/>
+      <c r="AN1" s="75"/>
+      <c r="AO1" s="76"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="75"/>
-      <c r="B2" s="81" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="86" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="102" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="93" t="s">
+      <c r="D2" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="99" t="s">
+      <c r="E2" s="101" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99" t="s">
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="101" t="s">
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="103" t="s">
         <v>184</v>
       </c>
-      <c r="L2" s="87" t="s">
+      <c r="L2" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="99" t="s">
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="87" t="s">
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="87"/>
-      <c r="U2" s="112" t="s">
+      <c r="T2" s="92"/>
+      <c r="U2" s="105" t="s">
         <v>127</v>
       </c>
-      <c r="V2" s="112" t="s">
+      <c r="V2" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="112" t="s">
+      <c r="W2" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="112" t="s">
+      <c r="X2" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="112" t="s">
+      <c r="Y2" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="112" t="s">
+      <c r="Z2" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="112" t="s">
+      <c r="AA2" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="112" t="s">
+      <c r="AB2" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="112" t="s">
+      <c r="AC2" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="112" t="s">
+      <c r="AD2" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="112" t="s">
+      <c r="AE2" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="112" t="s">
+      <c r="AF2" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="112" t="s">
+      <c r="AG2" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="87" t="s">
+      <c r="AH2" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="AI2" s="87"/>
-      <c r="AJ2" s="87" t="s">
+      <c r="AI2" s="92"/>
+      <c r="AJ2" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="AK2" s="87"/>
-      <c r="AL2" s="87" t="s">
+      <c r="AK2" s="92"/>
+      <c r="AL2" s="92" t="s">
         <v>139</v>
       </c>
-      <c r="AM2" s="87"/>
-      <c r="AN2" s="87" t="s">
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="AO2" s="87"/>
+      <c r="AO2" s="92"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A3" s="70"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="95"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="39" t="s">
         <v>20</v>
       </c>
@@ -25880,7 +25879,7 @@
       <c r="J3" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="K3" s="102"/>
+      <c r="K3" s="104"/>
       <c r="L3" s="30" t="s">
         <v>118</v>
       </c>
@@ -25908,19 +25907,19 @@
       <c r="T3" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="U3" s="112"/>
-      <c r="V3" s="112"/>
-      <c r="W3" s="112"/>
-      <c r="X3" s="112"/>
-      <c r="Y3" s="112"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="112"/>
-      <c r="AB3" s="112"/>
-      <c r="AC3" s="112"/>
-      <c r="AD3" s="112"/>
-      <c r="AE3" s="112"/>
-      <c r="AF3" s="112"/>
-      <c r="AG3" s="112"/>
+      <c r="U3" s="105"/>
+      <c r="V3" s="105"/>
+      <c r="W3" s="105"/>
+      <c r="X3" s="105"/>
+      <c r="Y3" s="105"/>
+      <c r="Z3" s="105"/>
+      <c r="AA3" s="105"/>
+      <c r="AB3" s="105"/>
+      <c r="AC3" s="105"/>
+      <c r="AD3" s="105"/>
+      <c r="AE3" s="105"/>
+      <c r="AF3" s="105"/>
+      <c r="AG3" s="105"/>
       <c r="AH3" s="41" t="s">
         <v>129</v>
       </c>
@@ -34549,6 +34548,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="KMk8iFoN3zdbSamIO5QoI5vr+1ZauOEkrFW9jZqT8WXmnzjv2f5XRCKnMtp2ZZV6ao+qLTzPyt4DPIWOB9bWBA==" saltValue="6784kBKSj4D5BGLAkX4o/w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="X2:X3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -34565,20 +34578,6 @@
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="AN2:AO2"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3 D2:D3 L3 M3 N3 O3 P3 Q3 R3 AH3 AI3 AJ3 AK3 AL3 AM3 AO3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -34636,75 +34635,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="74" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="72" t="s">
+      <c r="C1" s="76"/>
+      <c r="D1" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="74"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="76"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="75"/>
-      <c r="B2" s="113" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="113" t="s">
+      <c r="C2" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87" t="s">
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87" t="s">
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="75"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="87" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="92" t="s">
         <v>187</v>
       </c>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87" t="s">
+      <c r="E3" s="92"/>
+      <c r="F3" s="92" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87" t="s">
+      <c r="G3" s="92"/>
+      <c r="H3" s="92" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87" t="s">
+      <c r="I3" s="92"/>
+      <c r="J3" s="92" t="s">
         <v>146</v>
       </c>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="70"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
       <c r="D4" s="45" t="s">
         <v>18</v>
       </c>
@@ -34737,2804 +34736,2804 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="6"/>
-      <c r="L117" s="6"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
-      <c r="L118" s="6"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6"/>
-      <c r="L120" s="6"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6"/>
-      <c r="L123" s="6"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
-      <c r="K124" s="6"/>
-      <c r="L124" s="6"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6"/>
-      <c r="L125" s="6"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
+      <c r="J125" s="2"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6"/>
-      <c r="L126" s="6"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
-      <c r="L127" s="6"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="6"/>
-      <c r="K128" s="6"/>
-      <c r="L128" s="6"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
+      <c r="J128" s="2"/>
+      <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="6"/>
-      <c r="L132" s="6"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="6"/>
-      <c r="L133" s="6"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
-      <c r="L141" s="6"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
+      <c r="J141" s="2"/>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="6"/>
-      <c r="L142" s="6"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+      <c r="J142" s="2"/>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="6"/>
-      <c r="L143" s="6"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="2"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="6"/>
-      <c r="L144" s="6"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+      <c r="I144" s="2"/>
+      <c r="J144" s="2"/>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="6"/>
-      <c r="L145" s="6"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+      <c r="I145" s="2"/>
+      <c r="J145" s="2"/>
+      <c r="K145" s="2"/>
+      <c r="L145" s="2"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="6"/>
-      <c r="L146" s="6"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+      <c r="I146" s="2"/>
+      <c r="J146" s="2"/>
+      <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="6"/>
-      <c r="L147" s="6"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="2"/>
+      <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
-      <c r="L148" s="6"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+      <c r="I148" s="2"/>
+      <c r="J148" s="2"/>
+      <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="6"/>
-      <c r="L149" s="6"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="2"/>
+      <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6"/>
-      <c r="L150" s="6"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="2"/>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
-      <c r="L151" s="6"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="2"/>
+      <c r="J151" s="2"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
-      <c r="L152" s="6"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+      <c r="I152" s="2"/>
+      <c r="J152" s="2"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6"/>
-      <c r="K153" s="6"/>
-      <c r="L153" s="6"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+      <c r="I153" s="2"/>
+      <c r="J153" s="2"/>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
-      <c r="L154" s="6"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+      <c r="I154" s="2"/>
+      <c r="J154" s="2"/>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
-      <c r="L155" s="6"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+      <c r="I155" s="2"/>
+      <c r="J155" s="2"/>
+      <c r="K155" s="2"/>
+      <c r="L155" s="2"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6"/>
-      <c r="K157" s="6"/>
-      <c r="L157" s="6"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
-      <c r="L158" s="6"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+      <c r="I158" s="2"/>
+      <c r="J158" s="2"/>
+      <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
-      <c r="L159" s="6"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+      <c r="I159" s="2"/>
+      <c r="J159" s="2"/>
+      <c r="K159" s="2"/>
+      <c r="L159" s="2"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="6"/>
-      <c r="K160" s="6"/>
-      <c r="L160" s="6"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="I160" s="2"/>
+      <c r="J160" s="2"/>
+      <c r="K160" s="2"/>
+      <c r="L160" s="2"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
-      <c r="J161" s="6"/>
-      <c r="K161" s="6"/>
-      <c r="L161" s="6"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="I161" s="2"/>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
-      <c r="J162" s="6"/>
-      <c r="K162" s="6"/>
-      <c r="L162" s="6"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="I162" s="2"/>
+      <c r="J162" s="2"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="2"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
-      <c r="I163" s="6"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="6"/>
-      <c r="L163" s="6"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+      <c r="I163" s="2"/>
+      <c r="J163" s="2"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-      <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
-      <c r="I164" s="6"/>
-      <c r="J164" s="6"/>
-      <c r="K164" s="6"/>
-      <c r="L164" s="6"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2"/>
+      <c r="J164" s="2"/>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
-      <c r="I165" s="6"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
-      <c r="L165" s="6"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
+      <c r="J165" s="2"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
-      <c r="L166" s="6"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="2"/>
+      <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
-      <c r="L167" s="6"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
+      <c r="J167" s="2"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="6"/>
-      <c r="K168" s="6"/>
-      <c r="L168" s="6"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="2"/>
+      <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
-      <c r="K169" s="6"/>
-      <c r="L169" s="6"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+      <c r="I169" s="2"/>
+      <c r="J169" s="2"/>
+      <c r="K169" s="2"/>
+      <c r="L169" s="2"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
-      <c r="L170" s="6"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
-      <c r="L171" s="6"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+      <c r="I171" s="2"/>
+      <c r="J171" s="2"/>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-      <c r="K172" s="6"/>
-      <c r="L172" s="6"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+      <c r="I172" s="2"/>
+      <c r="J172" s="2"/>
+      <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
-      <c r="L173" s="6"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2"/>
+      <c r="J173" s="2"/>
+      <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
-      <c r="L174" s="6"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+      <c r="I175" s="2"/>
+      <c r="J175" s="2"/>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+      <c r="I176" s="2"/>
+      <c r="J176" s="2"/>
+      <c r="K176" s="2"/>
+      <c r="L176" s="2"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="6"/>
-      <c r="K177" s="6"/>
-      <c r="L177" s="6"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="6"/>
-      <c r="L178" s="6"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+      <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
-      <c r="J179" s="6"/>
-      <c r="K179" s="6"/>
-      <c r="L179" s="6"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+      <c r="I179" s="2"/>
+      <c r="J179" s="2"/>
+      <c r="K179" s="2"/>
+      <c r="L179" s="2"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
-      <c r="I180" s="6"/>
-      <c r="J180" s="6"/>
-      <c r="K180" s="6"/>
-      <c r="L180" s="6"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
+      <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
-      <c r="L181" s="6"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+      <c r="I181" s="2"/>
+      <c r="J181" s="2"/>
+      <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="6"/>
-      <c r="L182" s="6"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+      <c r="I182" s="2"/>
+      <c r="J182" s="2"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="6"/>
-      <c r="L183" s="6"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+      <c r="I183" s="2"/>
+      <c r="J183" s="2"/>
+      <c r="K183" s="2"/>
+      <c r="L183" s="2"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-      <c r="J184" s="6"/>
-      <c r="K184" s="6"/>
-      <c r="L184" s="6"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+      <c r="I184" s="2"/>
+      <c r="J184" s="2"/>
+      <c r="K184" s="2"/>
+      <c r="L184" s="2"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
-      <c r="L185" s="6"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+      <c r="I185" s="2"/>
+      <c r="J185" s="2"/>
+      <c r="K185" s="2"/>
+      <c r="L185" s="2"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
-      <c r="L186" s="6"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="2"/>
+      <c r="J186" s="2"/>
+      <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="6"/>
-      <c r="L187" s="6"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+      <c r="I187" s="2"/>
+      <c r="J187" s="2"/>
+      <c r="K187" s="2"/>
+      <c r="L187" s="2"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
-      <c r="L188" s="6"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+      <c r="I188" s="2"/>
+      <c r="J188" s="2"/>
+      <c r="K188" s="2"/>
+      <c r="L188" s="2"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-      <c r="L189" s="6"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+      <c r="I189" s="2"/>
+      <c r="J189" s="2"/>
+      <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="6"/>
-      <c r="L190" s="6"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="2"/>
+      <c r="I190" s="2"/>
+      <c r="J190" s="2"/>
+      <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="6"/>
-      <c r="L191" s="6"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2"/>
+      <c r="I191" s="2"/>
+      <c r="J191" s="2"/>
+      <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="6"/>
-      <c r="L192" s="6"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="2"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-      <c r="J193" s="6"/>
-      <c r="K193" s="6"/>
-      <c r="L193" s="6"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+      <c r="I193" s="2"/>
+      <c r="J193" s="2"/>
+      <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="6"/>
-      <c r="L194" s="6"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="2"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
-      <c r="J195" s="6"/>
-      <c r="K195" s="6"/>
-      <c r="L195" s="6"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+      <c r="I195" s="2"/>
+      <c r="J195" s="2"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="6"/>
-      <c r="L196" s="6"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
+      <c r="J196" s="2"/>
+      <c r="K196" s="2"/>
+      <c r="L196" s="2"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
-      <c r="L197" s="6"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="6"/>
-      <c r="L198" s="6"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="2"/>
+      <c r="I198" s="2"/>
+      <c r="J198" s="2"/>
+      <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-      <c r="J199" s="6"/>
-      <c r="K199" s="6"/>
-      <c r="L199" s="6"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
+      <c r="J199" s="2"/>
+      <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-      <c r="J200" s="6"/>
-      <c r="K200" s="6"/>
-      <c r="L200" s="6"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
-      <c r="J201" s="6"/>
-      <c r="K201" s="6"/>
-      <c r="L201" s="6"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="2"/>
+      <c r="J201" s="2"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
-      <c r="D202" s="6"/>
-      <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
-      <c r="G202" s="6"/>
-      <c r="H202" s="6"/>
-      <c r="I202" s="6"/>
-      <c r="J202" s="6"/>
-      <c r="K202" s="6"/>
-      <c r="L202" s="6"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+      <c r="H202" s="2"/>
+      <c r="I202" s="2"/>
+      <c r="J202" s="2"/>
+      <c r="K202" s="2"/>
+      <c r="L202" s="2"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
-      <c r="D203" s="6"/>
-      <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
-      <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
-      <c r="I203" s="6"/>
-      <c r="J203" s="6"/>
-      <c r="K203" s="6"/>
-      <c r="L203" s="6"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+      <c r="H203" s="2"/>
+      <c r="I203" s="2"/>
+      <c r="J203" s="2"/>
+      <c r="K203" s="2"/>
+      <c r="L203" s="2"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="6"/>
-      <c r="L204" s="6"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="2"/>
+      <c r="I204" s="2"/>
+      <c r="J204" s="2"/>
+      <c r="K204" s="2"/>
+      <c r="L204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6ovehArg0e9iLe13x1bzFJTxaXKKK7Ls6uaVbc2hU33Q3qzwlkEb3XqzZb75+ziaKviLibNLSoJXEDqOtUv5Ow==" saltValue="K49j7WadggjQwrZPE7mjOQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="A1:A4"/>
@@ -37584,91 +37583,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="100" t="s">
+      <c r="D1" s="68"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="102" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="105" t="s">
+      <c r="K1" s="110" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="87" t="s">
+      <c r="L1" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="87" t="s">
+      <c r="M1" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="N1" s="87" t="s">
+      <c r="N1" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="O1" s="72"/>
-      <c r="P1" s="69" t="s">
+      <c r="O1" s="74"/>
+      <c r="P1" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" s="74" t="s">
+      <c r="Q1" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="R1" s="87" t="s">
+      <c r="R1" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="87"/>
-      <c r="T1" s="87"/>
-      <c r="U1" s="87"/>
-      <c r="V1" s="87"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="75"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="106" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="99" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="87" t="s">
+      <c r="S2" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="T2" s="87"/>
-      <c r="U2" s="87" t="s">
+      <c r="T2" s="92"/>
+      <c r="U2" s="92" t="s">
         <v>157</v>
       </c>
-      <c r="V2" s="87"/>
+      <c r="V2" s="92"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="63"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="65"/>
       <c r="D3" s="31" t="s">
         <v>0</v>
       </c>
@@ -37687,23 +37686,23 @@
       <c r="I3" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="98"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
       <c r="N3" s="36" t="s">
         <v>70</v>
       </c>
       <c r="O3" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="114" t="s">
+      <c r="P3" s="72"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="T3" s="114" t="s">
+      <c r="T3" s="52" t="s">
         <v>73</v>
       </c>
       <c r="U3" s="33" t="s">
@@ -42517,11 +42516,6 @@
   <sheetProtection algorithmName="SHA-512" hashValue="LGbLE0X4mphbrvyDB8iHZbZ5jGyiClFuG1okIajSb/6AE438B82i1uIvOTrWorRsJspA6UxPow4rvWi+AhQlIA==" saltValue="1ksA3tQoetcJpOHsQN0vtA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:T2"/>
@@ -42534,6 +42528,11 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="P1:P3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K3 I3 F3 G3 H3 U3 V3" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -42579,7 +42578,7 @@
       <c r="B1" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="115" t="s">
+      <c r="C1" s="53" t="s">
         <v>74</v>
       </c>
       <c r="D1" s="35" t="s">
@@ -42588,7 +42587,7 @@
       <c r="E1" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="115" t="s">
+      <c r="F1" s="53" t="s">
         <v>75</v>
       </c>
     </row>
@@ -44229,47 +44228,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="77" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="107" t="s">
+      <c r="E1" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="108"/>
-      <c r="G1" s="96" t="s">
+      <c r="F1" s="112"/>
+      <c r="G1" s="77" t="s">
         <v>162</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="66"/>
-      <c r="K1" s="71"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="73"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="98"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="79"/>
       <c r="E2" s="38" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="98"/>
-      <c r="H2" s="70"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="72"/>
       <c r="I2" s="38" t="s">
         <v>163</v>
       </c>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BBF35A-2A31-564A-A9C4-35951F485C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710ACEAB-69E2-B945-8680-8505DB8F0894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="900" windowWidth="15500" windowHeight="16420" tabRatio="879" firstSheet="10" activeTab="12" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="13740" yWindow="900" windowWidth="15500" windowHeight="16420" tabRatio="879" activeTab="2" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -6498,7 +6498,7 @@
       <c r="T202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3qOMxfB9LqsHrZTN/PHvOq+TVrpVLdhmwC43FTgCeEgXWUaACNo8KJCFeAzgBey/Z1MHtl5DW1/+/yDYgb2uMA==" saltValue="HkiVk2jjUX/+IQOX2cd3+A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -13747,7 +13747,7 @@
       <c r="F201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HbibJB+DtoJIrlOwst4Na69KNz9rrCguyZhGwya3z1puDEnYqxKRQ9LEgi2pyLw1WYhIuBABzM44j+PXXSIOKg==" saltValue="ibe+Wn0asEHETkji3RN2Ew==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{A7F07E3F-7588-4A6B-9139-C33F06BE5D6F}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -22906,7 +22906,7 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IIhoLAtvbmDru1SgimWO/AwLd5/UWio0KXbcC3RcqSPS0dgq3MZDRLNgyFiO2h4WjWaF8HiVrbnXJnVJHVjraA==" saltValue="f442cmp87p7Ti3VieVWKAg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="K1:K3"/>
@@ -37533,7 +37533,7 @@
       <c r="L204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="B0Wn7tY6nlhryE6G92vE9K6mFTjzzZYp5W3UwdmQRnD38VtWr+Eoth9mVUf3o2Aqife52Q9fYuPaT56M0zB39g==" saltValue="e+XBQWPatMSb6ygwI0GFAA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="A1:A4"/>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710ACEAB-69E2-B945-8680-8505DB8F0894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BDAEFF-433E-0E4E-AF73-D7BB7CA9D42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="900" windowWidth="15500" windowHeight="16420" tabRatio="879" activeTab="2" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="13740" yWindow="900" windowWidth="15500" windowHeight="16420" tabRatio="879" firstSheet="1" activeTab="2" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -9299,2803 +9299,2803 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="6"/>
-      <c r="L117" s="6"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
-      <c r="L118" s="6"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6"/>
-      <c r="L120" s="6"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6"/>
-      <c r="L123" s="6"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
-      <c r="K124" s="6"/>
-      <c r="L124" s="6"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6"/>
-      <c r="L125" s="6"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
+      <c r="J125" s="2"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6"/>
-      <c r="L126" s="6"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
-      <c r="L127" s="6"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="6"/>
-      <c r="K128" s="6"/>
-      <c r="L128" s="6"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
+      <c r="J128" s="2"/>
+      <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="6"/>
-      <c r="L132" s="6"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="6"/>
-      <c r="L133" s="6"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
-      <c r="L141" s="6"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
+      <c r="J141" s="2"/>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="6"/>
-      <c r="L142" s="6"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+      <c r="J142" s="2"/>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="6"/>
-      <c r="L143" s="6"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="2"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="6"/>
-      <c r="L144" s="6"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+      <c r="I144" s="2"/>
+      <c r="J144" s="2"/>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="6"/>
-      <c r="L145" s="6"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+      <c r="I145" s="2"/>
+      <c r="J145" s="2"/>
+      <c r="K145" s="2"/>
+      <c r="L145" s="2"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="6"/>
-      <c r="L146" s="6"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+      <c r="I146" s="2"/>
+      <c r="J146" s="2"/>
+      <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="6"/>
-      <c r="L147" s="6"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="2"/>
+      <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
-      <c r="L148" s="6"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+      <c r="I148" s="2"/>
+      <c r="J148" s="2"/>
+      <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="6"/>
-      <c r="L149" s="6"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="2"/>
+      <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6"/>
-      <c r="L150" s="6"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="2"/>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
-      <c r="L151" s="6"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="2"/>
+      <c r="J151" s="2"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
-      <c r="L152" s="6"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+      <c r="I152" s="2"/>
+      <c r="J152" s="2"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6"/>
-      <c r="K153" s="6"/>
-      <c r="L153" s="6"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+      <c r="I153" s="2"/>
+      <c r="J153" s="2"/>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
-      <c r="L154" s="6"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+      <c r="I154" s="2"/>
+      <c r="J154" s="2"/>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
-      <c r="L155" s="6"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+      <c r="I155" s="2"/>
+      <c r="J155" s="2"/>
+      <c r="K155" s="2"/>
+      <c r="L155" s="2"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6"/>
-      <c r="K157" s="6"/>
-      <c r="L157" s="6"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
-      <c r="L158" s="6"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+      <c r="I158" s="2"/>
+      <c r="J158" s="2"/>
+      <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
-      <c r="L159" s="6"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+      <c r="I159" s="2"/>
+      <c r="J159" s="2"/>
+      <c r="K159" s="2"/>
+      <c r="L159" s="2"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="6"/>
-      <c r="K160" s="6"/>
-      <c r="L160" s="6"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="I160" s="2"/>
+      <c r="J160" s="2"/>
+      <c r="K160" s="2"/>
+      <c r="L160" s="2"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
-      <c r="J161" s="6"/>
-      <c r="K161" s="6"/>
-      <c r="L161" s="6"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="I161" s="2"/>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
-      <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
-      <c r="J162" s="6"/>
-      <c r="K162" s="6"/>
-      <c r="L162" s="6"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="I162" s="2"/>
+      <c r="J162" s="2"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="2"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
-      <c r="I163" s="6"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="6"/>
-      <c r="L163" s="6"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+      <c r="I163" s="2"/>
+      <c r="J163" s="2"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-      <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
-      <c r="I164" s="6"/>
-      <c r="J164" s="6"/>
-      <c r="K164" s="6"/>
-      <c r="L164" s="6"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2"/>
+      <c r="J164" s="2"/>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
-      <c r="I165" s="6"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
-      <c r="L165" s="6"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
+      <c r="J165" s="2"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
-      <c r="L166" s="6"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="2"/>
+      <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
-      <c r="L167" s="6"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
+      <c r="J167" s="2"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="6"/>
-      <c r="K168" s="6"/>
-      <c r="L168" s="6"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="2"/>
+      <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
-      <c r="K169" s="6"/>
-      <c r="L169" s="6"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+      <c r="I169" s="2"/>
+      <c r="J169" s="2"/>
+      <c r="K169" s="2"/>
+      <c r="L169" s="2"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
-      <c r="L170" s="6"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
-      <c r="L171" s="6"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+      <c r="I171" s="2"/>
+      <c r="J171" s="2"/>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-      <c r="K172" s="6"/>
-      <c r="L172" s="6"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+      <c r="I172" s="2"/>
+      <c r="J172" s="2"/>
+      <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
-      <c r="L173" s="6"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2"/>
+      <c r="J173" s="2"/>
+      <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
-      <c r="L174" s="6"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+      <c r="I175" s="2"/>
+      <c r="J175" s="2"/>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
+      <c r="I176" s="2"/>
+      <c r="J176" s="2"/>
+      <c r="K176" s="2"/>
+      <c r="L176" s="2"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="6"/>
-      <c r="K177" s="6"/>
-      <c r="L177" s="6"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="6"/>
-      <c r="L178" s="6"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+      <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
-      <c r="J179" s="6"/>
-      <c r="K179" s="6"/>
-      <c r="L179" s="6"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="2"/>
+      <c r="I179" s="2"/>
+      <c r="J179" s="2"/>
+      <c r="K179" s="2"/>
+      <c r="L179" s="2"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
-      <c r="I180" s="6"/>
-      <c r="J180" s="6"/>
-      <c r="K180" s="6"/>
-      <c r="L180" s="6"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="2"/>
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
+      <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
-      <c r="L181" s="6"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+      <c r="I181" s="2"/>
+      <c r="J181" s="2"/>
+      <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="6"/>
-      <c r="L182" s="6"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="2"/>
+      <c r="I182" s="2"/>
+      <c r="J182" s="2"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="6"/>
-      <c r="L183" s="6"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="2"/>
+      <c r="I183" s="2"/>
+      <c r="J183" s="2"/>
+      <c r="K183" s="2"/>
+      <c r="L183" s="2"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-      <c r="J184" s="6"/>
-      <c r="K184" s="6"/>
-      <c r="L184" s="6"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="2"/>
+      <c r="I184" s="2"/>
+      <c r="J184" s="2"/>
+      <c r="K184" s="2"/>
+      <c r="L184" s="2"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
-      <c r="L185" s="6"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="2"/>
+      <c r="I185" s="2"/>
+      <c r="J185" s="2"/>
+      <c r="K185" s="2"/>
+      <c r="L185" s="2"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
-      <c r="L186" s="6"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="2"/>
+      <c r="J186" s="2"/>
+      <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="6"/>
-      <c r="L187" s="6"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="2"/>
+      <c r="I187" s="2"/>
+      <c r="J187" s="2"/>
+      <c r="K187" s="2"/>
+      <c r="L187" s="2"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
-      <c r="L188" s="6"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="2"/>
+      <c r="I188" s="2"/>
+      <c r="J188" s="2"/>
+      <c r="K188" s="2"/>
+      <c r="L188" s="2"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-      <c r="L189" s="6"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="2"/>
+      <c r="I189" s="2"/>
+      <c r="J189" s="2"/>
+      <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="6"/>
-      <c r="L190" s="6"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="2"/>
+      <c r="I190" s="2"/>
+      <c r="J190" s="2"/>
+      <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="6"/>
-      <c r="L191" s="6"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="2"/>
+      <c r="I191" s="2"/>
+      <c r="J191" s="2"/>
+      <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="6"/>
-      <c r="L192" s="6"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="2"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-      <c r="J193" s="6"/>
-      <c r="K193" s="6"/>
-      <c r="L193" s="6"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="2"/>
+      <c r="I193" s="2"/>
+      <c r="J193" s="2"/>
+      <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="6"/>
-      <c r="L194" s="6"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="2"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
-      <c r="J195" s="6"/>
-      <c r="K195" s="6"/>
-      <c r="L195" s="6"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+      <c r="H195" s="2"/>
+      <c r="I195" s="2"/>
+      <c r="J195" s="2"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="6"/>
-      <c r="L196" s="6"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
+      <c r="J196" s="2"/>
+      <c r="K196" s="2"/>
+      <c r="L196" s="2"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
-      <c r="L197" s="6"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="6"/>
-      <c r="L198" s="6"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="2"/>
+      <c r="I198" s="2"/>
+      <c r="J198" s="2"/>
+      <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-      <c r="J199" s="6"/>
-      <c r="K199" s="6"/>
-      <c r="L199" s="6"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
+      <c r="J199" s="2"/>
+      <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-      <c r="J200" s="6"/>
-      <c r="K200" s="6"/>
-      <c r="L200" s="6"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
-      <c r="J201" s="6"/>
-      <c r="K201" s="6"/>
-      <c r="L201" s="6"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="2"/>
+      <c r="J201" s="2"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QMw2cG8bGvhh0Fd8tMDI22dYVyFI/+1OdAQh7QlavhKJrDyuSu6VqVJ6uqpP8ZzZ8VOBXTcz3nOpUwlBJ2ge4w==" saltValue="VzeJkKzahBCc5aLAXJwkGA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iVe1t/OsbbdBLFGlWh+NSkmwiJ8zxaIfOzzuiqPCrGJ4Lm1Yfs5BFGHpYF2Kpl2IyLvc+pMlDdJZ+ks/fQqbKw==" saltValue="2Q25QnDe9hGsAD4y75NURA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -22932,16 +22932,15 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C2:C3" r:id="rId1" location="countries" display="FLAG_OR_CHARTERING_STATE" xr:uid="{DA9CE3B1-74F9-4268-98AF-290FAC660EAD}"/>
-    <hyperlink ref="G2" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{4939BF01-E483-4611-A010-33B090D54E39}"/>
-    <hyperlink ref="J1" r:id="rId3" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{E9AF38ED-FD60-4672-8F14-35015A129362}"/>
-    <hyperlink ref="M3" r:id="rId4" location="countries" xr:uid="{10913ED0-4328-48D4-A042-6201D824CECA}"/>
-    <hyperlink ref="O3" r:id="rId5" location="countries" xr:uid="{3CF4C3FC-91EE-45A1-9C82-1871A741D19A}"/>
-    <hyperlink ref="H2" r:id="rId6" display="PORT_CODE" xr:uid="{C4D05E8A-B26C-4196-BF44-6883318591EB}"/>
-    <hyperlink ref="H2:H3" r:id="rId7" location="Ports" display="PORT" xr:uid="{44C3BCF2-CCDC-4213-9DFE-452592BB90D5}"/>
-    <hyperlink ref="G2:G3" r:id="rId8" location="countries" display="COUNTRY" xr:uid="{BD07189D-03AA-4AF5-B0D3-FF12F3E2E8CA}"/>
-    <hyperlink ref="J1:J3" r:id="rId9" location="targetSpecies" display="LICENSED_TARGET_SPECIES" xr:uid="{3E5E8972-E643-454E-9E2D-3185227AEE27}"/>
-    <hyperlink ref="K1:K3" r:id="rId10" location="gears" display="MAIN_FISHING_GEAR" xr:uid="{F9AD52CB-F3F1-40EF-8481-E96A756947D1}"/>
+    <hyperlink ref="G2" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{4939BF01-E483-4611-A010-33B090D54E39}"/>
+    <hyperlink ref="J1" r:id="rId2" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{E9AF38ED-FD60-4672-8F14-35015A129362}"/>
+    <hyperlink ref="M3" r:id="rId3" location="countries" xr:uid="{10913ED0-4328-48D4-A042-6201D824CECA}"/>
+    <hyperlink ref="O3" r:id="rId4" location="countries" xr:uid="{3CF4C3FC-91EE-45A1-9C82-1871A741D19A}"/>
+    <hyperlink ref="H2" r:id="rId5" display="PORT_CODE" xr:uid="{C4D05E8A-B26C-4196-BF44-6883318591EB}"/>
+    <hyperlink ref="H2:H3" r:id="rId6" location="Ports" display="PORT" xr:uid="{44C3BCF2-CCDC-4213-9DFE-452592BB90D5}"/>
+    <hyperlink ref="G2:G3" r:id="rId7" location="countries" display="COUNTRY" xr:uid="{BD07189D-03AA-4AF5-B0D3-FF12F3E2E8CA}"/>
+    <hyperlink ref="J1:J3" r:id="rId8" location="targetSpecies" display="LICENSED_TARGET_SPECIES" xr:uid="{3E5E8972-E643-454E-9E2D-3185227AEE27}"/>
+    <hyperlink ref="K1:K3" r:id="rId9" location="gears" display="MAIN_FISHING_GEAR" xr:uid="{F9AD52CB-F3F1-40EF-8481-E96A756947D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/form_reporting_templates/ros/Form-ROS-PS.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PS.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BDAEFF-433E-0E4E-AF73-D7BB7CA9D42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7810E59A-A990-6E4A-B8C7-9C5140D47AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="c5/ou8Cml7ZkaDU47Tuu3WsAbYP19DC42wRzPBn3vsHWJE2MFn5j3m9vhk0UNMu/icNe5bym2Fttv6xJI1ZSAw==" workbookSaltValue="pG4NehU6lkQVWVHx3qNlvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="900" windowWidth="15500" windowHeight="16420" tabRatio="879" firstSheet="1" activeTab="2" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="13740" yWindow="900" windowWidth="15500" windowHeight="16420" tabRatio="879" firstSheet="6" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="26" r:id="rId1"/>
@@ -1199,6 +1199,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1271,17 +1283,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1296,12 +1299,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1313,6 +1310,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1326,13 +1326,13 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2016,25 +2016,25 @@
       <c r="D1" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="84" t="s">
+      <c r="F1" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="101" t="s">
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="102" t="s">
         <v>169</v>
       </c>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101" t="s">
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="98" t="s">
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="77" t="s">
         <v>38</v>
       </c>
       <c r="P1" s="74" t="s">
@@ -2052,7 +2052,7 @@
       <c r="B2" s="114"/>
       <c r="C2" s="114"/>
       <c r="D2" s="114"/>
-      <c r="E2" s="79"/>
+      <c r="E2" s="82"/>
       <c r="F2" s="35" t="s">
         <v>19</v>
       </c>
@@ -2080,7 +2080,7 @@
       <c r="N2" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="O2" s="100"/>
+      <c r="O2" s="79"/>
       <c r="P2" s="37" t="s">
         <v>52</v>
       </c>
@@ -6500,17 +6500,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="3qOMxfB9LqsHrZTN/PHvOq+TVrpVLdhmwC43FTgCeEgXWUaACNo8KJCFeAzgBey/Z1MHtl5DW1/+/yDYgb2uMA==" saltValue="HkiVk2jjUX/+IQOX2cd3+A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="O1:O2"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="L1:N1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="O1:O2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2 F2 H2 I2 K2 L2 O1:O2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
@@ -6570,25 +6570,25 @@
       <c r="D1" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="98" t="s">
+      <c r="E1" s="77" t="s">
         <v>170</v>
       </c>
-      <c r="F1" s="98" t="s">
+      <c r="F1" s="77" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="98" t="s">
+      <c r="G1" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="H1" s="116" t="s">
+      <c r="H1" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="J1" s="116" t="s">
+      <c r="J1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="115" t="s">
+      <c r="K1" s="117" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6597,13 +6597,13 @@
       <c r="B2" s="114"/>
       <c r="C2" s="114"/>
       <c r="D2" s="114"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="87"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="90"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
@@ -9208,17 +9208,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="UEOkJqql+6bXjzeDjXVTayAmYnh9n1oqPSFnV6umLOYr9lZtqV9rKz85k3fGQuh6t2Yr3DiOx//LRdvP061mOQ==" saltValue="+R1cJAk8uUHACXVc/8Bf3w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 G1:G2 I1:I2 E1:E2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -19214,84 +19214,84 @@
       <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="93" t="s">
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="98" t="s">
+      <c r="H1" s="97"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="77" t="s">
         <v>179</v>
       </c>
-      <c r="K1" s="77" t="s">
+      <c r="K1" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="81" t="s">
+      <c r="L1" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="83"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="86"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="80"/>
+      <c r="A2" s="83"/>
       <c r="B2" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="94" t="s">
         <v>177</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="G2" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="89" t="s">
+      <c r="H2" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="96" t="s">
+      <c r="I2" s="99" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="99"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="84" t="s">
+      <c r="J2" s="78"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84" t="s">
+      <c r="M2" s="87"/>
+      <c r="N2" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="O2" s="84"/>
-      <c r="P2" s="85" t="s">
+      <c r="O2" s="87"/>
+      <c r="P2" s="88" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="72"/>
       <c r="B3" s="64"/>
-      <c r="C3" s="91"/>
+      <c r="C3" s="94"/>
       <c r="D3" s="64"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="79"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="82"/>
       <c r="L3" s="31" t="s">
         <v>3</v>
       </c>
@@ -19304,7 +19304,7 @@
       <c r="O3" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="P3" s="85"/>
+      <c r="P3" s="88"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -22908,6 +22908,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="IIhoLAtvbmDru1SgimWO/AwLd5/UWio0KXbcC3RcqSPS0dgq3MZDRLNgyFiO2h4WjWaF8HiVrbnXJnVJHVjraA==" saltValue="f442cmp87p7Ti3VieVWKAg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="K1:K3"/>
     <mergeCell ref="A1:A3"/>
@@ -22924,7 +22925,6 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 H2:H3 J1:K1" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -22971,23 +22971,23 @@
       <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84" t="s">
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="80"/>
+      <c r="A2" s="83"/>
       <c r="B2" s="67" t="s">
         <v>98</v>
       </c>
@@ -25761,105 +25761,105 @@
       <c r="AO1" s="76"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="80"/>
-      <c r="B2" s="86" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="102" t="s">
+      <c r="C2" s="103" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="101" t="s">
+      <c r="E2" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101" t="s">
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="103" t="s">
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="104" t="s">
         <v>184</v>
       </c>
-      <c r="L2" s="92" t="s">
+      <c r="L2" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="101" t="s">
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="92" t="s">
+      <c r="Q2" s="102"/>
+      <c r="R2" s="102"/>
+      <c r="S2" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="92"/>
-      <c r="U2" s="105" t="s">
+      <c r="T2" s="95"/>
+      <c r="U2" s="101" t="s">
         <v>127</v>
       </c>
-      <c r="V2" s="105" t="s">
+      <c r="V2" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="105" t="s">
+      <c r="W2" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="105" t="s">
+      <c r="X2" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="105" t="s">
+      <c r="Y2" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="105" t="s">
+      <c r="Z2" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="105" t="s">
+      <c r="AA2" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="105" t="s">
+      <c r="AB2" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="105" t="s">
+      <c r="AC2" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="105" t="s">
+      <c r="AD2" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="105" t="s">
+      <c r="AE2" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="105" t="s">
+      <c r="AF2" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="105" t="s">
+      <c r="AG2" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="92" t="s">
+      <c r="AH2" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="AI2" s="92"/>
-      <c r="AJ2" s="92" t="s">
+      <c r="AI2" s="95"/>
+      <c r="AJ2" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="AK2" s="92"/>
-      <c r="AL2" s="92" t="s">
+      <c r="AK2" s="95"/>
+      <c r="AL2" s="95" t="s">
         <v>139</v>
       </c>
-      <c r="AM2" s="92"/>
-      <c r="AN2" s="92" t="s">
+      <c r="AM2" s="95"/>
+      <c r="AN2" s="95" t="s">
         <v>140</v>
       </c>
-      <c r="AO2" s="92"/>
+      <c r="AO2" s="95"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A3" s="72"/>
-      <c r="B3" s="87"/>
+      <c r="B3" s="90"/>
       <c r="C3" s="69"/>
-      <c r="D3" s="100"/>
+      <c r="D3" s="79"/>
       <c r="E3" s="39" t="s">
         <v>20</v>
       </c>
@@ -25878,7 +25878,7 @@
       <c r="J3" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="K3" s="104"/>
+      <c r="K3" s="105"/>
       <c r="L3" s="30" t="s">
         <v>118</v>
       </c>
@@ -25906,19 +25906,19 @@
       <c r="T3" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="U3" s="105"/>
-      <c r="V3" s="105"/>
-      <c r="W3" s="105"/>
-      <c r="X3" s="105"/>
-      <c r="Y3" s="105"/>
-      <c r="Z3" s="105"/>
-      <c r="AA3" s="105"/>
-      <c r="AB3" s="105"/>
-      <c r="AC3" s="105"/>
-      <c r="AD3" s="105"/>
-      <c r="AE3" s="105"/>
-      <c r="AF3" s="105"/>
-      <c r="AG3" s="105"/>
+      <c r="U3" s="101"/>
+      <c r="V3" s="101"/>
+      <c r="W3" s="101"/>
+      <c r="X3" s="101"/>
+      <c r="Y3" s="101"/>
+      <c r="Z3" s="101"/>
+      <c r="AA3" s="101"/>
+      <c r="AB3" s="101"/>
+      <c r="AC3" s="101"/>
+      <c r="AD3" s="101"/>
+      <c r="AE3" s="101"/>
+      <c r="AF3" s="101"/>
+      <c r="AG3" s="101"/>
       <c r="AH3" s="41" t="s">
         <v>129</v>
       </c>
@@ -34547,20 +34547,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="KMk8iFoN3zdbSamIO5QoI5vr+1ZauOEkrFW9jZqT8WXmnzjv2f5XRCKnMtp2ZZV6ao+qLTzPyt4DPIWOB9bWBA==" saltValue="6784kBKSj4D5BGLAkX4o/w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="X2:X3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -34577,6 +34563,20 @@
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="AN2:AO2"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3 D2:D3 L3 M3 N3 O3 P3 Q3 R3 AH3 AI3 AJ3 AK3 AL3 AM3 AO3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -34654,50 +34654,50 @@
       <c r="L1" s="76"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="80"/>
+      <c r="A2" s="83"/>
       <c r="B2" s="106" t="s">
         <v>61</v>
       </c>
       <c r="C2" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="92" t="s">
+      <c r="D2" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92" t="s">
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="80"/>
+      <c r="A3" s="83"/>
       <c r="B3" s="106"/>
       <c r="C3" s="106"/>
-      <c r="D3" s="92" t="s">
+      <c r="D3" s="95" t="s">
         <v>187</v>
       </c>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92" t="s">
+      <c r="E3" s="95"/>
+      <c r="F3" s="95" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92" t="s">
+      <c r="G3" s="95"/>
+      <c r="H3" s="95" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92" t="s">
+      <c r="I3" s="95"/>
+      <c r="J3" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="K3" s="92"/>
-      <c r="L3" s="92"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="72"/>
@@ -37593,25 +37593,25 @@
       </c>
       <c r="D1" s="68"/>
       <c r="E1" s="73"/>
-      <c r="F1" s="102" t="s">
+      <c r="F1" s="103" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="77" t="s">
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="110" t="s">
+      <c r="K1" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="92" t="s">
+      <c r="L1" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="92" t="s">
+      <c r="M1" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="N1" s="92" t="s">
+      <c r="N1" s="95" t="s">
         <v>66</v>
       </c>
       <c r="O1" s="74"/>
@@ -37621,18 +37621,18 @@
       <c r="Q1" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="R1" s="92" t="s">
+      <c r="R1" s="95" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92"/>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="107" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="110" t="s">
         <v>48</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -37640,28 +37640,28 @@
       </c>
       <c r="E2" s="73"/>
       <c r="F2" s="69"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
       <c r="O2" s="74"/>
-      <c r="P2" s="80"/>
+      <c r="P2" s="83"/>
       <c r="Q2" s="76"/>
-      <c r="R2" s="101" t="s">
+      <c r="R2" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="92" t="s">
+      <c r="S2" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="T2" s="92"/>
-      <c r="U2" s="92" t="s">
+      <c r="T2" s="95"/>
+      <c r="U2" s="95" t="s">
         <v>157</v>
       </c>
-      <c r="V2" s="92"/>
+      <c r="V2" s="95"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="72"/>
@@ -37685,10 +37685,10 @@
       <c r="I3" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="79"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
       <c r="N3" s="36" t="s">
         <v>70</v>
       </c>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="P3" s="72"/>
       <c r="Q3" s="76"/>
-      <c r="R3" s="101"/>
+      <c r="R3" s="102"/>
       <c r="S3" s="52" t="s">
         <v>72</v>
       </c>
@@ -42515,6 +42515,11 @@
   <sheetProtection algorithmName="SHA-512" hashValue="LGbLE0X4mphbrvyDB8iHZbZ5jGyiClFuG1okIajSb/6AE438B82i1uIvOTrWorRsJspA6UxPow4rvWi+AhQlIA==" saltValue="1ksA3tQoetcJpOHsQN0vtA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:T2"/>
@@ -42527,11 +42532,6 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K3 I3 F3 G3 H3 U3 V3" xr:uid="{7CB5582D-4A36-46D9-AA38-ED8FA154223A}">
@@ -44236,14 +44236,14 @@
       <c r="C1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="80" t="s">
         <v>160</v>
       </c>
       <c r="E1" s="111" t="s">
         <v>56</v>
       </c>
       <c r="F1" s="112"/>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="80" t="s">
         <v>162</v>
       </c>
       <c r="H1" s="71" t="s">
@@ -44259,14 +44259,14 @@
       <c r="A2" s="72"/>
       <c r="B2" s="72"/>
       <c r="C2" s="72"/>
-      <c r="D2" s="79"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="38" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="79"/>
+      <c r="G2" s="82"/>
       <c r="H2" s="72"/>
       <c r="I2" s="38" t="s">
         <v>163</v>
